--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -1531,7 +1531,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>pages/05_funil.py (nível 'Criar' do COBRA -- volume de discurso oficial)</t>
+          <t>dashboard/screens/{resumo,produzir,discurso_reacao,funil}.py (ADR 0021)</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>pages/02_insights.py; pages/05_funil.py (nível 'Consumir' do COBRA)</t>
+          <t>dashboard/screens/{resumo,produzir,funil}.py (ADR 0021)</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (ModelEnricher.write_profile_clusters_engagement), via scripts/run_profile_clustering_engagement.py</t>
+          <t>src/features/gold/model_enricher.py (ModelEnricher.write_profile_clusters_engagement), via src/modeling/orchestration.py::run_deterministic_modeling (pipeline.py --run-modeling / scripts/run_modeling.py) ou, isoladamente, via scripts/run_profile_clustering_engagement.py</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>pages/04_recommendations.py (comparação de perfil vs. pares do mesmo cluster)</t>
+          <t>dashboard/screens/comparar.py (Tela 4 "Comparar perfis", ADR 0021 -- comparação de perfil vs. pares do mesmo cluster)</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Roda pós-Gold-de-engajamento (lê governor_engagement) -- na Lambda serverless, é a etapa `model`, disparada depois de `load` (ver seção 3 do README).</t>
+          <t>Roda pós-Gold-de-engajamento (lê governor_engagement), dentro do mesmo estágio determinístico das demais tabelas de modelagem -- na Lambda serverless, é a etapa `model`, disparada depois de `load` (ver seção 3 do README).</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>pages/03_performance.py (comparação entre governadores, coeficientes da regressão)</t>
+          <t>pages/03_performance.py (comparação entre governadores, coeficientes da regressão) -- órfã desde a ADR 0021, sem entrypoint ativo (ver seção 4 do README)</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>pages/03_performance.py (dispersão previsto vs. real, resíduos)</t>
+          <t>pages/03_performance.py (dispersão previsto vs. real, resíduos) -- órfã desde a ADR 0021, sem entrypoint ativo (ver seção 4 do README)</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>pages/04_recommendations.py; pages/05_funil.py (priorização do que produzir a seguir)</t>
+          <t>dashboard/screens/{resumo,produzir,radar}.py (priorização do que produzir a seguir, ADR 0021)</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>app.py (KPI 'NSM médio da base'); pages/05_funil.py</t>
+          <t>dashboard/screens/resumo.py (Tela 1, ADR 0021)</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>src/dashboard/filters.py (agregação, quando/se a tabela existir); pages/05_funil.py (nível 'Criar' do COBRA)</t>
+          <t>Nenhum consumidor de produção hoje -- dashboard/screens/funil.py (Tela 6, ADR 0021) proíbe estruturalmente qualquer referência a esta tabela (ver teste test_funil_module_never_references_ugc_tables); src/dashboard/filters.py tem a função de agregação, mas não é chamada por nenhuma tela atual</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>pages/05_funil.py (Ficha 7 -- crescimento e retenção)</t>
+          <t>Nenhuma tela do dashboard atual (ADR 0021) consome esta tabela -- dashboard/core/data.py::load_growth_metrics() existe, mas não é chamada por nenhuma das 6 telas</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/clustering.py + scripts/run_profile_clustering_engagement.py</t>
+          <t>src/modeling/profile_clustering.py, via src/modeling/orchestration.py::run_deterministic_modeling (ou isoladamente via scripts/run_profile_clustering_engagement.py)</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Dashboards Streamlit (pages/01-05, app.py) e notebooks/03-07</t>
+          <t>Dashboard Streamlit (dashboard/app.py + dashboard/screens/*.py, ADR 0021; pages/02-03 remanescentes, órfãs) e notebooks/03-07</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>src/repositories/delta_repository.py + src/dashboard/*</t>
+          <t>src/repositories/delta_repository.py + dashboard/core/* + src/dashboard/*</t>
         </is>
       </c>
     </row>

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -13,15 +13,17 @@
     <sheet name="Colunas - Silver" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Colunas - Gold" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Linhagem" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Glossário de Métricas" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Actors Apify" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Glossário de Métricas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabelas'!$A$1:$K$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Colunas - Bronze'!$A$1:$E$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Colunas - Silver'!$A$1:$E$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$164</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Linhagem'!$A$1:$D$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Glossário de Métricas'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Linhagem'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Actors Apify'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Glossário de Métricas'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -488,7 +490,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Fonte técnica: src/schemas_delta.py (contratos PyArrow validados em runtime pelos writers). Fonte de negócio: leitura direta dos módulos src/features/*, src/modeling/*, config/settings.py.</t>
+          <t>Fonte técnica: src/schemas_delta.py (contratos PyArrow validados em runtime pelos writers). Fonte de negócio: leitura direta dos módulos src/features/*, src/modeling/*, config/settings.py. Fonte de actors/parâmetros de extração: src/data_extract/scraper.py e src/data_extract/ingestion.py (código realmente em produção), cruzada com a pesquisa primária em docs/research/apify-instagram-actors-cobra-mapping.md (preço/adoção/schema, consultada na Apify Store e API pública em 2026-09-08).</t>
         </is>
       </c>
     </row>
@@ -605,14 +607,21 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>3. Aba 'Linhagem' -- de onde cada tabela vem e o que a transformação aplica.</t>
+          <t>3. Aba 'Linhagem' -- de onde cada tabela vem e o que a transformação aplica, incluindo o hop pela landing zone (data/landing/&lt;run_id&gt;/*.json) ANTES de qualquer escrita Bronze.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>4. Aba 'Glossário de Métricas' -- fórmula completa de cada métrica derivada (% ENGAJAMENTO, NSM, Score ICE, CMGR, retenção, Y da regressão, cluster_score).</t>
+          <t>4. Aba 'Actors Apify' -- qual actor (slug + ID técnico) raspa cada entidade Bronze, com quais parâmetros REALMENTE usados em produção (src/data_extract/scraper.py), status produção/piloto e confiabilidade da fonte (cruzado com docs/research/apify-instagram-actors-cobra-mapping.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>5. Aba 'Glossário de Métricas' -- fórmula completa de cada métrica derivada (% ENGAJAMENTO, NSM, Score ICE, CMGR, retenção, Y da regressão, cluster_score).</t>
         </is>
       </c>
     </row>
@@ -748,12 +757,12 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Metadados de perfil (seguidores, verificação, categoria de negócio) coletados via apify/instagram-profile-scraper.</t>
+          <t>Metadados de perfil (seguidores, verificação, categoria de negócio) coletados via apify/instagram-scraper (ver aba Actors Apify), rodando em modo perfil (resultsType='details').</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Fidelidade total ao retorno do Apify -- nenhuma limpeza aqui; campos list/dict do Apify são serializados como JSON string (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Fidelidade total ao retorno do Apify -- nenhuma limpeza aqui; campos list/dict do Apify são serializados como JSON string (BronzeWriter._add_ingestion_metadata). Payload bruto arquivado em data/landing/&lt;run_id&gt;/profiles.json (ou /tmp/landing/... na Lambda) ANTES desta escrita -- ver aba Linhagem.</t>
         </is>
       </c>
     </row>
@@ -805,12 +814,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Posts do feed do Instagram (não-Reels) dos 27 perfis, via apify/instagram-scraper.</t>
+          <t>Posts do feed do Instagram (não-Reels) dos 27 perfis, via apify/instagram-post-scraper (ver aba Actors Apify).</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Não tem campo de comentário embutido (latestComments) -- por isso governor_sentiment/comments_clean só cobrem comentário de Reels, nunca de post de feed.</t>
+          <t>Não tem campo de comentário embutido (latestComments) -- por isso governor_sentiment/comments_clean só cobrem comentário de Reels, nunca de post de feed. Payload bruto arquivado em data/landing/&lt;run_id&gt;/posts.json (ou /tmp/landing/... na Lambda) ANTES desta escrita -- ver aba Linhagem.</t>
         </is>
       </c>
     </row>
@@ -862,12 +871,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Reels dos 27 perfis, incluindo os comentários mais recentes embutidos (latestComments) e, quando a flag paga includeTranscript está ativa, a transcrição de fala do vídeo.</t>
+          <t>Reels dos 27 perfis, via apify/instagram-reel-scraper (ver aba Actors Apify), incluindo os comentários mais recentes embutidos (latestComments) e, quando a flag paga includeTranscript está ativa, a transcrição de fala do vídeo.</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>`transcript` é nullable e só vem preenchido quando a execução ligou explicitamente a flag paga do actor (custo por minuto de vídeo) -- não confundir ausência com 'sem fala'.</t>
+          <t>`transcript` é nullable e só vem preenchido quando a execução ligou explicitamente a flag paga do actor (custo por minuto de vídeo) -- não confundir ausência com 'sem fala'. Payload bruto arquivado em data/landing/&lt;run_id&gt;/reels.json (ou /tmp/landing/... na Lambda) ANTES desta escrita -- ver aba Linhagem.</t>
         </is>
       </c>
     </row>
@@ -919,12 +928,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>UGC (user-generated content) de terceiros mencionando/marcando o governador, via apify/instagram-tagged-scraper.</t>
+          <t>UGC (user-generated content) de terceiros mencionando/marcando o governador, via apify/instagram-tagged-scraper (ver aba Actors Apify -- status PILOTO).</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>O piloto obrigatório da issue #93 (scripts/run_apify_mentions_pilot.py) grava só em data/pilot/*.json, FORA do Delta Lake -- os nomes de campo abaixo seguem a especificação da issue/ADR cruzada com docs/research/apify-instagram-actors-cobra-mapping.md, mas não foram confirmados 1:1 contra um exemplo real do actor para os 27 perfis. Não rodar decisões do TCC sobre esta tabela sem primeiro confirmar o piloto.</t>
+          <t>O piloto obrigatório da issue #93 (scripts/run_apify_mentions_pilot.py) grava só em data/pilot/*.json, FORA do Delta Lake -- não passa pela landing zone data/landing/ das demais entidades Bronze, nem por BronzeWriter. Os nomes de campo abaixo seguem a especificação da issue/ADR cruzada com docs/research/apify-instagram-actors-cobra-mapping.md, mas não foram confirmados 1:1 contra um exemplo real do actor para os 27 perfis. Não rodar decisões do TCC sobre esta tabela sem primeiro confirmar o piloto.</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10925,39 +10934,39 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Apify (apify/instagram-profile-scraper)</t>
+          <t>Apify (apify/instagram-scraper, ID shu8hvrXbJbY3Eb9W, modo resultsType='details' -- ver aba Actors Apify)</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_profiles</t>
+          <t>Landing zone: data/landing/&lt;run_id&gt;/profiles.json (local) ou /tmp/landing/&lt;run_id&gt;/profiles.json (Lambda, efêmero)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Ingestão bruta + metadados de execução (_ingested_at/_run_id/_source); serialização de campos list/dict para JSON string.</t>
+          <t>Arquivamento do JSON bruto retornado pela Apify, SEM projeção de schema -- fidelidade total, inclusive de campos que a Bronze descarta silenciosamente. Sempre executado antes da escrita Bronze, para que uma falha nesta não implique perda do dado já raspado (e já pago).</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/bronze_writer.py</t>
+          <t>src/data_extract/ingestion.py (archive_raw_json / extract_and_land)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Apify (apify/instagram-scraper)</t>
+          <t>Landing zone: profiles.json</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_posts</t>
+          <t>Bronze: instagram_profiles</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Idem instagram_profiles.</t>
+          <t>Ingestão bruta + metadados de execução (_ingested_at/_run_id/_source); serialização de campos list/dict para JSON string. Destino físico: data/bronze/instagram_profiles (local) ou s3://&lt;bucket&gt;/bronze/instagram_profiles (Lambda, quando infra AWS aplicada).</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -10969,384 +10978,685 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Apify (apify/instagram-reel-scraper)</t>
+          <t>Apify (apify/instagram-post-scraper -- ver aba Actors Apify)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_reels</t>
+          <t>Landing zone: data/landing/&lt;run_id&gt;/posts.json (local) ou /tmp/landing/&lt;run_id&gt;/posts.json (Lambda, efêmero)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Idem instagram_profiles; inclui latestComments e, opcionalmente, transcript (flag paga includeTranscript).</t>
+          <t>Idem profiles.json.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/bronze_writer.py</t>
+          <t>src/data_extract/ingestion.py (archive_raw_json / extract_and_land)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_profiles</t>
+          <t>Landing zone: posts.json</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Silver: profiles_clean</t>
+          <t>Bronze: instagram_posts</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Descarta linha sem id; drop de colunas de baixo valor (biografia, URLs de foto); cast para int32/bool não-nulo; deduplicação por id; fallback de fullName.</t>
+          <t>Idem instagram_profiles. Destino físico: data/bronze/instagram_posts (local) ou s3://&lt;bucket&gt;/bronze/instagram_posts (Lambda).</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/profile_cleaner.py</t>
+          <t>src/data_extract/bronze_writer.py</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_posts</t>
+          <t>Apify (apify/instagram-reel-scraper -- ver aba Actors Apify)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Silver: posts_clean</t>
+          <t>Landing zone: data/landing/&lt;run_id&gt;/reels.json (local) ou /tmp/landing/&lt;run_id&gt;/reels.json (Lambda, efêmero)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Descarta linha sem id; parse de timestamp -&gt; data_hora (America/Sao_Paulo); preserva type_raw; fixa Tipo='FEED'; cast numérico; drop de colunas ruído (mentions/images/musicInfo/...); deduplicação por id.</t>
+          <t>Idem profiles.json; payload já inclui latestComments e, opcionalmente, transcript (flag paga includeTranscript).</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/post_cleaner.py</t>
+          <t>src/data_extract/ingestion.py (archive_raw_json / extract_and_land)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>Landing zone: reels.json</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>Bronze: instagram_reels</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Silver: reels_clean</t>
-        </is>
-      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Mesma limpeza de posts_clean, mais: fixa Tipo='REELS'; calcula 'Total de Engajamento' (likes+comentários); propaga transcript sem alteração.</t>
+          <t>Idem instagram_profiles; inclui latestComments e, opcionalmente, transcript (flag paga includeTranscript). Destino físico: data/bronze/instagram_reels (local) ou s3://&lt;bucket&gt;/bronze/instagram_reels (Lambda).</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/post_cleaner.py</t>
+          <t>src/data_extract/bronze_writer.py</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_reels (campo latestComments)</t>
+          <t>Bronze: instagram_profiles</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Silver: comments_clean</t>
+          <t>Silver: profiles_clean</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Explode a lista JSON de comentários em uma linha por comentário; filtra texto &gt;= 512 caracteres; deduplicação por id_comment.</t>
+          <t>Descarta linha sem id; drop de colunas de baixo valor (biografia, URLs de foto); cast para int32/bool não-nulo; deduplicação por id; fallback de fullName.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/comment_cleaner.py</t>
+          <t>src/features/silver/profile_cleaner.py</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>reference/governadores.xlsx</t>
+          <t>Bronze: instagram_posts</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Silver: governors_metadata</t>
+          <t>Silver: posts_clean</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Renomeia colunas (Governador-&gt;nome, Unidade Federativa-&gt;uf, Partido-&gt;partido, Link-&gt;inputUrl); dedup por inputUrl.</t>
+          <t>Descarta linha sem id; parse de timestamp -&gt; data_hora (America/Sao_Paulo); preserva type_raw; fixa Tipo='FEED'; cast numérico; drop de colunas ruído (mentions/images/musicInfo/...); deduplicação por id.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/governors_metadata_cleaner.py</t>
+          <t>src/features/silver/post_cleaner.py</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Silver: profiles_clean + posts_clean + reels_clean</t>
+          <t>Bronze: instagram_reels</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_engagement / governor_engagement_history</t>
+          <t>Silver: reels_clean</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Agrega posts+reels por perfil; calcula TOTAL ENGAJAMENTO, % ENGAJAMENTO (ponderado por _WC_COMENTARIO), RECENCIA e FREQUENCIA.</t>
+          <t>Mesma limpeza de posts_clean, mais: fixa Tipo='REELS'; calcula 'Total de Engajamento' (likes+comentários); propaga transcript sem alteração.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/engagement_aggregator.py</t>
+          <t>src/features/silver/post_cleaner.py</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Silver: comments_clean + reels_clean/posts_clean (legenda/transcrição)</t>
+          <t>Bronze: instagram_reels (campo latestComments)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment / governor_sentiment_history</t>
+          <t>Silver: comments_clean</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Classificação de sentimento (cardiffnlp/twitter-xlm-roberta-base-sentiment) + tópico BERTopic determinístico, por comentário/legenda/transcrição.</t>
+          <t>Explode a lista JSON de comentários em uma linha por comentário; filtra texto &gt;= 512 caracteres; deduplicação por id_comment.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/sentiment.py + src/modeling/topics.py, gravado por src/features/gold/model_enricher.py</t>
+          <t>src/features/silver/comment_cleaner.py</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment</t>
+          <t>reference/governadores.xlsx</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>governor_sentiment (rótulos atualizados)</t>
+          <t>Silver: governors_metadata</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Refinamento manual dos rótulos de tópico (Name) via Gemini -- reescreve a mesma tabela, não gera nova medição de sentimento.</t>
+          <t>Renomeia colunas (Governador-&gt;nome, Unidade Federativa-&gt;uf, Partido-&gt;partido, Link-&gt;inputUrl); dedup por inputUrl.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>scripts/refine_topics.py + src/modeling/gemini_refiner.py</t>
+          <t>src/features/silver/governors_metadata_cleaner.py</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Silver: reels_clean + posts_clean</t>
+          <t>Silver: profiles_clean + posts_clean + reels_clean</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_clusters</t>
+          <t>Gold: governor_engagement / governor_engagement_history</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>PCA (engajamento/duração) + AutoClusterHPO (KMeans/DBSCAN/Agglomerative eleito por score CVI) por post; content_type discrimina reel/feed.</t>
+          <t>Agrega posts+reels por perfil; calcula TOTAL ENGAJAMENTO, % ENGAJAMENTO (ponderado por _WC_COMENTARIO), RECENCIA e FREQUENCIA.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/clustering.py, gravado por src/features/gold/model_enricher.py</t>
+          <t>src/features/gold/engagement_aggregator.py</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_engagement</t>
+          <t>Silver: comments_clean + reels_clean/posts_clean (legenda/transcrição)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_profile_clusters_engagement</t>
+          <t>Gold: governor_sentiment / governor_sentiment_history</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Mesma pipeline PCA-&gt;AutoClusterHPO, mas com features agregadas por PERFIL em vez de por post.</t>
+          <t>Classificação de sentimento (cardiffnlp/twitter-xlm-roberta-base-sentiment) + tópico BERTopic determinístico, por comentário/legenda/transcrição.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/profile_clustering.py, via src/modeling/orchestration.py::run_deterministic_modeling (ou isoladamente via scripts/run_profile_clustering_engagement.py)</t>
+          <t>src/modeling/sentiment.py + src/modeling/topics.py, gravado por src/features/gold/model_enricher.py</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Silver: posts_clean (caption/hashtags/Topic) + reels_clean + Gold: governor_engagement</t>
+          <t>Gold: governor_sentiment</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Gold: post_performance_coefficients / post_performance_predictions</t>
+          <t>governor_sentiment (rótulos atualizados)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Regressão Lasso de Y = (likes+comentários×Wc)/seguidores sobre preditores temporais/de formato/conteúdo, separada em grupo vídeo/estático; checagem de circularidade antes de treinar.</t>
+          <t>Refinamento manual dos rótulos de tópico (Name) via Gemini -- reescreve a mesma tabela, não gera nova medição de sentimento.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/post_performance.py</t>
+          <t>scripts/refine_topics.py + src/modeling/gemini_refiner.py</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment (fonte='comentario')</t>
+          <t>Silver: reels_clean + posts_clean</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Gold: topic_priority_score</t>
+          <t>Gold: governor_clusters</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Score ICE = Impacto(alcance_normalizado×%positivo) × Confiança(sentiment_score médio) × Facilidade(fixa=1.0), agregado por Topic.</t>
+          <t>PCA (engajamento/duração) + AutoClusterHPO (KMeans/DBSCAN/Agglomerative eleito por score CVI) por post; content_type discrimina reel/feed.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/topic_priority_scorer.py</t>
+          <t>src/modeling/clustering.py, gravado por src/features/gold/model_enricher.py</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment (fonte='comentario') + governor_engagement</t>
+          <t>Gold: governor_engagement</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_nsm</t>
+          <t>Gold: governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>NSM = (%comentários positivos) × (TOTAL ENGAJAMENTO / count, como proxy de alcance), merge outer por inputUrl.</t>
+          <t>Mesma pipeline PCA-&gt;AutoClusterHPO, mas com features agregadas por PERFIL em vez de por post.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/nsm_scorer.py</t>
+          <t>src/modeling/profile_clustering.py, via src/modeling/orchestration.py::run_deterministic_modeling (ou isoladamente via scripts/run_profile_clustering_engagement.py)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_engagement_history + governor_sentiment_history</t>
+          <t>Silver: posts_clean (caption/hashtags/Topic) + reels_clean + Gold: governor_engagement</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_growth_metrics</t>
+          <t>Gold: post_performance_coefficients / post_performance_predictions</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>CMGR sobre followersCount mensal + retenção sobre share mensal de sentimento positivo; marca ilustrativo/confiavel conforme volume de histórico.</t>
+          <t>Regressão Lasso de Y = (likes+comentários×Wc)/seguidores sobre preditores temporais/de formato/conteúdo, separada em grupo vídeo/estático; checagem de circularidade antes de treinar.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/growth_history.py + scripts/run_growth_metrics.py</t>
+          <t>src/modeling/post_performance.py</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Apify (apify/instagram-tagged-scraper) -- PILOTO</t>
+          <t>Gold: governor_sentiment (fonte='comentario')</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Bronze/Silver/Gold: ugc_mentions</t>
+          <t>Gold: topic_priority_score</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Contrato de schema definido e testado com dado sintético; piloto real (scripts/run_apify_mentions_pilot.py) grava só em data/pilot/*.json, fora do Delta Lake -- pipeline de produção NÃO grava esta cadeia ainda.</t>
+          <t>Score ICE = Impacto(alcance_normalizado×%positivo) × Confiança(sentiment_score médio) × Facilidade(fixa=1.0), agregado por Topic.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/ugc_mention_cleaner.py + src/features/gold/ugc_mentions_aggregator.py</t>
+          <t>src/features/gold/topic_priority_scorer.py</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>Gold: governor_sentiment (fonte='comentario') + governor_engagement</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Gold: governor_nsm</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>NSM = (%comentários positivos) × (TOTAL ENGAJAMENTO / count, como proxy de alcance), merge outer por inputUrl.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>src/features/gold/nsm_scorer.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Gold: governor_engagement_history + governor_sentiment_history</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Gold: governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>CMGR sobre followersCount mensal + retenção sobre share mensal de sentimento positivo; marca ilustrativo/confiavel conforme volume de histórico.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>src/modeling/growth_history.py + scripts/run_growth_metrics.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Apify (apify/instagram-tagged-scraper) -- PILOTO</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Bronze/Silver/Gold: ugc_mentions</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Contrato de schema definido e testado com dado sintético; piloto real (scripts/run_apify_mentions_pilot.py) grava só em data/pilot/*.json, fora do Delta Lake -- pipeline de produção NÃO grava esta cadeia ainda.</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>src/features/silver/ugc_mention_cleaner.py + src/features/gold/ugc_mentions_aggregator.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
           <t>Gold (todas as tabelas acima)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Dashboard Streamlit (dashboard/app.py + dashboard/screens/*.py, ADR 0021; pages/02-03 remanescentes, órfãs) e notebooks/03-07</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Leitura read-only via src/repositories/delta_repository.py (DeltaRepository) -- nunca escreve, save() levanta NotImplementedError deliberadamente.</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>src/repositories/delta_repository.py + dashboard/core/* + src/dashboard/*</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D20"/>
+  <autoFilter ref="A1:D23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Papel no pipeline</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Actor (slug)</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Actor ID técnico</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Desenvolvedor</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Parâmetros usados em produção</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Confiabilidade da fonte</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Perfis (instagram_profiles)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>apify/instagram-scraper</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>shu8hvrXbJbY3Eb9W</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Apify (oficial)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Produção</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>directUrls=&lt;links&gt;, addParentData=False, resultsLimit=100, resultsType='details', searchType='user' (src/data_extract/scraper.py::InstagramScraper.scrape_profiles).</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>ID confirmado via api.apify.com/v2/acts/shu8hvrXbJbY3Eb9W -&gt; {"name":"instagram-scraper","username":"apify"} (docs/research/..., §0).</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>É o actor GENÉRICO "canivete suíço" da Apify, não o dedicado apify/instagram-profile-scraper -- rodado só em resultsType='details' hoje. O mesmo actor/ID também suporta resultsType='mentions'/'comments' e busca por hashtag, não explorado no pipeline atual (ver docs/research/..., §7.3, para a rota de UGC que reaproveitaria este mesmo actor sem integrar um novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Posts de feed (instagram_posts)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>apify/instagram-post-scraper</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>(resolvido pelo slug pela Apify -- não fixado como ID literal no código)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Apify (oficial)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Produção</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>username=&lt;usernames&gt;, resultsLimit=30 (ScraperConfig.results_limit) + extra_run_input opcional (ex.: onlyPostsNewerThan, usado por scripts/run_apify_backfill.py para recorte incremental).</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Confirmado via página do actor + input-schema (docs/research/..., §1.1) -- pay-per-event, ~$1.00/1.000 posts.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Não tem includeTranscript nem includeSharesCount (esses são do reel-scraper) -- não confundir com o actor genérico usado para perfis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Reels (instagram_reels)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>apify/instagram-reel-scraper</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>(resolvido pelo slug pela Apify -- não fixado como ID literal no código)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Apify (oficial)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Produção</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>username=&lt;usernames&gt;, resultsLimit=30 + includeTranscript=True SOMENTE quando ScraperConfig.include_transcript=True (default False -- flag paga, cobrada por minuto de vídeo transcrito) + extra_run_input opcional.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Confirmado via página do actor + input-schema (docs/research/..., §1.2) -- pay-per-event, ~$1.00/1.000 reels.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Também suporta includeSharesCount (plano Starter+) e includeDownloadedVideo (cobrado por MB) -- nenhuma das duas está habilitada em ScraperConfig hoje (ver docs/research/..., §1.2, achado chave sobre sharesCount).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Menções/UGC de terceiros (ugc_mentions) -- PILOTO, não produção</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>apify/instagram-tagged-scraper</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>(resolvido pelo slug pela Apify -- não fixado como ID literal no código)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Apify (oficial)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>PILOTO -- schema definido e testado com dado sintético; piloto real grava só em data/pilot/*.json (scripts/run_apify_mentions_pilot.py), nunca na Bronze</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>username=&lt;usernames&gt;, resultsLimit=&lt;baixo no piloto&gt; (ScraperConfig.mentions_actor_id, InstagramScraper.scrape_mentions).</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Escolhido sobre fetch_cat/instagram-mentions-scraper por reprodutibilidade (9.999 usuários, 5.0 estrelas vs. actor community "under maintenance", 2 usuários -- docs/research/..., §7.1). Schema de output confirmado por exemplo real da Apify, mas ainda NÃO confirmado 1:1 contra os 27 perfis do projeto.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>docs/research/apify-instagram-actors-cobra-mapping.md (§7) também mapeia uma rota alternativa sem integrar actor novo: reconfigurar o actor de perfis já em uso (shu8hvrXbJbY3Eb9W) para resultsType='mentions' -- capacidade confirmada, schema de output dessa rota específica NÃO confirmado por exemplo primário.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Produção (verificação com dado real dos 27 perfis ainda pendente -- ver notas)</t>
+          <t>Produção -- verificado com dado real dos 27 perfis (ver notas)</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>'alcance_medio' é proxy (TOTAL ENGAJAMENTO / count de governor_engagement), não alcance/views real -- Instagram não expõe alcance real para posts estáticos. Critério de aceite da issue #90 (ranking NSM inverter o ranking por engajamento bruto em pelo menos 1 caso real) só foi validado com dado SINTÉTICO em teste; falta confirmar contra os 27 perfis reais antes de fechar o Cap. 6 do TCC neste ponto.</t>
+          <t>'alcance_medio' é proxy (TOTAL ENGAJAMENTO / count de governor_engagement), não alcance/views real -- Instagram não expõe alcance real para posts estáticos. Critério de aceite da issue #90 (ranking NSM inverter o ranking por engajamento bruto em pelo menos 1 caso real) confirmado em 2026-09-19 contra os 27 perfis reais: 25 dos 27 mudam de posição entre os dois rankings, inclusive o 1º lugar (tarcisiogdf ultrapassa romeuzemaoficial). Ver ADR 0020, Ficha 5, para o detalhe completo.</t>
         </is>
       </c>
     </row>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>alcance_medio é proxy de intensidade de engajamento por post, não alcance/views real. Validação com os 27 perfis reais ainda pendente (ver aba Tabelas).</t>
+          <t>alcance_medio é proxy de intensidade de engajamento por post, não alcance/views real. Validado contra os 27 perfis reais em 2026-09-19: 25/27 perfis mudam de posição vs. ranking por engajamento bruto (ver aba Tabelas / ADR 0020 Ficha 5).</t>
         </is>
       </c>
     </row>

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -990,7 +990,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Linha sem `id` é descartada (não quebra a escrita da tabela inteira); `fullName` ausente cai para `username`, depois `inputUrl`, nunca fica nulo por acidente.</t>
+          <t>Linha sem `id` é descartada (não quebra a escrita da tabela inteira) E gera um `logger.warning` com o(s) username(s) afetado(s) -- achado real: o link morto do Espírito Santo (PR #132) gerava esse descarte silenciosamente até ser descoberto manualmente; `fullName` ausente cai para `username`, depois `inputUrl`, nunca fica nulo por acidente.</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>`caption`/`hashtags` são preservados aqui (mas não em reels_clean) -- Reels não têm campo de legenda coletado, limitação estrutural de dado, não de design.</t>
+          <t>`caption`/`hashtags` são preservados aqui (mas não em reels_clean) -- Reels não têm campo de legenda coletado, limitação estrutural de dado, não de design. Linha sem `id` é descartada e gera `logger.warning` (mesmo tratamento de profiles_clean).</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>`Total de Engajamento` aqui é por-reel (insumo do PCA/AutoClusterHPO) -- não confundir com `TOTAL ENGAJAMENTO` (maiúsculo, com espaço) de governor_engagement, que é por-perfil agregado.</t>
+          <t>`Total de Engajamento` aqui é por-reel (insumo do PCA/AutoClusterHPO) -- não confundir com `TOTAL ENGAJAMENTO` (maiúsculo, com espaço) de governor_engagement, que é por-perfil agregado. Linha sem `id` é descartada e gera `logger.warning` (mesmo tratamento de profiles_clean).</t>
         </is>
       </c>
     </row>

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Não tem campo de comentário embutido (latestComments) -- por isso governor_sentiment/comments_clean só cobrem comentário de Reels, nunca de post de feed. Payload bruto arquivado em data/landing/&lt;run_id&gt;/posts.json (ou /tmp/landing/... na Lambda) ANTES desta escrita -- ver aba Linhagem.</t>
+          <t>Não tem campo de comentário embutido (latestComments) -- por isso governor_sentiment/comments_clean só cobrem comentário de Reels, nunca de post de feed. Payload bruto arquivado em data/landing/&lt;run_id&gt;/posts.json (ou /tmp/landing/... na Lambda) ANTES desta escrita -- ver aba Linhagem. Perfil sem NENHUM post próprio (0 itens, não confundir com perfil sem `id`) gera item de erro `{"error": "no_items", "errorDescription": "Empty or private data..."}` -- caso real (2026-09): claudiocastrorj (verificado, 2M+ seguidores) tinha só marcações de terceiros na grade, zero posts/reels próprios publicados.</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>`transcript` é nullable e só vem preenchido quando a execução ligou explicitamente a flag paga do actor (custo por minuto de vídeo) -- não confundir ausência com 'sem fala'. Payload bruto arquivado em data/landing/&lt;run_id&gt;/reels.json (ou /tmp/landing/... na Lambda) ANTES desta escrita -- ver aba Linhagem.</t>
+          <t>`transcript` é nullable e só vem preenchido quando a execução ligou explicitamente a flag paga do actor (custo por minuto de vídeo) -- não confundir ausência com 'sem fala'. Payload bruto arquivado em data/landing/&lt;run_id&gt;/reels.json (ou /tmp/landing/... na Lambda) ANTES desta escrita -- ver aba Linhagem. Mesma ressalva de instagram_posts sobre perfil com zero itens próprios (`error: 'no_items'`).</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por governador, deduplicada por `inputUrl`.</t>
+          <t>Uma linha por governador COM Instagram rastreável, deduplicada por `inputUrl` -- governador sem `Link` na planilha (célula em branco) não gera linha aqui.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Produção</t>
+          <t>Produção (26 de 27 governadores -- ver notas)</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>`reference/governadores.xlsx` é mantido manualmente, fora do pipeline (ADR 0013) -- esta é a ÚNICA leitura de Excel que resta no projeto, e é de configuração, não de dado coletado.</t>
+          <t>`reference/governadores.xlsx` é mantido manualmente, fora do pipeline (ADR 0013) -- esta é a ÚNICA leitura de Excel que resta no projeto, e é de configuração, não de dado coletado. Governador sem Instagram rastreável (`Link` em branco) é descartado ANTES do cast para string, para não virar o texto literal 'nan' em `inputUrl` (NOT NULL, chave de junção do pipeline inteiro) -- mesmo filtro em scripts/apify_backfill_shared.py::load_links(). Caso real (2026-09): Rio de Janeiro fica sem Instagram rastreável desde a renúncia de Cláudio Castro (2026-03-23) -- o titular interino (desembargador Ricardo Couto, presidente do TJ-RJ) não tem perfil público de gestão. governors_metadata/Bronze/Silver/Gold refletem 26 governadores enquanto essa situação persistir.</t>
         </is>
       </c>
     </row>

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Produção</t>
+          <t>Produção (LIMITAÇÃO CONHECIDA -- ver notas: governador removido de governadores.xlsx continua aparecendo aqui)</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Sempre sobrescrita por completo a cada execução -- para série temporal, ver governor_engagement_history.</t>
+          <t>Sempre sobrescrita por completo a cada execução -- para série temporal, ver governor_engagement_history. LIMITAÇÃO CONHECIDA (2026-09-19): EngagementAggregator recalcula a partir de profiles_clean/posts_clean/reels_clean (Silver, que por sua vez vem de TODA a Bronze acumulada) -- não filtra contra governors_metadata/governadores.xlsx. Um governador removido da planilha (ex.: Rio de Janeiro/claudiocastrorj, sem Instagram rastreável desde 2026-03 -- ver PR #136) continua reaparecendo aqui indefinidamente, com o último snapshot real da Bronze (cada vez mais desatualizado) só recebendo um `_generated_at` novo a cada execução -- parece fresco, mas o dado por trás não é. Não afeta o seletor de governador do dashboard (vem de governors_metadata, filtra corretamente), mas PODE vazar como 'par' em telas que comparam perfis por cluster (ex.: Tela 4, via governor_profile_clusters_engagement, mesma limitação -- ver notas daquela tabela). Correção exigiria EngagementAggregator/estágio de modelagem cruzarem contra governors_metadata antes de processar -- fora de escopo até aqui, fica para decisão futura.</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Produção</t>
+          <t>Produção (LIMITAÇÃO CONHECIDA -- herda de governor_engagement, ver notas)</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Roda pós-Gold-de-engajamento (lê governor_engagement), dentro do mesmo estágio determinístico das demais tabelas de modelagem -- na Lambda serverless, é a etapa `model`, disparada depois de `load` (ver seção 3 do README).</t>
+          <t>Roda pós-Gold-de-engajamento (lê governor_engagement), dentro do mesmo estágio determinístico das demais tabelas de modelagem -- na Lambda serverless, é a etapa `model`, disparada depois de `load` (ver seção 3 do README). LIMITAÇÃO CONHECIDA (2026-09-19): como lê governor_engagement (que não filtra contra governadores.xlsx atual -- ver notas daquela tabela), um governador removido da planilha continua recebendo `cluster_perfil_engajamento` aqui e PODE aparecer como 'par' na Tela 4 (Comparar perfis) para outro governador do mesmo cluster, com dado cada vez mais desatualizado. Caso real: claudiocastrorj (RJ, sem Instagram rastreável desde 2026-03 -- PR #136).</t>
         </is>
       </c>
     </row>

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -18,9 +18,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabelas'!$A$1:$K$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Colunas - Bronze'!$A$1:$E$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Colunas - Silver'!$A$1:$E$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Colunas - Bronze'!$A$1:$E$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Colunas - Silver'!$A$1:$E$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$162</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Linhagem'!$A$1:$D$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Actors Apify'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Glossário de Métricas'!$A$1:$E$11</definedName>
@@ -918,7 +918,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>PILOTO -- schema definido e testado com dado sintético, mas SEM dado real gravado em produção</t>
+          <t>PILOTO -- schema CORRIGIDO contra dado real (2026-09-19), mas SEM dado gravado em produção (Bronze) ainda</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>O piloto obrigatório da issue #93 (scripts/run_apify_mentions_pilot.py) grava só em data/pilot/*.json, FORA do Delta Lake -- não passa pela landing zone data/landing/ das demais entidades Bronze, nem por BronzeWriter. Os nomes de campo abaixo seguem a especificação da issue/ADR cruzada com docs/research/apify-instagram-actors-cobra-mapping.md, mas não foram confirmados 1:1 contra um exemplo real do actor para os 27 perfis. Não rodar decisões do TCC sobre esta tabela sem primeiro confirmar o piloto.</t>
+          <t>O piloto obrigatório da issue #93 (scripts/run_apify_mentions_pilot.py) rodou de verdade em 2026-09-19 contra os 26 perfis com Instagram rastreável (119 posts, data/pilot/mentions_pilot_20260919T030401Z.json) -- grava em data/pilot/*.json, FORA do Delta Lake, não passa pela landing zone nem por BronzeWriter. O schema abaixo foi CORRIGIDO a partir desse resultado real: `authorUsername`/`authorIsVerified`/`isPaidPartnership`/`isAd`/`isAffiliate`/`matchTypes` da especificação original (issue #93) NÃO existem no retorno do actor -- removidos/substituídos por `ownerUsername`/`ownerFullName`/`ownerId`/`paidPartnership`/`taggedUsers` (nomes reais). Ainda sem writer de produção (`BronzeWriter.write_ugc_mentions` não existe) -- essa etapa falta antes de fechar a Ficha 8.</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>UGC de terceiros já limpo: `governor_username` derivado de `mentions` cruzado com a lista de usernames conhecidos; `authorUsername` normaliza `authorUsername`/`ownerUsername` brutos num só campo.</t>
+          <t>UGC de terceiros já limpo: `governor_username` derivado de `mentions` E `taggedUsers` (Bronze) cruzados com a lista de usernames conhecidos; `authorUsername` normaliza o handle do autor terceiro (na prática, sempre a partir de `ownerUsername` -- ver Bronze).</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>`id`/`shortCode` são nullable aqui (ao contrário do padrão NOT NULL de profiles/posts/reels) porque o piloto ainda não confirmou presença garantida de `id` no actor escolhido -- o cleaner descarta linha sem os dois.</t>
+          <t>`id`/`shortCode` são nullable aqui (ao contrário do padrão NOT NULL de profiles/posts/reels) porque o piloto ainda não confirmou presença garantida de `id` no actor escolhido -- o cleaner descarta linha sem os dois. Piloto real (2026-09-19) confirmou que checar só `mentions` perderia ~69% dos posts correlacionáveis -- a maioria só tem a marcação visual em `taggedUsers`, não @-menção em texto.</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>UGC orgânico vs. publi paga por post, com `is_organic` derivado de isPaidPartnership/isAd/isAffiliate -- separa apoio espontâneo de publi paga ANTES de qualquer agregação.</t>
+          <t>UGC orgânico vs. publi paga por post, com `is_organic` derivado de `paidPartnership` -- separa apoio espontâneo de publi paga ANTES de qualquer agregação.</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>`GovernorUGCAggregator.aggregate_by_governor` (a 'view' de contagem/engajamento médio por governador) nunca expõe `authorUsername` individual no agregado, por desenho -- privacidade de quem menciona o governador, não só do próprio governador.</t>
+          <t>`GovernorUGCAggregator.aggregate_by_governor` (a 'view' de contagem/engajamento médio por governador) nunca expõe `authorUsername` individual no agregado, por desenho -- privacidade de quem menciona o governador, não só do próprio governador. Piloto real (2026-09-19) confirmou que `paidPartnership` é o único campo de publi que o actor expõe -- `isAd`/`isAffiliate` não existem como conceitos distintos, removidos do schema.</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
+          <t>Id do perfil de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
+          <t>Id do perfil de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Lista de usernames marcados/mencionados no post de UGC, serializada como JSON string.</t>
+          <t>Lista de usernames @-mencionados em legenda/comentário do post de UGC, serializada como JSON string -- só ~31% dos posts reais têm este campo preenchido.</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>matchTypes</t>
+          <t>taggedUsers</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Tipo de correlação do UGC ao perfil: marcação visual ('tagged') vs. menção textual ('mentioned').</t>
+          <t>Lista de objetos (um por pessoa marcada visualmente na foto/vídeo, com `username`/`full_name`/`is_verified`/`is_private`) do post de UGC, serializada como JSON string -- substitui o campo `matchTypes` (não existe no actor real); presente em ~69% dos posts, mais frequente que `mentions`.</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>authorUsername</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado).</t>
+          <t>Username de quem publicou o post de UGC (autor terceiro que marcou/mencionou o governador -- Bronze, nome real do actor apify/instagram-tagged-scraper). Normalizado para `authorUsername` na Silver.</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>ownerFullName</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil que publicou o post/reel/comentário.</t>
+          <t>Nome completo de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
         </is>
       </c>
     </row>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>authorIsVerified</t>
+          <t>ownerId</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Se o autor do post de UGC tem selo de verificação.</t>
+          <t>Id do perfil de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>isPaidPartnership</t>
+          <t>paidPartnership</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Flag de parceria paga (publi) declarada pelo Instagram no post.</t>
+          <t>Flag de parceria paga (publi) declarada pelo Instagram no post de UGC -- único campo de publi que o actor real expõe (piloto 2026-09-19); `isAd`/`isAffiliate` da especificação original não existem.</t>
         </is>
       </c>
     </row>
@@ -3913,22 +3913,22 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>isAd</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Flag de anúncio pago.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
@@ -3940,22 +3940,22 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>isAffiliate</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Flag de conteúdo de afiliado.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
@@ -3967,12 +3967,12 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>_source</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -3982,66 +3982,12 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>_run_id</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>_source</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
           <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E74"/>
+  <autoFilter ref="A1:E72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4052,7 +3998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4517,7 +4463,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
+          <t>Id do perfil de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4922,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
+          <t>Id do perfil de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6014,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>matchTypes</t>
+          <t>governor_username</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -6083,7 +6029,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Tipo de correlação do UGC ao perfil: marcação visual ('tagged') vs. menção textual ('mentioned').</t>
+          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6041,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>governor_username</t>
+          <t>authorUsername</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -6110,7 +6056,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Username do governador mencionado/marcado, resolvido a partir de `mentions` cruzado com a lista de perfis conhecidos.</t>
+          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
         </is>
       </c>
     </row>
@@ -6122,22 +6068,22 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>authorUsername</t>
+          <t>paidPartnership</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado).</t>
+          <t>Flag de parceria paga (publi) declarada pelo Instagram no post de UGC -- único campo de publi que o actor real expõe (piloto 2026-09-19); `isAd`/`isAffiliate` da especificação original não existem.</t>
         </is>
       </c>
     </row>
@@ -6149,12 +6095,12 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>authorIsVerified</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -6164,7 +6110,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Se o autor do post de UGC tem selo de verificação.</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -6176,12 +6122,12 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>isPaidPartnership</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -6191,7 +6137,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Flag de parceria paga (publi) declarada pelo Instagram no post.</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
@@ -6203,22 +6149,22 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>isAd</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Flag de anúncio pago.</t>
+          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
         </is>
       </c>
     </row>
@@ -6230,12 +6176,12 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>isAffiliate</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>timestamp[us]</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -6245,7 +6191,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Flag de conteúdo de afiliado.</t>
+          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
         </is>
       </c>
     </row>
@@ -6257,12 +6203,12 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -6272,7 +6218,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6230,12 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -6299,7 +6245,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
@@ -6311,135 +6257,27 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>_source_layer</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>data_hora</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>timestamp[us]</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>_ingested_at</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>timestamp[us, tz=UTC]</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>_run_id</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>_source_layer</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
           <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E88"/>
+  <autoFilter ref="A1:E84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6450,7 +6288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E164"/>
+  <dimension ref="A1:E162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -10155,7 +9993,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Username do governador mencionado/marcado, resolvido a partir de `mentions` cruzado com a lista de perfis conhecidos.</t>
+          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
         </is>
       </c>
     </row>
@@ -10182,7 +10020,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado).</t>
+          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
         </is>
       </c>
     </row>
@@ -10194,22 +10032,22 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>authorIsVerified</t>
+          <t>caption</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Se o autor do post de UGC tem selo de verificação.</t>
+          <t>Legenda do post de UGC (do autor terceiro, não do governador).</t>
         </is>
       </c>
     </row>
@@ -10221,22 +10059,22 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>caption</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>Legenda do post de UGC (do autor terceiro, não do governador).</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -10248,22 +10086,22 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>matchTypes</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Tipo de correlação do UGC ao perfil: marcação visual ('tagged') vs. menção textual ('mentioned').</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
@@ -10275,7 +10113,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -10285,12 +10123,12 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
         </is>
       </c>
     </row>
@@ -10302,12 +10140,12 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>is_organic</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -10317,7 +10155,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>Derivado de `paidPartnership`: True quando ausente/False -- separa apoio espontâneo de publi paga.</t>
         </is>
       </c>
     </row>
@@ -10329,22 +10167,22 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>timestamp[us]</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
+          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10194,12 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>is_organic</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -10371,7 +10209,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Derivado de isPaidPartnership/isAd/isAffiliate: True quando NENHuma das três é True -- separa apoio espontâneo de publi paga.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
@@ -10383,12 +10221,12 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us]</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -10398,19 +10236,19 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -10420,39 +10258,39 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>valor_inicial</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Valor da métrica-base (followersCount) no primeiro mês-calendário com execução registrada.</t>
         </is>
       </c>
     </row>
@@ -10464,12 +10302,12 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>valor_final</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -10479,7 +10317,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Valor da métrica-base (followersCount) no último mês-calendário com execução registrada.</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10329,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>valor_inicial</t>
+          <t>cmgr</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -10506,7 +10344,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Valor da métrica-base (followersCount) no primeiro mês-calendário com execução registrada.</t>
+          <t>(valor_final / valor_inicial) ** (1 / n_meses) - 1 -- crescimento mensal composto. NaN quando não calculável (ver cmgr_motivo).</t>
         </is>
       </c>
     </row>
@@ -10518,22 +10356,22 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>valor_final</t>
+          <t>cmgr_n_periodos</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Valor da métrica-base (followersCount) no último mês-calendário com execução registrada.</t>
+          <t>Número de meses-calendário com execução registrada usados no cálculo do CMGR.</t>
         </is>
       </c>
     </row>
@@ -10545,22 +10383,22 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>cmgr</t>
+          <t>cmgr_confiavel</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>(valor_final / valor_inicial) ** (1 / n_meses) - 1 -- crescimento mensal composto. NaN quando não calculável (ver cmgr_motivo).</t>
+          <t>False sempre que cmgr_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL) -- sinaliza resultado ilustrativo, não conclusivo.</t>
         </is>
       </c>
     </row>
@@ -10572,22 +10410,22 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>cmgr_n_periodos</t>
+          <t>cmgr_motivo</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Número de meses-calendário com execução registrada usados no cálculo do CMGR.</t>
+          <t>Motivo do CMGR ser NaN, quando aplicável: historico_insuficiente / periodo_zero / valor_inicial_invalido.</t>
         </is>
       </c>
     </row>
@@ -10599,22 +10437,22 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>cmgr_confiavel</t>
+          <t>retencao</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>False sempre que cmgr_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL) -- sinaliza resultado ilustrativo, não conclusivo.</t>
+          <t>Média de valor_t/valor_(t-1) (capada em 1.0) do share mensal de sentimento positivo entre meses consecutivos -- 1.0 = manteve 100% (ou mais); mede o quanto do período anterior foi retido, não crescimento.</t>
         </is>
       </c>
     </row>
@@ -10626,22 +10464,22 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>cmgr_motivo</t>
+          <t>retencao_n_periodos</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Motivo do CMGR ser NaN, quando aplicável: historico_insuficiente / periodo_zero / valor_inicial_invalido.</t>
+          <t>Número de meses-calendário com execução registrada usados no cálculo da retenção.</t>
         </is>
       </c>
     </row>
@@ -10653,22 +10491,22 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>retencao</t>
+          <t>retencao_n_pares_validos</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Média de valor_t/valor_(t-1) (capada em 1.0) do share mensal de sentimento positivo entre meses consecutivos -- 1.0 = manteve 100% (ou mais); mede o quanto do período anterior foi retido, não crescimento.</t>
+          <t>Número de pares de meses consecutivos válidos usados na média da retenção.</t>
         </is>
       </c>
     </row>
@@ -10680,12 +10518,12 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>retencao_n_periodos</t>
+          <t>retencao_confiavel</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -10695,7 +10533,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Número de meses-calendário com execução registrada usados no cálculo da retenção.</t>
+          <t>False sempre que retencao_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL).</t>
         </is>
       </c>
     </row>
@@ -10707,22 +10545,22 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>retencao_n_pares_validos</t>
+          <t>retencao_motivo</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Número de pares de meses consecutivos válidos usados na média da retenção.</t>
+          <t>Motivo da retenção ser NaN, quando aplicável (mesmas categorias do cmgr_motivo).</t>
         </is>
       </c>
     </row>
@@ -10734,7 +10572,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>retencao_confiavel</t>
+          <t>ilustrativo</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -10749,7 +10587,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>False sempre que retencao_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL).</t>
+          <t>True enquanto o pipeline não tiver acumulado histórico real suficiente -- sinaliza que o valor valida a FÓRMULA, não sustenta conclusão definitiva no TCC.</t>
         </is>
       </c>
     </row>
@@ -10761,7 +10599,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>retencao_motivo</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -10771,12 +10609,12 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Motivo da retenção ser NaN, quando aplicável (mesmas categorias do cmgr_motivo).</t>
+          <t>Texto explicando por que o resultado é (ou não) ilustrativo, para exibição direta em dashboard/relatório sem reprocessar nada.</t>
         </is>
       </c>
     </row>
@@ -10788,12 +10626,12 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>ilustrativo</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -10803,7 +10641,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>True enquanto o pipeline não tiver acumulado histórico real suficiente -- sinaliza que o valor valida a FÓRMULA, não sustenta conclusão definitiva no TCC.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10653,12 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -10830,66 +10668,12 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Texto explicando por que o resultado é (ou não) ilustrativo, para exibição direta em dashboard/relatório sem reprocessar nada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>governor_growth_metrics</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>_run_id</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>governor_growth_metrics</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>_generated_at</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>timestamp[us, tz=UTC]</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
           <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E164"/>
+  <autoFilter ref="A1:E162"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sem caminho fixo em config/settings.py ainda -- não existe BronzeWriter.write_ugc_mentions</t>
+          <t>config/settings.py::BRONZE_UGC_MENTIONS (data/bronze/ugc_mentions)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -903,22 +903,22 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>append (planejado)</t>
+          <t>append</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Nenhum -- schema definido em src/schemas_delta.py para a issue #93, mas nenhum writer de produção grava esta tabela ainda</t>
+          <t>src/data_extract/bronze_writer.py (BronzeWriter.write_ugc_mentions), chamado por scripts/run_ugc_mentions.py</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/ugc_mention_cleaner.py (testado com dado sintético)</t>
+          <t>src/features/silver/ugc_mention_cleaner.py</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>PILOTO -- schema CORRIGIDO contra dado real (2026-09-19), mas SEM dado gravado em produção (Bronze) ainda</t>
+          <t>Produção (ressalva) -- writer implementado e testado (2026-09-19), mas SEM execução real disparada ainda (custo Apify -- ver scripts/run_ugc_mentions.py)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>O piloto obrigatório da issue #93 (scripts/run_apify_mentions_pilot.py) rodou de verdade em 2026-09-19 contra os 26 perfis com Instagram rastreável (119 posts, data/pilot/mentions_pilot_20260919T030401Z.json) -- grava em data/pilot/*.json, FORA do Delta Lake, não passa pela landing zone nem por BronzeWriter. O schema abaixo foi CORRIGIDO a partir desse resultado real: `authorUsername`/`authorIsVerified`/`isPaidPartnership`/`isAd`/`isAffiliate`/`matchTypes` da especificação original (issue #93) NÃO existem no retorno do actor -- removidos/substituídos por `ownerUsername`/`ownerFullName`/`ownerId`/`paidPartnership`/`taggedUsers` (nomes reais). Ainda sem writer de produção (`BronzeWriter.write_ugc_mentions` não existe) -- essa etapa falta antes de fechar a Ficha 8.</t>
+          <t>O piloto obrigatório da issue #93 (scripts/run_apify_mentions_pilot.py) rodou de verdade em 2026-09-19 contra os 26 perfis com Instagram rastreável (119 posts, data/pilot/mentions_pilot_20260919T030401Z.json) -- grava em data/pilot/*.json, FORA do Delta Lake, não passa pela landing zone nem por BronzeWriter. O schema abaixo foi CORRIGIDO a partir desse resultado real: `authorUsername`/`authorIsVerified`/`isPaidPartnership`/`isAd`/`isAffiliate`/`matchTypes` da especificação original (issue #93) NÃO existem no retorno do actor -- removidos/substituídos por `ownerUsername`/`ownerFullName`/`ownerId`/`paidPartnership`/`taggedUsers` (nomes reais). `scripts/run_ugc_mentions.py` (novo, 2026-09-19) fecha o loop Bronze-&gt;Silver-&gt;Gold sob o mesmo run_id, mesmo padrão de scripts/run_apify_backfill.py -- testado ponta a ponta (Delta real via tmp_path), mas nunca disparado contra a Apify de produção (custo real, decisão do usuário).</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Sem caminho fixo em config/settings.py ainda</t>
+          <t>config/settings.py::SILVER_UGC_MENTIONS (data/silver/ugc_mentions)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1245,22 +1245,22 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>overwrite (planejado)</t>
+          <t>overwrite</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/ugc_mention_cleaner.py (UgcMentionCleaner) -- testado com dado sintético, sem chamador de produção ainda</t>
+          <t>src/features/silver/ugc_mention_cleaner.py (UGCMentionCleaner), chamado por scripts/run_ugc_mentions.py</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/ugc_mentions_aggregator.py (testado com dado sintético)</t>
+          <t>src/features/gold/ugc_mentions_aggregator.py, chamado por scripts/run_ugc_mentions.py</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>PILOTO -- mesma ressalva da Bronze ugc_mentions</t>
+          <t>Produção (ressalva) -- mesma ressalva da Bronze ugc_mentions</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sem caminho fixo em config/settings.py ainda -- GovernorUGCAggregator.write() exige path explícito do chamador, que ainda não existe em produção</t>
+          <t>config/settings.py::GOLD_UGC_MENTIONS (data/gold/governor_ugc_mentions)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1929,12 +1929,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>overwrite (planejado)</t>
+          <t>overwrite</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Nenhum caminho de produção -- src/features/gold/ugc_mentions_aggregator.py (GovernorUGCAggregator) só é exercitado pelos testes (dado sintético)</t>
+          <t>src/features/gold/ugc_mentions_aggregator.py (GovernorUGCAggregator), chamado por scripts/run_ugc_mentions.py</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>PILOTO -- mesma ressalva de Bronze/Silver ugc_mentions</t>
+          <t>Produção (ressalva) -- mesma ressalva de Bronze/Silver ugc_mentions</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
+          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
+          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
+          <t>Id do perfil de quem publicou o post de UGC (autor terceiro, Bronze, confirmado pelo piloto real) -- distinto do `ownerId` de posts/reels, que é o próprio governador.</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
+          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
+          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
         </is>
       </c>
     </row>
@@ -11158,22 +11158,22 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Apify (apify/instagram-tagged-scraper) -- PILOTO</t>
+          <t>Apify (apify/instagram-tagged-scraper -- ver aba Actors Apify)</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Bronze/Silver/Gold: ugc_mentions</t>
+          <t>Bronze/Silver/Gold: ugc_mentions / governor_ugc_mentions</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Contrato de schema definido e testado com dado sintético; piloto real (scripts/run_apify_mentions_pilot.py) grava só em data/pilot/*.json, fora do Delta Lake -- pipeline de produção NÃO grava esta cadeia ainda.</t>
+          <t>Coleta -&gt; landing zone -&gt; Bronze -&gt; Silver (dedup id/shortCode, normalização de handle, resolução de governor_username via mentions+taggedUsers) -&gt; Gold (is_organic a partir de paidPartnership), tudo sob o mesmo run_id -- mesmo padrão de scripts/run_apify_backfill.py. Schema corrigido contra o piloto real (scripts/run_apify_mentions_pilot.py, 2026-09-19, data/pilot/*.json, fora do Delta Lake). Writer de produção implementado e testado, mas ainda NUNCA disparado contra a Apify de produção (custo real).</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/ugc_mention_cleaner.py + src/features/gold/ugc_mentions_aggregator.py</t>
+          <t>scripts/run_ugc_mentions.py + src/data_extract/bronze_writer.py + src/features/silver/ugc_mention_cleaner.py + src/features/gold/ugc_mentions_aggregator.py</t>
         </is>
       </c>
     </row>

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -990,7 +990,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Linha sem `id` é descartada (não quebra a escrita da tabela inteira) E gera um `logger.warning` com o(s) username(s) afetado(s) -- achado real: o link morto do Espírito Santo (PR #132) gerava esse descarte silenciosamente até ser descoberto manualmente; `fullName` ausente cai para `username`, depois `inputUrl`, nunca fica nulo por acidente.</t>
+          <t>Linha sem `id` é descartada (não quebra a escrita da tabela inteira) E gera um `logger.warning` com o(s) username(s) afetado(s) -- achado real: o link morto do Espírito Santo (PR #132) gerava esse descarte silenciosamente até ser descoberto manualmente; `fullName` ausente cai para `username`, depois `inputUrl`, nunca fica nulo por acidente. `clean()` também filtra por `governor_usernames` (opcional, passado por pipeline.py via scripts.apify_backfill_shared.load_governor_usernames()) -- governador removido de governadores.xlsx some daqui e, em cascata, de toda a Gold derivada (achado original: PR #137).</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>`caption`/`hashtags` são preservados aqui (mas não em reels_clean) -- Reels não têm campo de legenda coletado, limitação estrutural de dado, não de design. Linha sem `id` é descartada e gera `logger.warning` (mesmo tratamento de profiles_clean).</t>
+          <t>`caption`/`hashtags` são preservados aqui (mas não em reels_clean) -- Reels não têm campo de legenda coletado, limitação estrutural de dado, não de design. Linha sem `id` é descartada e gera `logger.warning` (mesmo tratamento de profiles_clean). `clean_posts()` também filtra por `governor_usernames` via `ownerUsername` -- mesmo tratamento de profiles_clean (achado original: PR #137).</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>`Total de Engajamento` aqui é por-reel (insumo do PCA/AutoClusterHPO) -- não confundir com `TOTAL ENGAJAMENTO` (maiúsculo, com espaço) de governor_engagement, que é por-perfil agregado. Linha sem `id` é descartada e gera `logger.warning` (mesmo tratamento de profiles_clean).</t>
+          <t>`Total de Engajamento` aqui é por-reel (insumo do PCA/AutoClusterHPO) -- não confundir com `TOTAL ENGAJAMENTO` (maiúsculo, com espaço) de governor_engagement, que é por-perfil agregado. Linha sem `id` é descartada e gera `logger.warning` (mesmo tratamento de profiles_clean). `clean_reels()` também filtra por `governor_usernames` via `ownerUsername` -- mesmo tratamento de profiles_clean (achado original: PR #137).</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Deriva EXCLUSIVAMENTE de Reels -- posts de feed não carregam comentário embutido no dado coletado, então não existe 'comentário de post' em nenhuma tabela do projeto.</t>
+          <t>Deriva EXCLUSIVAMENTE de Reels -- posts de feed não carregam comentário embutido no dado coletado, então não existe 'comentário de post' em nenhuma tabela do projeto. `clean()` também filtra por `governor_usernames`, pelo `ownerUsername` do REEL (o governador) ANTES do explode -- depois dele, `ownerUsername` passa a se referir ao autor do comentário, não ao governador (achado original: PR #137).</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Produção (LIMITAÇÃO CONHECIDA -- ver notas: governador removido de governadores.xlsx continua aparecendo aqui)</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Sempre sobrescrita por completo a cada execução -- para série temporal, ver governor_engagement_history. LIMITAÇÃO CONHECIDA (2026-09-19): EngagementAggregator recalcula a partir de profiles_clean/posts_clean/reels_clean (Silver, que por sua vez vem de TODA a Bronze acumulada) -- não filtra contra governors_metadata/governadores.xlsx. Um governador removido da planilha (ex.: Rio de Janeiro/claudiocastrorj, sem Instagram rastreável desde 2026-03 -- ver PR #136) continua reaparecendo aqui indefinidamente, com o último snapshot real da Bronze (cada vez mais desatualizado) só recebendo um `_generated_at` novo a cada execução -- parece fresco, mas o dado por trás não é. Não afeta o seletor de governador do dashboard (vem de governors_metadata, filtra corretamente), mas PODE vazar como 'par' em telas que comparam perfis por cluster (ex.: Tela 4, via governor_profile_clusters_engagement, mesma limitação -- ver notas daquela tabela). Correção exigiria EngagementAggregator/estágio de modelagem cruzarem contra governors_metadata antes de processar -- fora de escopo até aqui, fica para decisão futura.</t>
+          <t>Sempre sobrescrita por completo a cada execução -- para série temporal, ver governor_engagement_history. LIMITAÇÃO CORRIGIDA (2026-09-19): profiles_clean/posts_clean/reels_clean/comments_clean agora filtram contra governor_usernames (scripts.apify_backfill_shared.load_governor_usernames(), a partir de governadores.xlsx atual) ANTES de qualquer Gold -- um governador removido da planilha (ex.: Rio de Janeiro/claudiocastrorj até 2026-09, ver PR #136) some de profiles_clean e, em cascata, desta tabela e de todas as demais Gold derivadas, em vez de continuar reaparecendo indefinidamente com dado cada vez mais desatualizado (achado original: PR #137).</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Produção (LIMITAÇÃO CONHECIDA -- herda de governor_engagement, ver notas)</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Roda pós-Gold-de-engajamento (lê governor_engagement), dentro do mesmo estágio determinístico das demais tabelas de modelagem -- na Lambda serverless, é a etapa `model`, disparada depois de `load` (ver seção 3 do README). LIMITAÇÃO CONHECIDA (2026-09-19): como lê governor_engagement (que não filtra contra governadores.xlsx atual -- ver notas daquela tabela), um governador removido da planilha continua recebendo `cluster_perfil_engajamento` aqui e PODE aparecer como 'par' na Tela 4 (Comparar perfis) para outro governador do mesmo cluster, com dado cada vez mais desatualizado. Caso real: claudiocastrorj (RJ, sem Instagram rastreável desde 2026-03 -- PR #136).</t>
+          <t>Roda pós-Gold-de-engajamento (lê governor_engagement), dentro do mesmo estágio determinístico das demais tabelas de modelagem -- na Lambda serverless, é a etapa `model`, disparada depois de `load` (ver seção 3 do README). LIMITAÇÃO CORRIGIDA (2026-09-19): herdava o vazamento de governor_engagement (ver notas daquela tabela) -- agora que profiles_clean/posts_clean/reels_clean filtram contra governadores.xlsx atual, um governador removido nunca chega a ter governor_engagement calculado, então também não aparece mais aqui nem como 'par' na Tela 4 (Comparar perfis).</t>
         </is>
       </c>
     </row>

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -17,10 +17,10 @@
     <sheet name="Glossário de Métricas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabelas'!$A$1:$K$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabelas'!$A$1:$K$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Colunas - Bronze'!$A$1:$E$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Colunas - Silver'!$A$1:$E$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$170</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Linhagem'!$A$1:$D$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Actors Apify'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Glossário de Métricas'!$A$1:$E$11</definedName>
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters</t>
+          <t>governor_clusters_reels</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_clusters</t>
+          <t>data/gold/governor_clusters_reels</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por Reel OU post de feed (discriminado por `content_type`) -- clusterização de CONTEÚDO, não de perfil.</t>
+          <t>Uma linha por Reel -- clusterização de CONTEÚDO, não de perfil.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1607,17 +1607,17 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 2 / issue #87 (content_type)</t>
+          <t>ADR 0020 Ficha 2 / issue #87 (content_type); issue #152 (tabela separada de governor_clusters_posts)</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Cluster de engajamento/duração por post (PCA -&gt; KMeans/DBSCAN/Agglomerative via AutoClusterHPO, algoritmo eleito por score CVI combinado).</t>
+          <t>Cluster de engajamento/duração por reel (PCA -&gt; KMeans/DBSCAN/Agglomerative via AutoClusterHPO, algoritmo eleito por score CVI combinado).</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>`cluster_label = -1` é ruído do DBSCAN, não um cluster de negócio (ver seção 2.2 do README) -- nunca a mesma coisa que clusterização de PERFIL (governor_profile_clusters_engagement, tabela separada).</t>
+          <t>`cluster_label = -1` é ruído do DBSCAN, não um cluster de negócio (ver seção 2.2 do README) -- nunca a mesma coisa que clusterização de PERFIL (governor_profile_clusters_engagement, tabela separada). Antes da issue #152, coexistia com os posts de feed numa única tabela `governor_clusters` discriminada por `content_type` -- separada porque `posts_clean`/`reels_clean` (Silver) se sobrepõem (mesmo Reel capturado por dois actors Apify distintos), o que duplicava posts sob os dois `content_type`.</t>
         </is>
       </c>
     </row>
@@ -1629,17 +1629,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>governor_profile_clusters_engagement</t>
+          <t>governor_clusters_posts</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_profile_clusters_engagement</t>
+          <t>data/gold/governor_clusters_posts</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por GOVERNADOR (não por post) -- clusterização de PERFIL por padrão de engajamento.</t>
+          <t>Uma linha por post de feed -- clusterização de CONTEÚDO, não de perfil.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (ModelEnricher.write_profile_clusters_engagement), via src/modeling/orchestration.py::run_deterministic_modeling (pipeline.py --run-modeling / scripts/run_modeling.py) ou, isoladamente, via scripts/run_profile_clustering_engagement.py</t>
+          <t>src/features/gold/model_enricher.py (ModelEnricher.write_clusters), a partir de src/modeling/clustering.py (AutoClusterHPO)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/comparar.py (Tela 4 "Comparar perfis", ADR 0021 -- comparação de perfil vs. pares do mesmo cluster)</t>
+          <t>Nenhum consumidor de produção hoje (Tela de "Padrões de conteúdo" do feed ainda não existe no dashboard atual, ADR 0021).</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1664,17 +1664,17 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Fase 2 / issue #86; ADR 0004/0005 (schema próprio, não genérico)</t>
+          <t>ADR 0020 Ficha 2 / issue #87 (content_type); issue #152 (tabela separada de governor_clusters_reels)</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Agrupa governadores por semelhança de padrão de engajamento (mesma pipeline PCA-&gt;AutoClusterHPO do nível de conteúdo, mas features agregadas por perfil).</t>
+          <t>Cluster de engajamento por post de feed (PCA -&gt; KMeans/DBSCAN/Agglomerative via AutoClusterHPO, algoritmo eleito por score CVI combinado).</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Roda pós-Gold-de-engajamento (lê governor_engagement), dentro do mesmo estágio determinístico das demais tabelas de modelagem -- na Lambda serverless, é a etapa `model`, disparada depois de `load` (ver seção 3 do README). LIMITAÇÃO CORRIGIDA (2026-09-19): herdava o vazamento de governor_engagement (ver notas daquela tabela) -- agora que profiles_clean/posts_clean/reels_clean filtram contra governadores.xlsx atual, um governador removido nunca chega a ter governor_engagement calculado, então também não aparece mais aqui nem como 'par' na Tela 4 (Comparar perfis).</t>
+          <t>Mesmo schema de `governor_clusters_reels` (`content_type` constante = 'feed' dentro desta tabela) -- separada por causa da mesma sobreposição Silver descrita lá.</t>
         </is>
       </c>
     </row>
@@ -1686,17 +1686,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>post_performance_coefficients</t>
+          <t>governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>data/gold/post_performance_coefficients</t>
+          <t>data/gold/governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por preditor por grupo (vídeo/estático) por execução -- formato longo.</t>
+          <t>Uma linha por GOVERNADOR (não por post) -- clusterização de PERFIL por padrão de engajamento.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (write_post_performance_coefficients), a partir de src/modeling/post_performance.py (LassoCV)</t>
+          <t>src/features/gold/model_enricher.py (ModelEnricher.write_profile_clusters_engagement), via src/modeling/orchestration.py::run_deterministic_modeling (pipeline.py --run-modeling / scripts/run_modeling.py) ou, isoladamente, via scripts/run_profile_clustering_engagement.py</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>pages/03_performance.py (comparação entre governadores, coeficientes da regressão) -- órfã desde a ADR 0021, sem entrypoint ativo (ver seção 4 do README)</t>
+          <t>dashboard/screens/comparar.py (Tela 4 "Comparar perfis", ADR 0021 -- comparação de perfil vs. pares do mesmo cluster)</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>ADR 0019 parte C</t>
+          <t>ADR 0020 Fase 2 / issue #86; ADR 0004/0005 (schema próprio, não genérico)</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Coeficientes e R² (treino/holdout) da regressão Lasso que explica performance-por-post, separada em grupo vídeo (Reels) e estático (posts de imagem/carrossel) por terem preditores distintos (ex.: duração de vídeo só existe no grupo vídeo).</t>
+          <t>Agrupa governadores por semelhança de padrão de engajamento (mesma pipeline PCA-&gt;AutoClusterHPO do nível de conteúdo, mas features agregadas por perfil).</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>`preditor` inclui, entre outros: hora_do_dia, dia_da_semana, tem_duracao, videoDuration (grupo vídeo), comprimento_legenda e Tema/Topic do BERTopic sobre legenda (grupo estático), paidPartnership (grupo vídeo). `r2_holdout` é nulo só no caso degenerado de um grupo sem governador em holdout.</t>
+          <t>Roda pós-Gold-de-engajamento (lê governor_engagement), dentro do mesmo estágio determinístico das demais tabelas de modelagem -- na Lambda serverless, é a etapa `model`, disparada depois de `load` (ver seção 3 do README). LIMITAÇÃO CORRIGIDA (2026-09-19): herdava o vazamento de governor_engagement (ver notas daquela tabela) -- agora que profiles_clean/posts_clean/reels_clean filtram contra governadores.xlsx atual, um governador removido nunca chega a ter governor_engagement calculado, então também não aparece mais aqui nem como 'par' na Tela 4 (Comparar perfis).</t>
         </is>
       </c>
     </row>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>post_performance_predictions</t>
+          <t>post_performance_coefficients</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>data/gold/post_performance_predictions</t>
+          <t>data/gold/post_performance_coefficients</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por post individual (treino + holdout juntos, discriminados implicitamente pelo pipeline que os gerou).</t>
+          <t>Uma linha por preditor por grupo (vídeo/estático) por execução -- formato longo.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (write_post_performance_predictions)</t>
+          <t>src/features/gold/model_enricher.py (write_post_performance_coefficients), a partir de src/modeling/post_performance.py (LassoCV)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>pages/03_performance.py (dispersão previsto vs. real, resíduos) -- órfã desde a ADR 0021, sem entrypoint ativo (ver seção 4 do README)</t>
+          <t>pages/03_performance.py (comparação entre governadores, coeficientes da regressão) -- órfã desde a ADR 0021, sem entrypoint ativo (ver seção 4 do README)</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1778,17 +1778,17 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>ADR 0019 parte C, decisão 9</t>
+          <t>ADR 0019 parte C</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Y real, Y previsto e resíduo por post -- Y = (likesCount + commentsCount × _WC_COMENTARIO) / followersCount, a mesma lógica de taxa ponderada de governor_engagement.% ENGAJAMENTO, mas por post em vez de agregada por perfil.</t>
+          <t>Coeficientes e R² (treino/holdout) da regressão Lasso que explica performance-por-post, separada em grupo vídeo (Reels) e estático (posts de imagem/carrossel) por terem preditores distintos (ex.: duração de vídeo só existe no grupo vídeo).</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Habilita a 'lacuna de execução' do dashboard (issue E da ADR 0019) sem precisar de uma tabela extra só para holdout.</t>
+          <t>`preditor` inclui, entre outros: hora_do_dia, dia_da_semana, tem_duracao, videoDuration (grupo vídeo), comprimento_legenda e Tema/Topic do BERTopic sobre legenda (grupo estático), paidPartnership (grupo vídeo). `r2_holdout` é nulo só no caso degenerado de um grupo sem governador em holdout.</t>
         </is>
       </c>
     </row>
@@ -1800,17 +1800,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>topic_priority_score</t>
+          <t>post_performance_predictions</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>data/gold/topic_priority_score</t>
+          <t>data/gold/post_performance_predictions</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por tópico de COMENTÁRIO (ranking global, não por governador).</t>
+          <t>Uma linha por post individual (treino + holdout juntos, discriminados implicitamente pelo pipeline que os gerou).</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/topic_priority_scorer.py (TopicPriorityScorer)</t>
+          <t>src/features/gold/model_enricher.py (write_post_performance_predictions)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/{resumo,produzir,radar}.py (priorização do que produzir a seguir, ADR 0021)</t>
+          <t>pages/03_performance.py (dispersão previsto vs. real, resíduos) -- órfã desde a ADR 0021, sem entrypoint ativo (ver seção 4 do README)</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 6 / issue #91</t>
+          <t>ADR 0019 parte C, decisão 9</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Score ICE (Impacto x Confiança x Facilidade) de priorização de tópicos de comentário -- responde 'sobre o que o governador deveria produzir a seguir'.</t>
+          <t>Y real, Y previsto e resíduo por post -- Y = (likesCount + commentsCount × _WC_COMENTARIO) / followersCount, a mesma lógica de taxa ponderada de governor_engagement.% ENGAJAMENTO, mas por post em vez de agregada por perfil.</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>'Facilidade' é fixa em 1.0 nesta v1 (FACILIDADE_V1) -- não há dado de custo de produção real para calibrar, decisão deliberada em vez de inventar uma heurística sem lastro. 'alcance_topico' é proxy (likes+replies do comentário), não alcance/views real.</t>
+          <t>Habilita a 'lacuna de execução' do dashboard (issue E da ADR 0019) sem precisar de uma tabela extra só para holdout.</t>
         </is>
       </c>
     </row>
@@ -1857,17 +1857,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm</t>
+          <t>topic_priority_score</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_nsm</t>
+          <t>data/gold/topic_priority_score</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por perfil de governador.</t>
+          <t>Uma linha por tópico de COMENTÁRIO (ranking global, não por governador).</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1877,32 +1877,32 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/nsm_scorer.py (NsmScorer)</t>
+          <t>src/features/gold/topic_priority_scorer.py (TopicPriorityScorer)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/resumo.py (Tela 1, ADR 0021)</t>
+          <t>dashboard/screens/{resumo,produzir,radar}.py (priorização do que produzir a seguir, ADR 0021)</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Produção -- verificado com dado real dos 27 perfis (ver notas)</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 5 / issue #90</t>
+          <t>ADR 0020 Ficha 6 / issue #91</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>North Star Metric: (comentários positivos / comentários totais) × alcance médio -- engajamento qualificado por QUALIDADE de reação, não só volume.</t>
+          <t>Score ICE (Impacto x Confiança x Facilidade) de priorização de tópicos de comentário -- responde 'sobre o que o governador deveria produzir a seguir'.</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>'alcance_medio' é proxy (TOTAL ENGAJAMENTO / count de governor_engagement), não alcance/views real -- Instagram não expõe alcance real para posts estáticos. Critério de aceite da issue #90 (ranking NSM inverter o ranking por engajamento bruto em pelo menos 1 caso real) confirmado em 2026-09-19 contra os 27 perfis reais: 25 dos 27 mudam de posição entre os dois rankings, inclusive o 1º lugar (tarcisiogdf ultrapassa romeuzemaoficial). Ver ADR 0020, Ficha 5, para o detalhe completo.</t>
+          <t>'Facilidade' é fixa em 1.0 nesta v1 (FACILIDADE_V1) -- não há dado de custo de produção real para calibrar, decisão deliberada em vez de inventar uma heurística sem lastro. 'alcance_topico' é proxy (likes+replies do comentário), não alcance/views real.</t>
         </is>
       </c>
     </row>
@@ -1914,17 +1914,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_nsm</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>config/settings.py::GOLD_UGC_MENTIONS (data/gold/governor_ugc_mentions)</t>
+          <t>data/gold/governor_nsm</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por post de UGC (grão fino -- agregação por governador é uma view em memória, não persistida).</t>
+          <t>Uma linha por perfil de governador.</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1934,32 +1934,32 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/ugc_mentions_aggregator.py (GovernorUGCAggregator), chamado por scripts/run_ugc_mentions.py</t>
+          <t>src/features/gold/nsm_scorer.py (NsmScorer)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Nenhum consumidor de produção hoje -- dashboard/screens/funil.py (Tela 6, ADR 0021) proíbe estruturalmente qualquer referência a esta tabela (ver teste test_funil_module_never_references_ugc_tables); src/dashboard/filters.py tem a função de agregação, mas não é chamada por nenhuma tela atual</t>
+          <t>dashboard/screens/resumo.py (Tela 1, ADR 0021)</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Produção (ressalva) -- mesma ressalva de Bronze/Silver ugc_mentions</t>
+          <t>Produção -- verificado com dado real dos 27 perfis (ver notas)</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 8 / issue #93</t>
+          <t>ADR 0020 Ficha 5 / issue #90</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>UGC orgânico vs. publi paga por post, com `is_organic` derivado de `paidPartnership` -- separa apoio espontâneo de publi paga ANTES de qualquer agregação.</t>
+          <t>North Star Metric: (comentários positivos / comentários totais) × alcance médio -- engajamento qualificado por QUALIDADE de reação, não só volume.</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>`GovernorUGCAggregator.aggregate_by_governor` (a 'view' de contagem/engajamento médio por governador) nunca expõe `authorUsername` individual no agregado, por desenho -- privacidade de quem menciona o governador, não só do próprio governador. Piloto real (2026-09-19) confirmou que `paidPartnership` é o único campo de publi que o actor expõe -- `isAd`/`isAffiliate` não existem como conceitos distintos, removidos do schema.</t>
+          <t>'alcance_medio' é proxy (TOTAL ENGAJAMENTO / count de governor_engagement), não alcance/views real -- Instagram não expõe alcance real para posts estáticos. Critério de aceite da issue #90 (ranking NSM inverter o ranking por engajamento bruto em pelo menos 1 caso real) confirmado em 2026-09-19 contra os 27 perfis reais: 25 dos 27 mudam de posição entre os dois rankings, inclusive o 1º lugar (tarcisiogdf ultrapassa romeuzemaoficial). Ver ADR 0020, Ficha 5, para o detalhe completo.</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,114 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
+          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>config/settings.py::GOLD_UGC_MENTIONS (data/gold/governor_ugc_mentions)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Uma linha por post de UGC (grão fino -- agregação por governador é uma view em memória, não persistida).</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>overwrite</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>src/features/gold/ugc_mentions_aggregator.py (GovernorUGCAggregator), chamado por scripts/run_ugc_mentions.py</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Nenhum consumidor de produção hoje -- dashboard/screens/funil.py (Tela 6, ADR 0021) proíbe estruturalmente qualquer referência a esta tabela (ver teste test_funil_module_never_references_ugc_tables); src/dashboard/filters.py tem a função de agregação, mas não é chamada por nenhuma tela atual</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Produção (ressalva) -- mesma ressalva de Bronze/Silver ugc_mentions</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>ADR 0020 Ficha 8 / issue #93</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>UGC orgânico vs. publi paga por post, com `is_organic` derivado de `paidPartnership` -- separa apoio espontâneo de publi paga ANTES de qualquer agregação.</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>`GovernorUGCAggregator.aggregate_by_governor` (a 'view' de contagem/engajamento médio por governador) nunca expõe `authorUsername` individual no agregado, por desenho -- privacidade de quem menciona o governador, não só do próprio governador. Piloto real (2026-09-19) confirmou que `paidPartnership` é o único campo de publi que o actor expõe -- `isAd`/`isAffiliate` não existem como conceitos distintos, removidos do schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>governor_growth_metrics</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>data/gold/governor_growth_metrics</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Uma linha por perfil de governador -- snapshot recalculável a partir do histórico acumulado (sempre overwrite, nunca append).</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>overwrite</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>src/features/gold/model_enricher.py (write_growth_metrics), via scripts/run_growth_metrics.py e src/modeling/growth_history.py</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Nenhuma tela do dashboard atual (ADR 0021) consome esta tabela -- dashboard/core/data.py::load_growth_metrics() existe, mas não é chamada por nenhuma das 6 telas</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>PRODUÇÃO, mas resultado marcado ILUSTRATIVO (ver notas) -- não sustenta conclusão definitiva ainda</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>ADR 0020 Ficha 7 / issue #92</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>CMGR (crescimento mensal composto de seguidores) e retenção de sentimento positivo, calculados sobre governor_engagement_history/governor_sentiment_history.</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>`cmgr_confiavel`/`retencao_confiavel` são False sempre que houver menos de MIN_PERIODS_CONFIAVEL=6 execuções mensais acumuladas -- em 2026-09 o pipeline ainda não acumulou histórico suficiente, então os valores validam a FÓRMULA, não sustentam conclusão real sobre crescimento dos perfis. `motivo`/`nota` explicam o porquê sempre que o valor for NaN ou não confiável.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K24"/>
+  <autoFilter ref="A1:K25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6288,7 +6345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -8434,7 +8491,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters</t>
+          <t>governor_clusters_reels</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -8461,7 +8518,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters</t>
+          <t>governor_clusters_reels</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -8488,7 +8545,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters</t>
+          <t>governor_clusters_reels</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -8515,7 +8572,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters</t>
+          <t>governor_clusters_reels</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -8542,7 +8599,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters</t>
+          <t>governor_clusters_reels</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -8569,7 +8626,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters</t>
+          <t>governor_clusters_reels</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -8589,14 +8646,14 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Discrimina se a linha é de 'reel' ou 'feed' dentro de governor_clusters (ADR 0020 Ficha 2 / issue #87).</t>
+          <t>Valor constante por tabela ('reel' em governor_clusters_reels, 'feed' em governor_clusters_posts) -- mantido no schema das duas para permitir recombinação futura via pd.concat sem precisar re-derivar o rótulo (ADR 0020 Ficha 2 / issue #87; tabelas separadas desde a issue #152).</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters</t>
+          <t>governor_clusters_reels</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -8623,7 +8680,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters</t>
+          <t>governor_clusters_reels</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -8650,12 +8707,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>governor_profile_clusters_engagement</t>
+          <t>governor_clusters_posts</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>id_reel</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -8670,24 +8727,24 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Id do reel/post de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>governor_profile_clusters_engagement</t>
+          <t>governor_clusters_posts</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>cluster_label</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -8697,24 +8754,24 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Rótulo do cluster atribuído pelo AutoClusterHPO (-1 = ruído do DBSCAN).</t>
+          <t>Username do perfil que publicou o post/reel/comentário.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>governor_profile_clusters_engagement</t>
+          <t>governor_clusters_posts</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>cluster_algo</t>
+          <t>cluster_label</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -8724,78 +8781,78 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Nome do algoritmo eleito pelo AutoClusterHPO para esta execução (KMeans/DBSCAN/Agglomerative).</t>
+          <t>Rótulo do cluster atribuído pelo AutoClusterHPO (-1 = ruído do DBSCAN).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>governor_profile_clusters_engagement</t>
+          <t>governor_clusters_posts</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>cluster_score</t>
+          <t>cluster_algo</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Score CVI combinado (Silhouette + Calinski-Harabasz normalizado + Davies-Bouldin invertido) do algoritmo eleito -- ver src/modeling/clustering.py.</t>
+          <t>Nome do algoritmo eleito pelo AutoClusterHPO para esta execução (KMeans/DBSCAN/Agglomerative).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>governor_profile_clusters_engagement</t>
+          <t>governor_clusters_posts</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>cluster_score</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Score CVI combinado (Silhouette + Calinski-Harabasz normalizado + Davies-Bouldin invertido) do algoritmo eleito -- ver src/modeling/clustering.py.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>governor_profile_clusters_engagement</t>
+          <t>governor_clusters_posts</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>content_type</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -8805,19 +8862,19 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Valor constante por tabela ('reel' em governor_clusters_reels, 'feed' em governor_clusters_posts) -- mantido no schema das duas para permitir recombinação futura via pd.concat sem precisar re-derivar o rótulo (ADR 0020 Ficha 2 / issue #87; tabelas separadas desde a issue #152).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>post_performance_coefficients</t>
+          <t>governor_clusters_posts</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>grupo</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -8832,24 +8889,24 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Discrimina o grupo da regressão de performance-por-post: 'video' (Reels) ou 'estatico' (posts de imagem/carrossel).</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>post_performance_coefficients</t>
+          <t>governor_clusters_posts</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>preditor</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -8859,24 +8916,24 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Nome do preditor da regressão (varia por grupo -- ver coluna Notas da aba Tabelas).</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>post_performance_coefficients</t>
+          <t>governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>coeficiente</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -8886,24 +8943,24 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Coeficiente estimado pelo LassoCV para este preditor (0.0 = preditor descartado pela regularização L1).</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>post_performance_coefficients</t>
+          <t>governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>r2_treino</t>
+          <t>cluster_label</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -8913,78 +8970,78 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>R² do modelo no conjunto de treino.</t>
+          <t>Rótulo do cluster atribuído pelo AutoClusterHPO (-1 = ruído do DBSCAN).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>post_performance_coefficients</t>
+          <t>governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>r2_holdout</t>
+          <t>cluster_algo</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>R² do modelo no conjunto de holdout -- nulo só no caso degenerado de um grupo sem governador em holdout.</t>
+          <t>Nome do algoritmo eleito pelo AutoClusterHPO para esta execução (KMeans/DBSCAN/Agglomerative).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>post_performance_coefficients</t>
+          <t>governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>n_treino</t>
+          <t>cluster_score</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Número de posts no conjunto de treino deste grupo.</t>
+          <t>Score CVI combinado (Silhouette + Calinski-Harabasz normalizado + Davies-Bouldin invertido) do algoritmo eleito -- ver src/modeling/clustering.py.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>post_performance_coefficients</t>
+          <t>governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>n_holdout</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -8994,24 +9051,24 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Número de posts no conjunto de holdout deste grupo.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>post_performance_coefficients</t>
+          <t>governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -9021,7 +9078,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Hiperparâmetro de regularização (força da penalização L1) escolhido pelo LassoCV via validação cruzada.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -9033,7 +9090,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>grupo</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -9048,7 +9105,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Discrimina o grupo da regressão de performance-por-post: 'video' (Reels) ou 'estatico' (posts de imagem/carrossel).</t>
         </is>
       </c>
     </row>
@@ -9060,12 +9117,12 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>preditor</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -9075,24 +9132,24 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Nome do preditor da regressão (varia por grupo -- ver coluna Notas da aba Tabelas).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>post_performance_predictions</t>
+          <t>post_performance_coefficients</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>coeficiente</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -9102,78 +9159,78 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Coeficiente estimado pelo LassoCV para este preditor (0.0 = preditor descartado pela regularização L1).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>post_performance_predictions</t>
+          <t>post_performance_coefficients</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>r2_treino</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>R² do modelo no conjunto de treino.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>post_performance_predictions</t>
+          <t>post_performance_coefficients</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>grupo</t>
+          <t>r2_holdout</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>Discrimina o grupo da regressão de performance-por-post: 'video' (Reels) ou 'estatico' (posts de imagem/carrossel).</t>
+          <t>R² do modelo no conjunto de holdout -- nulo só no caso degenerado de um grupo sem governador em holdout.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>post_performance_predictions</t>
+          <t>post_performance_coefficients</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>y_real</t>
+          <t>n_treino</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -9183,24 +9240,24 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Valor real de Y = (likesCount + commentsCount × _WC_COMENTARIO) / followersCount para este post.</t>
+          <t>Número de posts no conjunto de treino deste grupo.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>post_performance_predictions</t>
+          <t>post_performance_coefficients</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>y_previsto</t>
+          <t>n_holdout</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -9210,19 +9267,19 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>Valor de Y previsto pela regressão Lasso treinada para o grupo (vídeo/estático) deste post.</t>
+          <t>Número de posts no conjunto de holdout deste grupo.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>post_performance_predictions</t>
+          <t>post_performance_coefficients</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>residuo</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -9237,14 +9294,14 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>y_real - y_previsto -- posts com resíduo muito positivo performaram acima do esperado pelo modelo, e vice-versa.</t>
+          <t>Hiperparâmetro de regularização (força da penalização L1) escolhido pelo LassoCV via validação cruzada.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>post_performance_predictions</t>
+          <t>post_performance_coefficients</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -9271,7 +9328,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>post_performance_predictions</t>
+          <t>post_performance_coefficients</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -9298,17 +9355,17 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>topic_priority_score</t>
+          <t>post_performance_predictions</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -9318,19 +9375,19 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Id numérico do tópico BERTopic (-1 = ruído/sem tópico atribuído).</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>topic_priority_score</t>
+          <t>post_performance_predictions</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -9345,24 +9402,24 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Rótulo textual do tópico BERTopic -- determinístico (KeyBERTInspired) por padrão, ou refinado manualmente via Gemini (scripts/refine_topics.py).</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>topic_priority_score</t>
+          <t>post_performance_predictions</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios</t>
+          <t>grupo</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -9372,24 +9429,24 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários atribuídos a este tópico pelo BERTopic.</t>
+          <t>Discrimina o grupo da regressão de performance-por-post: 'video' (Reels) ou 'estatico' (posts de imagem/carrossel).</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>topic_priority_score</t>
+          <t>post_performance_predictions</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>alcance_topico</t>
+          <t>y_real</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -9399,19 +9456,19 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Soma de (likesCount + repliesCount) dos comentários do tópico -- PROXY de visibilidade/ressonância, não alcance/views real.</t>
+          <t>Valor real de Y = (likesCount + commentsCount × _WC_COMENTARIO) / followersCount para este post.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>topic_priority_score</t>
+          <t>post_performance_predictions</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>alcance_normalizado</t>
+          <t>y_previsto</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -9426,19 +9483,19 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>alcance_topico / (alcance_topico + 1) -- normalização que satura suavemente em [0,1), nunca divide por zero, e não depende de quais outros tópicos existem na mesma execução.</t>
+          <t>Valor de Y previsto pela regressão Lasso treinada para o grupo (vídeo/estático) deste post.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>topic_priority_score</t>
+          <t>post_performance_predictions</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>proporcao_sentimento_positivo</t>
+          <t>residuo</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -9453,24 +9510,24 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Fração de comentários do tópico com sentiment_label == 'positive'.</t>
+          <t>y_real - y_previsto -- posts com resíduo muito positivo performaram acima do esperado pelo modelo, e vice-versa.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>topic_priority_score</t>
+          <t>post_performance_predictions</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -9480,24 +9537,24 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Média de sentiment_score (confiança do classificador, não polaridade) dos comentários do tópico.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>topic_priority_score</t>
+          <t>post_performance_predictions</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>impacto</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -9507,7 +9564,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>alcance_normalizado × proporcao_sentimento_positivo.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -9519,12 +9576,12 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -9534,7 +9591,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Fixa em 1.0 nesta v1 (FACILIDADE_V1) -- sem dado de custo de produção real para calibrar; o ranking de Score reduz-se, na prática, a Impacto × Confiança.</t>
+          <t>Id numérico do tópico BERTopic (-1 = ruído/sem tópico atribuído).</t>
         </is>
       </c>
     </row>
@@ -9546,22 +9603,22 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Impacto × Confiança × Facilidade -- ranking final de priorização de produção de conteúdo.</t>
+          <t>Rótulo textual do tópico BERTopic -- determinístico (KeyBERTInspired) por padrão, ou refinado manualmente via Gemini (scripts/refine_topics.py).</t>
         </is>
       </c>
     </row>
@@ -9573,12 +9630,12 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>n_comentarios</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -9588,7 +9645,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Número de comentários atribuídos a este tópico pelo BERTopic.</t>
         </is>
       </c>
     </row>
@@ -9600,12 +9657,12 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>alcance_topico</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -9615,78 +9672,78 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Soma de (likesCount + repliesCount) dos comentários do tópico -- PROXY de visibilidade/ressonância, não alcance/views real.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm</t>
+          <t>topic_priority_score</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>alcance_normalizado</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>alcance_topico / (alcance_topico + 1) -- normalização que satura suavemente em [0,1), nunca divide por zero, e não depende de quais outros tópicos existem na mesma execução.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm</t>
+          <t>topic_priority_score</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>proporcao_sentimento_positivo</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Nome de usuário do perfil de Instagram.</t>
+          <t>Fração de comentários do tópico com sentiment_label == 'positive'.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm</t>
+          <t>topic_priority_score</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_positivos</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -9696,24 +9753,24 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários (fonte == 'comentario') com sentiment_label == 'positive' deste perfil.</t>
+          <t>Média de sentiment_score (confiança do classificador, não polaridade) dos comentários do tópico.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm</t>
+          <t>topic_priority_score</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_totais</t>
+          <t>impacto</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -9723,19 +9780,19 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Número total de comentários (fonte == 'comentario') deste perfil.</t>
+          <t>alcance_normalizado × proporcao_sentimento_positivo.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm</t>
+          <t>topic_priority_score</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>proporcao_positivos</t>
+          <t>facilidade</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -9750,24 +9807,24 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_positivos / n_comentarios_totais -- 0.0 quando o perfil não tem nenhum comentário (nunca NaN/erro).</t>
+          <t>Fixa em 1.0 nesta v1 (FACILIDADE_V1) -- sem dado de custo de produção real para calibrar; o ranking de Score reduz-se, na prática, a Impacto × Confiança.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm</t>
+          <t>topic_priority_score</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>total_engajamento</t>
+          <t>score</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -9777,24 +9834,24 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Cópia de governor_engagement['TOTAL ENGAJAMENTO'] para este perfil, mantida para auditoria/contraste no dashboard.</t>
+          <t>Impacto × Confiança × Facilidade -- ranking final de priorização de produção de conteúdo.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm</t>
+          <t>topic_priority_score</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>count_posts</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -9804,24 +9861,24 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Cópia de governor_engagement['count'] para este perfil.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm</t>
+          <t>topic_priority_score</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>alcance_medio</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -9831,7 +9888,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>total_engajamento / count_posts -- PROXY de alcance (intensidade de engajamento por post), não alcance/views real. 0.0 quando count_posts == 0.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -9843,22 +9900,22 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>nsm</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>proporcao_positivos × alcance_medio -- North Star Metric de engajamento QUALIFICADO (pondera qualidade de reação, não só volume).</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -9870,7 +9927,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>username</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -9880,12 +9937,12 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Nome de usuário do perfil de Instagram.</t>
         </is>
       </c>
     </row>
@@ -9897,12 +9954,12 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>n_comentarios_positivos</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
@@ -9912,159 +9969,159 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Número de comentários (fonte == 'comentario') com sentiment_label == 'positive' deste perfil.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_nsm</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>n_comentarios_totais</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Número total de comentários (fonte == 'comentario') deste perfil.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_nsm</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>proporcao_positivos</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>n_comentarios_positivos / n_comentarios_totais -- 0.0 quando o perfil não tem nenhum comentário (nunca NaN/erro).</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_nsm</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>governor_username</t>
+          <t>total_engajamento</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
+          <t>Cópia de governor_engagement['TOTAL ENGAJAMENTO'] para este perfil, mantida para auditoria/contraste no dashboard.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_nsm</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>authorUsername</t>
+          <t>count_posts</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
+          <t>Cópia de governor_engagement['count'] para este perfil.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_nsm</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>caption</t>
+          <t>alcance_medio</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Legenda do post de UGC (do autor terceiro, não do governador).</t>
+          <t>total_engajamento / count_posts -- PROXY de alcance (intensidade de engajamento por post), não alcance/views real. 0.0 quando count_posts == 0.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_nsm</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>nsm</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -10074,24 +10131,24 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>proporcao_positivos × alcance_medio -- North Star Metric de engajamento QUALIFICADO (pondera qualidade de reação, não só volume).</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_nsm</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -10101,34 +10158,34 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_nsm</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -10140,22 +10197,22 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>is_organic</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Derivado de `paidPartnership`: True quando ausente/False -- separa apoio espontâneo de publi paga.</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
@@ -10167,22 +10224,22 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>shortCode</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10251,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>governor_username</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -10204,12 +10261,12 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
         </is>
       </c>
     </row>
@@ -10221,34 +10278,34 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>authorUsername</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>caption</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -10263,78 +10320,78 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Legenda do post de UGC (do autor terceiro, não do governador).</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>valor_inicial</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Valor da métrica-base (followersCount) no primeiro mês-calendário com execução registrada.</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>valor_final</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Valor da métrica-base (followersCount) no último mês-calendário com execução registrada.</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>cmgr</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -10344,24 +10401,24 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>(valor_final / valor_inicial) ** (1 / n_meses) - 1 -- crescimento mensal composto. NaN quando não calculável (ver cmgr_motivo).</t>
+          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>cmgr_n_periodos</t>
+          <t>is_organic</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -10371,24 +10428,24 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Número de meses-calendário com execução registrada usados no cálculo do CMGR.</t>
+          <t>Derivado de `paidPartnership`: True quando ausente/False -- separa apoio espontâneo de publi paga.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>cmgr_confiavel</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>timestamp[us]</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -10398,19 +10455,19 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>False sempre que cmgr_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL) -- sinaliza resultado ilustrativo, não conclusivo.</t>
+          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>cmgr_motivo</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -10420,39 +10477,39 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Motivo do CMGR ser NaN, quando aplicável: historico_insuficiente / periodo_zero / valor_inicial_invalido.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>retencao</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Média de valor_t/valor_(t-1) (capada em 1.0) do share mensal de sentimento positivo entre meses consecutivos -- 1.0 = manteve 100% (ou mais); mede o quanto do período anterior foi retido, não crescimento.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -10464,22 +10521,22 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>retencao_n_periodos</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Número de meses-calendário com execução registrada usados no cálculo da retenção.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -10491,22 +10548,22 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>retencao_n_pares_validos</t>
+          <t>valor_inicial</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Número de pares de meses consecutivos válidos usados na média da retenção.</t>
+          <t>Valor da métrica-base (followersCount) no primeiro mês-calendário com execução registrada.</t>
         </is>
       </c>
     </row>
@@ -10518,22 +10575,22 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>retencao_confiavel</t>
+          <t>valor_final</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>False sempre que retencao_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL).</t>
+          <t>Valor da métrica-base (followersCount) no último mês-calendário com execução registrada.</t>
         </is>
       </c>
     </row>
@@ -10545,12 +10602,12 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>retencao_motivo</t>
+          <t>cmgr</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -10560,7 +10617,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Motivo da retenção ser NaN, quando aplicável (mesmas categorias do cmgr_motivo).</t>
+          <t>(valor_final / valor_inicial) ** (1 / n_meses) - 1 -- crescimento mensal composto. NaN quando não calculável (ver cmgr_motivo).</t>
         </is>
       </c>
     </row>
@@ -10572,12 +10629,12 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>ilustrativo</t>
+          <t>cmgr_n_periodos</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -10587,7 +10644,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>True enquanto o pipeline não tiver acumulado histórico real suficiente -- sinaliza que o valor valida a FÓRMULA, não sustenta conclusão definitiva no TCC.</t>
+          <t>Número de meses-calendário com execução registrada usados no cálculo do CMGR.</t>
         </is>
       </c>
     </row>
@@ -10599,12 +10656,12 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>cmgr_confiavel</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -10614,7 +10671,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Texto explicando por que o resultado é (ou não) ilustrativo, para exibição direta em dashboard/relatório sem reprocessar nada.</t>
+          <t>False sempre que cmgr_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL) -- sinaliza resultado ilustrativo, não conclusivo.</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10683,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>cmgr_motivo</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -10636,12 +10693,12 @@
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Motivo do CMGR ser NaN, quando aplicável: historico_insuficiente / periodo_zero / valor_inicial_invalido.</t>
         </is>
       </c>
     </row>
@@ -10653,27 +10710,243 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
+          <t>retencao</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>Média de valor_t/valor_(t-1) (capada em 1.0) do share mensal de sentimento positivo entre meses consecutivos -- 1.0 = manteve 100% (ou mais); mede o quanto do período anterior foi retido, não crescimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>retencao_n_periodos</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>Número de meses-calendário com execução registrada usados no cálculo da retenção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>retencao_n_pares_validos</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>Número de pares de meses consecutivos válidos usados na média da retenção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>retencao_confiavel</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>False sempre que retencao_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL).</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>retencao_motivo</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>Motivo da retenção ser NaN, quando aplicável (mesmas categorias do cmgr_motivo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>ilustrativo</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>True enquanto o pipeline não tiver acumulado histórico real suficiente -- sinaliza que o valor valida a FÓRMULA, não sustenta conclusão definitiva no TCC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>nota</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>Texto explicando por que o resultado é (ou não) ilustrativo, para exibição direta em dashboard/relatório sem reprocessar nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>_run_id</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
           <t>_generated_at</t>
         </is>
       </c>
-      <c r="C162" s="3" t="inlineStr">
+      <c r="C170" s="3" t="inlineStr">
         <is>
           <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="inlineStr">
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E162"/>
+  <autoFilter ref="A1:E170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11031,12 +11304,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_clusters</t>
+          <t>Gold: governor_clusters_reels + governor_clusters_posts</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>PCA (engajamento/duração) + AutoClusterHPO (KMeans/DBSCAN/Agglomerative eleito por score CVI) por post; content_type discrimina reel/feed.</t>
+          <t>PCA (engajamento/duração) + AutoClusterHPO (KMeans/DBSCAN/Agglomerative eleito por score CVI) por post; duas tabelas separadas (uma por formato, issue #152) em vez de uma combinada, porque reels_clean/posts_clean se sobrepõem (mesmo Reel capturado por dois actors Apify distintos).</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -11729,12 +12002,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>cluster_score (governor_clusters / governor_profile_clusters_engagement)</t>
+          <t>cluster_score (governor_clusters_reels / governor_clusters_posts / governor_profile_clusters_engagement)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters / governor_profile_clusters_engagement</t>
+          <t>governor_clusters_reels / governor_clusters_posts / governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -559,7 +559,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>PILOTO -- contrato de schema definido e cobertura de teste com dado sintético, mas SEM caminho de escrita de produção ainda; nenhuma linha real esperada em data/ hoje (ADR 0020 Ficha 8 / issue #93, UGC de menções).</t>
+          <t>PILOTO -- contrato de schema definido e cobertura de teste com dado sintético, mas SEM caminho de escrita de produção ainda; nenhuma linha real esperada em data/ hoje. Nenhuma tabela está neste status no momento -- UGC de menções (ADR 0020 Ficha 8 / issue #93) saiu de PILOTO para Produção em 2026-09-19.</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Produção (ressalva) -- writer implementado e testado (2026-09-19), mas SEM execução real disparada ainda (custo Apify -- ver scripts/run_ugc_mentions.py)</t>
+          <t>Produção -- `scripts/run_ugc_mentions.py` rodou contra a Apify de produção pela 1a vez em 2026-09-19 (achado no PR #140), materializando esta tabela com dado real</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>UGC (user-generated content) de terceiros mencionando/marcando o governador, via apify/instagram-tagged-scraper (ver aba Actors Apify -- status PILOTO).</t>
+          <t>UGC (user-generated content) de terceiros mencionando/marcando o governador, via apify/instagram-tagged-scraper (ver aba Actors Apify).</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>O piloto obrigatório da issue #93 (scripts/run_apify_mentions_pilot.py) rodou de verdade em 2026-09-19 contra os 26 perfis com Instagram rastreável (119 posts, data/pilot/mentions_pilot_20260919T030401Z.json) -- grava em data/pilot/*.json, FORA do Delta Lake, não passa pela landing zone nem por BronzeWriter. O schema abaixo foi CORRIGIDO a partir desse resultado real: `authorUsername`/`authorIsVerified`/`isPaidPartnership`/`isAd`/`isAffiliate`/`matchTypes` da especificação original (issue #93) NÃO existem no retorno do actor -- removidos/substituídos por `ownerUsername`/`ownerFullName`/`ownerId`/`paidPartnership`/`taggedUsers` (nomes reais). `scripts/run_ugc_mentions.py` (novo, 2026-09-19) fecha o loop Bronze-&gt;Silver-&gt;Gold sob o mesmo run_id, mesmo padrão de scripts/run_apify_backfill.py -- testado ponta a ponta (Delta real via tmp_path), mas nunca disparado contra a Apify de produção (custo real, decisão do usuário).</t>
+          <t>O piloto obrigatório da issue #93 (scripts/run_apify_mentions_pilot.py) rodou de verdade em 2026-09-19 contra os 26 perfis com Instagram rastreável (119 posts, data/pilot/mentions_pilot_20260919T030401Z.json) -- grava em data/pilot/*.json, FORA do Delta Lake, não passa pela landing zone nem por BronzeWriter. O schema abaixo foi CORRIGIDO a partir desse resultado real: `authorUsername`/`authorIsVerified`/`isPaidPartnership`/`isAd`/`isAffiliate`/`matchTypes` da especificação original (issue #93) NÃO existem no retorno do actor -- removidos/substituídos por `ownerUsername`/`ownerFullName`/`ownerId`/`paidPartnership`/`taggedUsers` (nomes reais). `scripts/run_ugc_mentions.py` (novo, 2026-09-19) fecha o loop Bronze-&gt;Silver-&gt;Gold sob o mesmo run_id, mesmo padrão de scripts/run_apify_backfill.py -- rodou de verdade contra a Apify de produção em 2026-09-19 (o FutureWarning de downcast do PR #140 só apareceu ao processar esse dado real).</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Produção (ressalva) -- mesma ressalva da Bronze ugc_mentions</t>
+          <t>Produção -- mesma execução real de 2026-09-19 da Bronze ugc_mentions</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Nenhum consumidor de produção hoje -- dashboard/screens/funil.py (Tela 6, ADR 0021) proíbe estruturalmente qualquer referência a esta tabela (ver teste test_funil_module_never_references_ugc_tables); src/dashboard/filters.py tem a função de agregação, mas não é chamada por nenhuma tela atual</t>
+          <t>Nenhum consumidor de produção hoje -- dashboard/screens/funil.py (Tela 6, ADR 0021) proíbe estruturalmente qualquer referência a esta tabela (ver teste test_funil_module_never_references_ugc_tables); src/dashboard/filters.py tem a função de agregação, mas não é chamada por nenhuma tela atual. Materializada com dado real desde 2026-09-19, mas o funil (Tela 6, issue #114) continua mostrando 'Engage · Criar' como 'em construção' por decisão de design, não por falta de dado.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Produção (ressalva) -- mesma ressalva de Bronze/Silver ugc_mentions</t>
+          <t>Produção -- mesma execução real de 2026-09-19 de Bronze/Silver ugc_mentions</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3587,7 +3587,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3614,7 +3614,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3641,7 +3641,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3668,7 +3668,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3695,7 +3695,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3722,7 +3722,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3749,7 +3749,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3776,7 +3776,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -3803,7 +3803,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3857,7 +3857,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3884,7 +3884,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3911,7 +3911,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3965,7 +3965,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3992,7 +3992,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4019,7 +4019,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -5958,7 +5958,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -5985,7 +5985,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -6012,7 +6012,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -6039,7 +6039,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -6066,7 +6066,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -6093,7 +6093,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -6120,7 +6120,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -6147,7 +6147,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -6201,7 +6201,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -6228,7 +6228,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -6255,7 +6255,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -6282,7 +6282,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -6309,7 +6309,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -10192,7 +10192,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -10219,7 +10219,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -10273,7 +10273,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -10300,7 +10300,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -10327,7 +10327,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -10354,7 +10354,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -10381,7 +10381,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -10408,7 +10408,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -10435,7 +10435,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -10462,7 +10462,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -10489,7 +10489,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions (schema definido, ainda não materializado)</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Coleta -&gt; landing zone -&gt; Bronze -&gt; Silver (dedup id/shortCode, normalização de handle, resolução de governor_username via mentions+taggedUsers) -&gt; Gold (is_organic a partir de paidPartnership), tudo sob o mesmo run_id -- mesmo padrão de scripts/run_apify_backfill.py. Schema corrigido contra o piloto real (scripts/run_apify_mentions_pilot.py, 2026-09-19, data/pilot/*.json, fora do Delta Lake). Writer de produção implementado e testado, mas ainda NUNCA disparado contra a Apify de produção (custo real).</t>
+          <t>Coleta -&gt; landing zone -&gt; Bronze -&gt; Silver (dedup id/shortCode, normalização de handle, resolução de governor_username via mentions+taggedUsers) -&gt; Gold (is_organic a partir de paidPartnership), tudo sob o mesmo run_id -- mesmo padrão de scripts/run_apify_backfill.py. Schema corrigido contra o piloto real (scripts/run_apify_mentions_pilot.py, 2026-09-19, data/pilot/*.json, fora do Delta Lake). Writer de produção rodou contra a Apify de produção pela 1a vez em 2026-09-19 (achado no PR #140, que corrigiu um FutureWarning de pandas revelado por esse dado real).</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -11668,7 +11668,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Menções/UGC de terceiros (ugc_mentions) -- PILOTO, não produção</t>
+          <t>Menções/UGC de terceiros (ugc_mentions) -- Produção</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>PILOTO -- schema definido e testado com dado sintético; piloto real grava só em data/pilot/*.json (scripts/run_apify_mentions_pilot.py), nunca na Bronze</t>
+          <t>Produção -- scripts/run_ugc_mentions.py rodou contra a Apify de produção em 2026-09-19 (achado no PR #140), gravando Bronze/Silver/Gold com dado real; o piloto isolado (scripts/run_apify_mentions_pilot.py, data/pilot/*.json) continua existindo à parte, para confirmar campo/schema antes de qualquer mudança futura de contrato.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Escolhido sobre fetch_cat/instagram-mentions-scraper por reprodutibilidade (9.999 usuários, 5.0 estrelas vs. actor community "under maintenance", 2 usuários -- docs/research/..., §7.1). Schema de output confirmado por exemplo real da Apify, mas ainda NÃO confirmado 1:1 contra os 27 perfis do projeto.</t>
+          <t>Escolhido sobre fetch_cat/instagram-mentions-scraper por reprodutibilidade (9.999 usuários, 5.0 estrelas vs. actor community "under maintenance", 2 usuários -- docs/research/..., §7.1). Schema de output confirmado 1:1 contra os 27 perfis do projeto pelo piloto real de 2026-09-19, e validado de novo pela execução de produção do mesmo dia.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -17,10 +17,10 @@
     <sheet name="Glossário de Métricas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabelas'!$A$1:$K$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabelas'!$A$1:$K$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Colunas - Bronze'!$A$1:$E$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Colunas - Silver'!$A$1:$E$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$181</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Linhagem'!$A$1:$D$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Actors Apify'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Glossário de Métricas'!$A$1:$E$11</definedName>
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1971,52 +1971,52 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>config/settings.py::GOLD_UGC_MENTIONS (data/gold/governor_ugc_mentions)</t>
+          <t>data/gold/governor_nsm_history</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por post de UGC (grão fino -- agregação por governador é uma view em memória, não persistida).</t>
+          <t>Uma linha por perfil POR EXECUÇÃO do pipeline (mesmo schema de governor_nsm, mas em modo append) -- histórico acumulado ao longo do tempo.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>overwrite</t>
+          <t>append</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/ugc_mentions_aggregator.py (GovernorUGCAggregator), chamado por scripts/run_ugc_mentions.py</t>
+          <t>src/features/gold/nsm_scorer.py (mesmo NsmScorer, path diferente)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Nenhum consumidor de produção hoje -- dashboard/screens/funil.py (Tela 6, ADR 0021) proíbe estruturalmente qualquer referência a esta tabela (ver teste test_funil_module_never_references_ugc_tables); src/dashboard/filters.py tem a função de agregação, mas não é chamada por nenhuma tela atual. Materializada com dado real desde 2026-09-19, mas o funil (Tela 6, issue #114) continua mostrando 'Engage · Criar' como 'em construção' por decisão de design, não por falta de dado.</t>
+          <t>dashboard/core/data.py::load_nsm_history() -&gt; dashboard/screens/resumo.py (Tela 1, delta "vs. média histórica" do KPI Engajamento qualificado)</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Produção -- mesma execução real de 2026-09-19 de Bronze/Silver ugc_mentions</t>
+          <t>Produção -- fecha lacuna que a ADR 0025 previu e adiou (ADR 0027 / issue #160)</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 8 / issue #93</t>
+          <t>ADR 0020 Ficha 5 / ADR 0025 / ADR 0027 / issue #90 / issue #160</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>UGC orgânico vs. publi paga por post, com `is_organic` derivado de `paidPartnership` -- separa apoio espontâneo de publi paga ANTES de qualquer agregação.</t>
+          <t>Base de série temporal de NSM -- permite comparar o NSM da execução mais recente contra a média histórica de execuções anteriores, mesmo raciocínio de governor_engagement_history (ADR 0016).</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>`GovernorUGCAggregator.aggregate_by_governor` (a 'view' de contagem/engajamento médio por governador) nunca expõe `authorUsername` individual no agregado, por desenho -- privacidade de quem menciona o governador, não só do próprio governador. Piloto real (2026-09-19) confirmou que `paidPartnership` é o único campo de publi que o actor expõe -- `isAd`/`isAffiliate` não existem como conceitos distintos, removidos do schema.</t>
+          <t>Nunca sobrescrita nem deduplicada por execução -- cresce indefinidamente; governor_nsm (sem sufixo) continua em overwrite para não quebrar consumidores existentes. Precisa de &gt;= 2 execuções acumuladas para o primeiro delta aparecer no dashboard (mesmo critério de compare_vs_historical_average já usado por % engajamento/Seguidores).</t>
         </is>
       </c>
     </row>
@@ -2028,57 +2028,114 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>governor_ugc_mentions</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>config/settings.py::GOLD_UGC_MENTIONS (data/gold/governor_ugc_mentions)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Uma linha por post de UGC (grão fino -- agregação por governador é uma view em memória, não persistida).</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>overwrite</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>src/features/gold/ugc_mentions_aggregator.py (GovernorUGCAggregator), chamado por scripts/run_ugc_mentions.py</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Nenhum consumidor de produção hoje -- dashboard/screens/funil.py (Tela 6, ADR 0021) proíbe estruturalmente qualquer referência a esta tabela (ver teste test_funil_module_never_references_ugc_tables); src/dashboard/filters.py tem a função de agregação, mas não é chamada por nenhuma tela atual. Materializada com dado real desde 2026-09-19, mas o funil (Tela 6, issue #114) continua mostrando 'Engage · Criar' como 'em construção' por decisão de design, não por falta de dado.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Produção -- mesma execução real de 2026-09-19 de Bronze/Silver ugc_mentions</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>ADR 0020 Ficha 8 / issue #93</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>UGC orgânico vs. publi paga por post, com `is_organic` derivado de `paidPartnership` -- separa apoio espontâneo de publi paga ANTES de qualquer agregação.</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>`GovernorUGCAggregator.aggregate_by_governor` (a 'view' de contagem/engajamento médio por governador) nunca expõe `authorUsername` individual no agregado, por desenho -- privacidade de quem menciona o governador, não só do próprio governador. Piloto real (2026-09-19) confirmou que `paidPartnership` é o único campo de publi que o actor expõe -- `isAd`/`isAffiliate` não existem como conceitos distintos, removidos do schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
           <t>governor_growth_metrics</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>data/gold/governor_growth_metrics</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Uma linha por perfil de governador -- snapshot recalculável a partir do histórico acumulado (sempre overwrite, nunca append).</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>overwrite</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>src/features/gold/model_enricher.py (write_growth_metrics), via scripts/run_growth_metrics.py e src/modeling/growth_history.py</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Nenhuma tela do dashboard atual (ADR 0021) consome esta tabela -- dashboard/core/data.py::load_growth_metrics() existe, mas não é chamada por nenhuma das 6 telas</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>PRODUÇÃO, mas resultado marcado ILUSTRATIVO (ver notas) -- não sustenta conclusão definitiva ainda</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>ADR 0020 Ficha 7 / issue #92</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>CMGR (crescimento mensal composto de seguidores) e retenção de sentimento positivo, calculados sobre governor_engagement_history/governor_sentiment_history.</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>`cmgr_confiavel`/`retencao_confiavel` são False sempre que houver menos de MIN_PERIODS_CONFIAVEL=6 execuções mensais acumuladas -- em 2026-09 o pipeline ainda não acumulou histórico suficiente, então os valores validam a FÓRMULA, não sustentam conclusão real sobre crescimento dos perfis. `motivo`/`nota` explicam o porquê sempre que o valor for NaN ou não confiável.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K25"/>
+  <autoFilter ref="A1:K26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6345,7 +6402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E170"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -10192,12 +10249,12 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -10212,19 +10269,19 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>username</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -10239,100 +10296,100 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>Nome de usuário do perfil de Instagram.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>governor_username</t>
+          <t>n_comentarios_positivos</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
+          <t>Número de comentários (fonte == 'comentario') com sentiment_label == 'positive' deste perfil.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>authorUsername</t>
+          <t>n_comentarios_totais</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
+          <t>Número total de comentários (fonte == 'comentario') deste perfil.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>caption</t>
+          <t>proporcao_positivos</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Legenda do post de UGC (do autor terceiro, não do governador).</t>
+          <t>n_comentarios_positivos / n_comentarios_totais -- 0.0 quando o perfil não tem nenhum comentário (nunca NaN/erro).</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>total_engajamento</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -10347,19 +10404,19 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Cópia de governor_engagement['TOTAL ENGAJAMENTO'] para este perfil, mantida para auditoria/contraste no dashboard.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>count_posts</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -10374,51 +10431,51 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>Cópia de governor_engagement['count'] para este perfil.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>alcance_medio</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
+          <t>total_engajamento / count_posts -- PROXY de alcance (intensidade de engajamento por post), não alcance/views real. 0.0 quando count_posts == 0.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>is_organic</t>
+          <t>nsm</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -10428,24 +10485,24 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Derivado de `paidPartnership`: True quando ausente/False -- separa apoio espontâneo de publi paga.</t>
+          <t>proporcao_positivos × alcance_medio -- North Star Metric de engajamento QUALIFICADO (pondera qualidade de reação, não só volume).</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -10455,24 +10512,24 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -10482,7 +10539,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -10494,34 +10551,34 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>shortCode</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -10536,24 +10593,24 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>valor_inicial</t>
+          <t>governor_username</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -10563,24 +10620,24 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Valor da métrica-base (followersCount) no primeiro mês-calendário com execução registrada.</t>
+          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>valor_final</t>
+          <t>authorUsername</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -10590,24 +10647,24 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Valor da métrica-base (followersCount) no último mês-calendário com execução registrada.</t>
+          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>cmgr</t>
+          <t>caption</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -10617,19 +10674,19 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>(valor_final / valor_inicial) ** (1 / n_meses) - 1 -- crescimento mensal composto. NaN quando não calculável (ver cmgr_motivo).</t>
+          <t>Legenda do post de UGC (do autor terceiro, não do governador).</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>cmgr_n_periodos</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -10644,24 +10701,24 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Número de meses-calendário com execução registrada usados no cálculo do CMGR.</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>cmgr_confiavel</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -10671,24 +10728,24 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>False sempre que cmgr_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL) -- sinaliza resultado ilustrativo, não conclusivo.</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>cmgr_motivo</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -10698,51 +10755,51 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Motivo do CMGR ser NaN, quando aplicável: historico_insuficiente / periodo_zero / valor_inicial_invalido.</t>
+          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>retencao</t>
+          <t>is_organic</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Média de valor_t/valor_(t-1) (capada em 1.0) do share mensal de sentimento positivo entre meses consecutivos -- 1.0 = manteve 100% (ou mais); mede o quanto do período anterior foi retido, não crescimento.</t>
+          <t>Derivado de `paidPartnership`: True quando ausente/False -- separa apoio espontâneo de publi paga.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>retencao_n_periodos</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>timestamp[us]</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -10752,24 +10809,24 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Número de meses-calendário com execução registrada usados no cálculo da retenção.</t>
+          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>retencao_n_pares_validos</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -10779,24 +10836,24 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Número de pares de meses consecutivos válidos usados na média da retenção.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>retencao_confiavel</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -10806,7 +10863,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>False sempre que retencao_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL).</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -10818,7 +10875,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>retencao_motivo</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -10833,7 +10890,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Motivo da retenção ser NaN, quando aplicável (mesmas categorias do cmgr_motivo).</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -10845,22 +10902,22 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>ilustrativo</t>
+          <t>valor_inicial</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>True enquanto o pipeline não tiver acumulado histórico real suficiente -- sinaliza que o valor valida a FÓRMULA, não sustenta conclusão definitiva no TCC.</t>
+          <t>Valor da métrica-base (followersCount) no primeiro mês-calendário com execução registrada.</t>
         </is>
       </c>
     </row>
@@ -10872,22 +10929,22 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>valor_final</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Texto explicando por que o resultado é (ou não) ilustrativo, para exibição direta em dashboard/relatório sem reprocessar nada.</t>
+          <t>Valor da métrica-base (followersCount) no último mês-calendário com execução registrada.</t>
         </is>
       </c>
     </row>
@@ -10899,22 +10956,22 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>cmgr</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>(valor_final / valor_inicial) ** (1 / n_meses) - 1 -- crescimento mensal composto. NaN quando não calculável (ver cmgr_motivo).</t>
         </is>
       </c>
     </row>
@@ -10926,27 +10983,324 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
+          <t>cmgr_n_periodos</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>Número de meses-calendário com execução registrada usados no cálculo do CMGR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>cmgr_confiavel</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>False sempre que cmgr_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL) -- sinaliza resultado ilustrativo, não conclusivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>cmgr_motivo</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>Motivo do CMGR ser NaN, quando aplicável: historico_insuficiente / periodo_zero / valor_inicial_invalido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>retencao</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>Média de valor_t/valor_(t-1) (capada em 1.0) do share mensal de sentimento positivo entre meses consecutivos -- 1.0 = manteve 100% (ou mais); mede o quanto do período anterior foi retido, não crescimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>retencao_n_periodos</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>Número de meses-calendário com execução registrada usados no cálculo da retenção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>retencao_n_pares_validos</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>Número de pares de meses consecutivos válidos usados na média da retenção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>retencao_confiavel</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>False sempre que retencao_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL).</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>retencao_motivo</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>Motivo da retenção ser NaN, quando aplicável (mesmas categorias do cmgr_motivo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>ilustrativo</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>True enquanto o pipeline não tiver acumulado histórico real suficiente -- sinaliza que o valor valida a FÓRMULA, não sustenta conclusão definitiva no TCC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>nota</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>Texto explicando por que o resultado é (ou não) ilustrativo, para exibição direta em dashboard/relatório sem reprocessar nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>_run_id</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
           <t>_generated_at</t>
         </is>
       </c>
-      <c r="C170" s="3" t="inlineStr">
+      <c r="C181" s="3" t="inlineStr">
         <is>
           <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E170"/>
+  <autoFilter ref="A1:E181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>src/modeling (análise de sentimento, BERTopic); src/dashboard/loaders.py (fallback quando governor_sentiment ainda não existe)</t>
+          <t>src/modeling (análise de sentimento, BERTopic)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>src/dashboard/filters.py (nome/UF/partido, seletor de governador)</t>
+          <t>dashboard/core/data.py::load_governors_metadata (nome/UF/partido, seletor de governador em todas as telas)</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/growth_history.py (CMGR); pages/03_performance.py (auto-refresh)</t>
+          <t>src/modeling/growth_history.py (CMGR); dashboard/core/data.py::load_engagement_history (comparação vs. média histórica no Resumo, ADR 0025)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>pages/02_insights.py; src/features/gold/nsm_scorer.py; src/features/gold/topic_priority_scorer.py; scripts/refine_topics.py</t>
+          <t>dashboard/core/data.py::load_sentiment (Resumo, O que produzir, Radar, Discurso x reação); src/features/gold/nsm_scorer.py; src/features/gold/topic_priority_scorer.py; scripts/refine_topics.py</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>pages/03_performance.py (comparação entre governadores, coeficientes da regressão) -- órfã desde a ADR 0021, sem entrypoint ativo (ver seção 4 do README)</t>
+          <t>Nenhum consumidor de produção hoje -- antigo consumidor (pages/03_performance.py, comparação entre governadores/coeficientes da regressão) era órfão desde a ADR 0021 e foi removido do repositório (cleanup pós-auditoria do dashboard, 2026-10)</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>pages/03_performance.py (dispersão previsto vs. real, resíduos) -- órfã desde a ADR 0021, sem entrypoint ativo (ver seção 4 do README)</t>
+          <t>Nenhum consumidor de produção hoje -- antigo consumidor (pages/03_performance.py, dispersão previsto vs. real/resíduos) era órfão desde a ADR 0021 e foi removido do repositório (cleanup pós-auditoria do dashboard, 2026-10)</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Nenhum consumidor de produção hoje -- dashboard/screens/funil.py (Tela 6, ADR 0021) proíbe estruturalmente qualquer referência a esta tabela (ver teste test_funil_module_never_references_ugc_tables); src/dashboard/filters.py tem a função de agregação, mas não é chamada por nenhuma tela atual. Materializada com dado real desde 2026-09-19, mas o funil (Tela 6, issue #114) continua mostrando 'Engage · Criar' como 'em construção' por decisão de design, não por falta de dado.</t>
+          <t>Nenhum consumidor de produção hoje -- dashboard/screens/funil.py (Tela 6, ADR 0021) proíbe estruturalmente qualquer referência a esta tabela (ver teste test_funil_module_never_references_ugc_tables). Materializada com dado real desde 2026-09-19, mas o funil (Tela 6, issue #114) continua mostrando 'Engage · Criar' como 'em construção' por decisão de design, não por falta de dado.</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Dashboard Streamlit (dashboard/app.py + dashboard/screens/*.py, ADR 0021; pages/02-03 remanescentes, órfãs) e notebooks/03-07</t>
+          <t>Dashboard Streamlit (dashboard/app.py + dashboard/screens/*.py, ADR 0021) e notebooks/03-07</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>src/repositories/delta_repository.py + dashboard/core/* + src/dashboard/*</t>
+          <t>src/repositories/delta_repository.py + dashboard/core/*</t>
         </is>
       </c>
     </row>

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -17,13 +17,13 @@
     <sheet name="Glossário de Métricas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabelas'!$A$1:$K$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabelas'!$A$1:$K$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Colunas - Bronze'!$A$1:$E$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Colunas - Silver'!$A$1:$E$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$181</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Linhagem'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Linhagem'!$A$1:$D$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Actors Apify'!$A$1:$H$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Glossário de Métricas'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Glossário de Métricas'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -576,7 +576,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Bronze: 4  |  Silver: 6  |  Gold: 13  |  Total: 23</t>
+          <t>Bronze: 4  |  Silver: 6  |  Gold: 17  |  Total: 27</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>5. Aba 'Glossário de Métricas' -- fórmula completa de cada métrica derivada (% ENGAJAMENTO, NSM, Score ICE, CMGR, retenção, Y da regressão, cluster_score).</t>
+          <t>5. Aba 'Glossário de Métricas' -- fórmula completa de cada métrica derivada (% ENGAJAMENTO, NSM, Score ICE, CMGR, retenção, Y da regressão, cluster_score, Escore composto, Score ICE por pauta).</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>dashboard/core/data.py::load_sentiment (Resumo, O que produzir, Radar, Discurso x reação); src/features/gold/nsm_scorer.py; src/features/gold/topic_priority_scorer.py; scripts/refine_topics.py</t>
+          <t>dashboard/core/data.py::load_sentiment (Resumo [sub-abas NSM e Funil], O que produzir, Radar, Comparar perfis, Discurso x reação); src/features/gold/nsm_scorer.py; src/features/gold/topic_priority_scorer.py; src/features/gold/content_topic_priority_scorer.py; src/modeling/governor_scorecard.py; scripts/refine_topics.py</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>`scripts/refine_topics.py` reescreve os rótulos de `Name` via Gemini sobre esta MESMA tabela (não gera nova medição de sentimento) -- ver ADR 0001. NSM e Score ICE filtram só `fonte == 'comentario'`; linhas de legenda/transcrição não entram nessas duas métricas.</t>
+          <t>`scripts/refine_topics.py` reescreve os rótulos de `Name` via Gemini sobre esta MESMA tabela (não gera nova medição de sentimento) -- ver ADR 0001. A escrita do refino (issue #186) é overwrite SÓ das linhas `fonte == 'comentario'`: as linhas de legenda e transcrição gravadas pela modelagem determinística são PRESERVADAS (antes do #186 o refino apagava essas linhas). NSM, Score ICE (comentário e pauta) e Escore composto (dimensão Qualidade) filtram só `fonte == 'comentario'`; linhas de legenda/transcrição não entram nessas métricas.</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/{resumo,produzir,discurso_reacao,funil}.py (ADR 0021)</t>
+          <t>dashboard/screens/{produzir,discurso_reacao}.py (ADR 0021); src/features/gold/content_topic_priority_scorer.py (pauta de cada reel pela legenda)</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 4 / issue #89</t>
+          <t>ADR 0020 Ficha 4 / issue #89; issue #186 (refino Gemini do discurso)</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Tópicos do que a ASSESSORIA publica (legenda de post/reel + transcrição de fala) -- BERTopic próprio, não misturado ao de comentário.</t>
+          <t>Tópicos do que a ASSESSORIA publica (legenda de post/reel + transcrição de fala) -- BERTopic próprio, não misturado ao de comentário. Cada tópico de legenda é uma PAUTA (assunto do conteúdo) na fila de "O que produzir".</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Conceitualmente distinta de governor_sentiment: fala da assessoria (aqui) vs. reação do público (lá). Nunca comparar os `Topic`/`Name` das duas tabelas como se fossem o mesmo espaço de tópicos.</t>
+          <t>Conceitualmente distinta de governor_sentiment: fala da assessoria (aqui) vs. reação do público (lá). Nunca comparar os `Topic`/`Name` das duas tabelas como se fossem o mesmo espaço de tópicos. RÓTULOS REFINADOS (issue #186): `Name` sai do modelo determinístico como `&lt;id&gt;_kw1_kw2...` (ou `1____` quando o tópico não tem palavra alguma); o refino manual (`scripts/refine_topics.py --target all|discourse`, fora do pipeline automático) troca por `&lt;id&gt;_&lt;rótulo legível&gt;_&lt;kw...&gt;`. O tópico de ruído (`-1`) nunca é refinado e mantém o `Name` que já tinha; o tópico degenerado (sem palavra alguma) recebe o rótulo fixo "sem assunto definido" em vez de um nome inventado. O refino escreve nesta MESMA tabela (overwrite) e recalcula `content_topic_priority_score`. Enquanto o refino real não for rodado, os rótulos são os provisórios do estágio determinístico.</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/{resumo,produzir,funil}.py (ADR 0021)</t>
+          <t>dashboard/screens/{produzir,comparar_clusters,resumo_funil}.py (ADR 0021; análise de clusters de reels em Comparar perfis, issue #189)</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/{resumo,produzir,radar}.py (priorização do que produzir a seguir, ADR 0021)</t>
+          <t>dashboard/screens/radar.py (tópicos de comentário em alerta). Desde a issue #191 a fila de "O que produzir" lê `content_topic_priority_score` (pautas), não esta tabela</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Score ICE (Impacto x Confiança x Facilidade) de priorização de tópicos de comentário -- responde 'sobre o que o governador deveria produzir a seguir'.</t>
+          <t>Score ICE (Impacto x Confiança x Facilidade) de priorização de tópicos de COMENTÁRIO (grupos de comentários) -- não confundir com `content_topic_priority_score`, o ICE por PAUTA (assunto do conteúdo) que alimenta a fila de "O que produzir".</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/resumo.py (Tela 1, ADR 0021)</t>
+          <t>dashboard/screens/resumo_nsm.py (Resumo, sub-aba NSM, ADR 0031 / issue #187)</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>dashboard/core/data.py::load_nsm_history() -&gt; dashboard/screens/resumo.py (Tela 1, delta "vs. média histórica" do KPI Engajamento qualificado)</t>
+          <t>dashboard/core/data.py::load_nsm_history() -&gt; dashboard/screens/resumo_nsm.py (Resumo, sub-aba NSM, delta "vs. média histórica" do KPI Engajamento qualificado)</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Nenhum consumidor de produção hoje -- dashboard/screens/funil.py (Tela 6, ADR 0021) proíbe estruturalmente qualquer referência a esta tabela (ver teste test_funil_module_never_references_ugc_tables). Materializada com dado real desde 2026-09-19, mas o funil (Tela 6, issue #114) continua mostrando 'Engage · Criar' como 'em construção' por decisão de design, não por falta de dado.</t>
+          <t>Nenhum consumidor de produção hoje -- dashboard/screens/resumo_funil.py (sub-aba Funil do Resumo, ADR 0031; antiga Tela 6) proíbe estruturalmente qualquer referência a esta tabela (ver teste test_funil_module_never_references_ugc_tables). Materializada com dado real desde 2026-09-19, mas o funil (issue #114) continua mostrando 'Engage · Criar' como 'em construção' por decisão de design, não por falta de dado.</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Nenhuma tela do dashboard atual (ADR 0021) consome esta tabela -- dashboard/core/data.py::load_growth_metrics() existe, mas não é chamada por nenhuma das 6 telas</t>
+          <t>dashboard/screens/resumo_nsm.py (KPIs de crescimento CMGR e retenção, Resumo sub-aba NSM) via dashboard/core/data.py::load_growth_metrics()</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -2134,8 +2134,122 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>data/gold/governor_scorecard</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Uma linha por governador (um perfil por `inputUrl` normalizado) -- snapshot recalculável a partir da Silver/Gold atual, sempre overwrite.</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>overwrite</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>src/modeling/governor_scorecard.py (GovernorScorecardScorer), via src/modeling/orchestration.py::run_deterministic_modeling (pipeline.py --run-modeling / scripts/run_modeling.py) ou, isoladamente, scripts/run_governor_scorecard.py</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>dashboard/screens/resumo_scorecard.py (Resumo, sub-aba Scorecard) via dashboard/core/data.py::load_governor_scorecard() -- o dashboard só lê, nada é recalculado</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Produção -- com selo de confiabilidade: dimensão Consistência pendente nos 26 governadores no dado de 2026-10-04 (ver notas)</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>ADR 0030 / issue #184 (spec #182)</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Escore composto (0 a 100) dos governadores: soma ponderada de cinco dimensões normalizadas min-máx entre os perfis (Alcance, Ativação, Qualidade, Profundidade, Consistência), seguindo a lógica de indicadores compostos do OECD Handbook (indicador bruto -&gt; normalização -&gt; ponderação -&gt; agregação). Relativo ao grupo: mede posição entre pares, não desempenho absoluto.</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>SELOS DE CONFIABILIDADE. (1) Alcance é medido em REPRODUÇÕES (plays: `videoPlayCount` dos reels), nunca em "visualizações únicas"; posts de feed não têm plays, então só reels entram em Alcance e Profundidade. (2) Consistência mede a TENDÊNCIA do engajamento médio por post por mês de publicação (CMGR de engajamento), NÃO crescimento de audiência -- o CMGR de audiência (seguidores entre coletas, `governor_growth_metrics.cmgr`) continua pendente e fora do escore. (3) Consistência exige &gt;= 4 meses completos com &gt;= 3 posts maduros (&gt;= 7 dias de vida); no dado de 2026-10-04 a Silver só tem ~226 posts de ago/set-2026 e NENHUM dos 26 governadores atinge isso, então `consistencia_pendente = True` e `consistencia`/`consistencia_norm` são nulas em todos: o escore usa as 4 dimensões restantes com peso 0,25 cada (com as 5, 0,20 cada) e `n_dimensoes = 4`. Isso muda sozinho conforme a Silver acumular histórico. (4) Perfil com menos de 4 dimensões disponíveis fica com `escore` e `ranking` nulos. (5) São 26 governadores (a Silver filtra governadores removidos de governadores.xlsx), não 27. Amplitude zero numa dimensão (todos iguais) normaliza para 50.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>data/gold/content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Uma linha por PAUTA (tópico de discurso da legenda do reel) -- ranking global, todos os perfis combinados, não por governador.</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>overwrite</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>src/features/gold/content_topic_priority_scorer.py (ContentTopicPriorityScorer), via src/modeling/orchestration.py::run_deterministic_modeling (provisório, rótulos brutos) e refine_discourse_topics_with_gemini (recalculado com os rótulos refinados)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>dashboard/screens/produzir.py (fila de pautas de "O que produzir") via dashboard/core/data.py::load_content_topic_priority()</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Produção -- com selo de confiabilidade: rótulos de pauta ainda provisórios até o refino manual via Gemini ser rodado de verdade (ver notas)</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>ADR 0020 Ficha 6 (fórmula); ADR 0028; issue #190 / #191 (spec #182)</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Score ICE (Impacto x Confiança x Facilidade) por PAUTA: sobre qual assunto de conteúdo o público reagiu bem. Pauta = tópico de discurso da LEGENDA do reel; os comentários são ligados à pauta pelo reel (`id_reel`).</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Cada reel pertence a uma única pauta (a da legenda; `governor_discourse_topics` tem reels duplicados, deduplicados por `id_reel`); comentários de reels sem pauta de legenda ficam de fora; o tópico de ruído (-1) não é pauta; a transcrição não define pauta (exige plano pago do coletor). `alcance_pauta` é PROXY por engajamento (soma de likesCount + repliesCount dos comentários), nunca "visualizações". `facilidade` fixa em 1,0 (v1, sem dado de custo de produção). O selo de prioridade do dashboard (Alta/Média/Cuidado) vem dos tercis de `score` sobre o ranking global de pautas; o score bruto nunca é exibido. SELO DE CONFIABILIDADE: o refino real dos rótulos via Gemini ainda não foi rodado -- até lá `Name` traz os rótulos provisórios do BERTopic (palavras-chave) e o tópico sem palavra alguma aparece como "sem assunto definido". O ICE é recalculado quando o refino do discurso roda (`scripts/refine_topics.py --target all|discourse`).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K26"/>
+  <autoFilter ref="A1:K28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2962,7 +3076,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3427,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3994,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4988,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5285,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6392,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -10755,7 +10869,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Número de plays do vídeo (Reels/vídeo de feed).</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -11299,8 +11413,926 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>inputUrl</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>URL do perfil do governador (chave de junção; normalizada em minúsculas, sem espaços e sem barra final para cruzar Silver e Gold).</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>username</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>Username do perfil (de governor_engagement); pode ser nulo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>alcance</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>Dimensão Alcance bruta: média de videoPlayCount (REPRODUÇÕES / plays, nunca "visualizações únicas") dos reels do perfil. Posts de feed não têm plays e não entram. Nulo sem reels com plays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>ativacao</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>Dimensão Ativação bruta: média de likesCount dos reels / followersCount do perfil. Nulo sem reels ou sem seguidores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>qualidade</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>Dimensão Qualidade bruta: comentários positivos / comentários totais do perfil (só governor_sentiment com fonte == 'comentario'). Nulo sem comentários.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>profundidade</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>Dimensão Profundidade bruta: média de commentsCount / média de videoPlayCount, ambas sobre os reels com plays (mesma base do Alcance). Nulo sem reels com plays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>consistencia</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>Dimensão Consistência bruta: CMGR de engajamento por data de publicação = exp(inclinação) - 1 da regressão log-linear sobre o engajamento médio por post (curtidas + comentários) de cada mês de publicação. Janela de até 12 meses completos (mês corrente excluído), mês válido com &gt;= 3 posts, posts com &lt; 7 dias de vida excluídos. Nula (pendente) com &lt; 4 meses válidos. NÃO é crescimento de audiência.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>alcance_norm</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>alcance normalizado min-máx 0-100 entre os perfis com a dimensão (100 = maior). Amplitude zero -&gt; 50. Nulo quando a dimensão bruta é nula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>ativacao_norm</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>ativacao normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>qualidade_norm</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>qualidade normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>profundidade_norm</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>profundidade normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>consistencia_norm</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>consistencia normalizada min-máx 0-100 entre os perfis com a dimensão. Nula quando Consistência está pendente (hoje, todos os 26 governadores).</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>consistencia_pendente</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>True quando a Consistência não pôde ser calculada (&lt; 4 meses válidos). Selo de confiabilidade: o escore daquele perfil usa só as outras dimensões, com os pesos renormalizados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>consistencia_n_meses</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>Número de meses de publicação válidos (&gt;= 3 posts maduros, dentro da janela) que entraram, ou entrariam, no cálculo da Consistência.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>n_dimensoes</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>Quantas das 5 dimensões normalizadas entraram no escore deste perfil (5, ou 4 com Consistência pendente). Perfil com &lt; 4 fica sem escore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>escore</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>Escore composto 0-100: média simples das dimensões normalizadas disponíveis (soma ponderada com pesos iguais: 0,20 com 5 dimensões, 0,25 com 4). Nulo com &lt; 4 dimensões. Relativo ao grupo de perfis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>ranking</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>Posição do perfil pelo escore (1 = maior; desempate por inputUrl). Nulo quando o perfil não tem escore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>_run_id</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>_generated_at</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>timestamp[us, tz=UTC]</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>Id numérico do tópico de DISCURSO (BERTopic de legendas) que define a pauta -- espaço de ids distinto do tópico de comentário. O ruído (-1) nunca é pauta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>Rótulo da pauta: tópico de discurso sem o prefixo de id; rótulo refinado via Gemini quando o refino do discurso rodou, palavras-chave separadas por vírgula quando provisório, ou "sem assunto definido" quando o tópico é degenerado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>n_reels</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>Número de reels distintos cuja legenda pertence à pauta e que receberam ao menos um comentário.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>n_comentarios</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>Número de comentários (fonte == 'comentario') dos reels da pauta -- cada reel conta numa única pauta, então os totais somam o total real de comentários com pauta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>n_comentarios_positivos</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>Comentários da pauta com sentiment_label == 'positive'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>n_comentarios_negativos</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>Comentários da pauta com sentiment_label == 'negative'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>proporcao_sentimento_positivo</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>n_comentarios_positivos / n_comentarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>alcance_pauta</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>Soma de (likesCount + repliesCount) dos comentários da pauta -- PROXY por engajamento, não alcance nem visualizações reais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>alcance_normalizado</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>alcance_pauta / (alcance_pauta + 1) -- satura suavemente em [0,1), estável entre execuções.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>confianca</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>Média de sentiment_score (confiança do classificador, não polaridade) dos comentários da pauta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>impacto</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>alcance_normalizado x proporcao_sentimento_positivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>facilidade</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>Fixa em 1,0 (v1) -- sem dado de custo de produção real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>Impacto x Confiança x Facilidade -- base do selo de prioridade (Alta/Média/Cuidado por tercis do ranking global de pautas) na fila de "O que produzir".</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>_run_id</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>_generated_at</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>timestamp[us, tz=UTC]</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E181"/>
+  <autoFilter ref="A1:E215"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11311,7 +12343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11763,71 +12795,137 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_engagement_history + governor_sentiment_history</t>
+          <t>Gold: governor_sentiment (fonte='comentario') + governor_discourse_topics (fonte='legenda')</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_growth_metrics</t>
+          <t>Gold: content_topic_priority_score</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>CMGR sobre followersCount mensal + retenção sobre share mensal de sentimento positivo; marca ilustrativo/confiavel conforme volume de histórico.</t>
+          <t>Score ICE por pauta: comentários ligados à pauta do reel (legenda) via id_reel; Impacto(alcance_normalizado x %positivo) x Confiança(sentiment_score médio) x Facilidade(fixa=1,0), agregado por Topic de discurso. Calculado de forma provisória no estágio determinístico e recalculado após o refino Gemini do discurso.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/growth_history.py + scripts/run_growth_metrics.py</t>
+          <t>src/features/gold/content_topic_priority_scorer.py (orchestration.py::run_deterministic_modeling e refine_discourse_topics_with_gemini)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Apify (apify/instagram-tagged-scraper -- ver aba Actors Apify)</t>
+          <t>Gold: governor_discourse_topics</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Bronze/Silver/Gold: ugc_mentions / governor_ugc_mentions</t>
+          <t>governor_discourse_topics (rótulos refinados)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Coleta -&gt; landing zone -&gt; Bronze -&gt; Silver (dedup id/shortCode, normalização de handle, resolução de governor_username via mentions+taggedUsers) -&gt; Gold (is_organic a partir de paidPartnership), tudo sob o mesmo run_id -- mesmo padrão de scripts/run_apify_backfill.py. Schema corrigido contra o piloto real (scripts/run_apify_mentions_pilot.py, 2026-09-19, data/pilot/*.json, fora do Delta Lake). Writer de produção rodou contra a Apify de produção pela 1a vez em 2026-09-19 (achado no PR #140, que corrigiu um FutureWarning de pandas revelado por esse dado real).</t>
+          <t>Refinamento manual dos rótulos de tópico de discurso (Name) via Gemini; ruído (-1) mantido, tópico degenerado vira "sem assunto definido". Reescreve a mesma tabela e recalcula content_topic_priority_score.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>scripts/run_ugc_mentions.py + src/data_extract/bronze_writer.py + src/features/silver/ugc_mention_cleaner.py + src/features/gold/ugc_mentions_aggregator.py</t>
+          <t>scripts/refine_topics.py (--target all|discourse) + src/modeling/orchestration.py::refine_discourse_topics_with_gemini</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>Gold: governor_engagement (seguidores) + Silver: reels_clean + posts_clean + Gold: governor_sentiment (fonte='comentario')</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Gold: governor_scorecard</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Escore composto: 5 dimensões por governador (Alcance, Ativação, Qualidade, Profundidade, Consistência), normalização min-máx 0-100 entre os perfis, média simples das dimensões disponíveis (pesos iguais renormalizados), ranking. Consistência = CMGR de engajamento por data de publicação (pendente sem &gt;= 4 meses válidos).</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>src/modeling/governor_scorecard.py (orchestration.py::run_deterministic_modeling ou scripts/run_governor_scorecard.py)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Gold: governor_engagement_history + governor_sentiment_history</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Gold: governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>CMGR sobre followersCount mensal + retenção sobre share mensal de sentimento positivo; marca ilustrativo/confiavel conforme volume de histórico.</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>src/modeling/growth_history.py + scripts/run_growth_metrics.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Apify (apify/instagram-tagged-scraper -- ver aba Actors Apify)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Bronze/Silver/Gold: ugc_mentions / governor_ugc_mentions</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Coleta -&gt; landing zone -&gt; Bronze -&gt; Silver (dedup id/shortCode, normalização de handle, resolução de governor_username via mentions+taggedUsers) -&gt; Gold (is_organic a partir de paidPartnership), tudo sob o mesmo run_id -- mesmo padrão de scripts/run_apify_backfill.py. Schema corrigido contra o piloto real (scripts/run_apify_mentions_pilot.py, 2026-09-19, data/pilot/*.json, fora do Delta Lake). Writer de produção rodou contra a Apify de produção pela 1a vez em 2026-09-19 (achado no PR #140, que corrigiu um FutureWarning de pandas revelado por esse dado real).</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>scripts/run_ugc_mentions.py + src/data_extract/bronze_writer.py + src/features/silver/ugc_mention_cleaner.py + src/features/gold/ugc_mentions_aggregator.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>Gold (todas as tabelas acima)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Dashboard Streamlit (dashboard/app.py + dashboard/screens/*.py, ADR 0021) e notebooks/03-07</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Leitura read-only via src/repositories/delta_repository.py (DeltaRepository) -- nunca escreve, save() levanta NotImplementedError deliberadamente.</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>src/repositories/delta_repository.py + dashboard/core/*</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D23"/>
+  <autoFilter ref="A1:D26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12073,7 +13171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -12275,113 +13373,194 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>CMGR (governor_growth_metrics.cmgr)</t>
+          <t>Score ICE por pauta (content_topic_priority_score.score)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>content_topic_priority_score</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>(valor_final / valor_inicial) ** (1 / n_meses) - 1, sobre followersCount mensal</t>
+          <t>Impacto x Confiança x Facilidade, onde Impacto = alcance_normalizado x %positivo, alcance_normalizado = alcance_pauta/(alcance_pauta+1), alcance_pauta = soma de (likes+replies) dos comentários dos reels da pauta</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Crescimento mensal composto de seguidores -- ADR 0020 Ficha 7.</t>
+          <t>Ranking de priorização de PAUTAS (assunto da legenda) para a fila de "O que produzir" -- sobre qual assunto de conteúdo o público reagiu bem. Spec #182 / issue #190.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>cmgr_confiavel=False com menos de 6 execuções mensais acumuladas -- resultado atual (2026-09) é ILUSTRATIVO, valida a fórmula, não sustenta conclusão real no TCC.</t>
+          <t>Facilidade fixa em 1,0; alcance_pauta é proxy por engajamento, não views reais; rótulos de pauta provisórios até o refino Gemini real ser rodado; reel sem pauta de legenda fica de fora.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Retenção (governor_growth_metrics.retencao)</t>
+          <t>Escore composto (governor_scorecard.escore)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Média (capada em 1.0) de valor_t/valor_(t-1) do share mensal de sentimento positivo entre meses consecutivos</t>
+          <t>Média simples das dimensões normalizadas (min-máx 0-100 entre os perfis) disponíveis: Alcance, Ativação, Qualidade, Profundidade, Consistência. Pesos iguais: 0,20 com 5 dimensões, 0,25 com 4 (Consistência pendente).</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Quanto do sentimento positivo do mês anterior foi mantido -- mede retenção, não crescimento (CMGR cobre magnitude).</t>
+          <t>Posição relativa do governador entre os pares, decomponível por dimensão -- ADR 0030 / issue #184.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Mesma ressalva de confiabilidade do CMGR (min. 6 períodos).</t>
+          <t>Relativo ao grupo (26 perfis hoje), não desempenho absoluto. Alcance = reproduções (plays) só de reels. Consistência pendente nos 26 perfis no dado de 2026-10-04 (histórico de publicação curto) -- hoje o escore é de 4 dimensões. Perfil com &lt; 4 dimensões não tem escore.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Y da regressão de performance-por-post</t>
+          <t>CMGR de engajamento (governor_scorecard.consistencia)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>post_performance_predictions (y_real/y_previsto/residuo)</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>(likesCount + commentsCount × _WC_COMENTARIO) / followersCount, por POST (não por perfil)</t>
+          <t>exp(inclinação da regressão log-linear do engajamento médio por post por mês de publicação) - 1; janela de até 12 meses completos, mês com &gt;= 3 posts, posts com &gt;= 7 dias de vida, &gt;= 4 meses válidos</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Mesma lógica ponderada de % ENGAJAMENTO, mas na granularidade de post individual -- variável explicada pela regressão Lasso (ADR 0019 parte C).</t>
+          <t>Tendência mensal composta do engajamento dos posts por data de publicação (ADR 0030). Distinto do CMGR de audiência (seguidores entre coletas).</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Preditores derivados das mesmas colunas brutas de Y são bloqueados por checagem de circularidade (CircularityError) antes do treino.</t>
+          <t>Não mede crescimento de audiência. Nula quando o histórico de publicação é curto (hoje, todos os perfis).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>CMGR (governor_growth_metrics.cmgr)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>(valor_final / valor_inicial) ** (1 / n_meses) - 1, sobre followersCount mensal</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Crescimento mensal composto de seguidores -- ADR 0020 Ficha 7.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>cmgr_confiavel=False com menos de 6 execuções mensais acumuladas -- resultado atual (2026-09) é ILUSTRATIVO, valida a fórmula, não sustenta conclusão real no TCC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Retenção (governor_growth_metrics.retencao)</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>governor_growth_metrics</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Média (capada em 1.0) de valor_t/valor_(t-1) do share mensal de sentimento positivo entre meses consecutivos</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Quanto do sentimento positivo do mês anterior foi mantido -- mede retenção, não crescimento (CMGR cobre magnitude).</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Mesma ressalva de confiabilidade do CMGR (min. 6 períodos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Y da regressão de performance-por-post</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>post_performance_predictions (y_real/y_previsto/residuo)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>(likesCount + commentsCount × _WC_COMENTARIO) / followersCount, por POST (não por perfil)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Mesma lógica ponderada de % ENGAJAMENTO, mas na granularidade de post individual -- variável explicada pela regressão Lasso (ADR 0019 parte C).</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Preditores derivados das mesmas colunas brutas de Y são bloqueados por checagem de circularidade (CircularityError) antes do treino.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>cluster_score (governor_clusters_reels / governor_clusters_posts / governor_profile_clusters_engagement)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>governor_clusters_reels / governor_clusters_posts / governor_profile_clusters_engagement</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Silhouette + Calinski-Harabasz normalizado (tanh(chi/10000)) + Davies-Bouldin invertido (tanh(1/dbi)), combinado</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Score CVI (Cluster Validity Index) combinado usado pelo AutoClusterHPO para eleger o algoritmo/hiperparâmetros de clusterização.</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Pontos de ruído do DBSCAN (cluster_label=-1) são filtrados ANTES do cálculo do CVI, para não distorcer a comparação entre algoritmos.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -2053,7 +2053,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Nenhum consumidor de produção hoje -- dashboard/screens/resumo_funil.py (sub-aba Funil do Resumo, ADR 0031; antiga Tela 6) proíbe estruturalmente qualquer referência a esta tabela (ver teste test_funil_module_never_references_ugc_tables). Materializada com dado real desde 2026-09-19, mas o funil (issue #114) continua mostrando 'Engage · Criar' como 'em construção' por decisão de design, não por falta de dado.</t>
+          <t>dashboard/screens/resumo_funil.py (sub-aba Funil do Resumo) via dashboard/core/data.py::load_ugc_mentions: o estágio Engage·Criar mostra a soma de curtidas + comentários dos posts orgânicos por governador, com selo 'piloto' (ADR 0032, que revisa a proibição original da issue #114). Limitação: o piloto coletou no máximo 5 posts por governador.</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -2053,7 +2053,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/resumo_funil.py (sub-aba Funil do Resumo) via dashboard/core/data.py::load_ugc_mentions: o estágio Engage·Criar mostra a soma de curtidas + comentários dos posts orgânicos por governador, com selo 'piloto' (ADR 0032, que revisa a proibição original da issue #114). Limitação: o piloto coletou no máximo 5 posts por governador.</t>
+          <t>dashboard/screens/resumo_funil.py (sub-aba Funil do Resumo) via dashboard/core/data.py::load_ugc_mentions: o estágio Engage·Criar mostra a mediana de curtidas + comentários por post orgânico de cada governador, com selo 'piloto' (ADR 0032, que revisa a proibição original da issue #114). Limitação: o piloto coletou no máximo 5 posts por governador.</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -2053,7 +2053,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/resumo_funil.py (sub-aba Funil do Resumo) via dashboard/core/data.py::load_ugc_mentions: o estágio Engage·Criar mostra a mediana de curtidas + comentários por post orgânico de cada governador, com selo 'piloto' (ADR 0032, que revisa a proibição original da issue #114). Limitação: o piloto coletou no máximo 5 posts por governador.</t>
+          <t>dashboard/screens/resumo_funil.py (sub-aba Funil do Resumo) via dashboard/core/data.py::load_ugc_mentions: o estágio Engage·Criar mostra o número de posts de UGC orgânico de cada governador, com selo 'piloto' (ADR 0032, que revisa a proibição original da issue #114). Limitação: o piloto atual é uma amostra de teste que coletou no máximo 5 posts por governador (a tela avisa e esconde o comparativo enquanto o máximo for &lt;= 5).</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -2053,7 +2053,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/resumo_funil.py (sub-aba Funil do Resumo) via dashboard/core/data.py::load_ugc_mentions: o estágio Engage·Criar mostra o número de posts de UGC orgânico de cada governador, com selo 'piloto' (ADR 0032, que revisa a proibição original da issue #114). Limitação: o piloto atual é uma amostra de teste que coletou no máximo 5 posts por governador (a tela avisa e esconde o comparativo enquanto o máximo for &lt;= 5).</t>
+          <t>dashboard/screens/resumo_funil.py (sub-aba Funil do Resumo) via dashboard/core/data.py::load_ugc_mentions: o estágio Engage·Criar mostra o número de posts de UGC orgânico de cada governador, com selo 'piloto' (ADR 0032, que revisa a proibição original da issue #114). Limitação: o piloto atual é uma amostra de teste que coletou no máximo 5 posts por governador (a tela esconde o comparativo do Engage enquanto o máximo for &lt;= 5).</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -17,11 +17,11 @@
     <sheet name="Glossário de Métricas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabelas'!$A$1:$K$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Colunas - Bronze'!$A$1:$E$72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Colunas - Silver'!$A$1:$E$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$215</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Linhagem'!$A$1:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabelas'!$A$1:$K$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Colunas - Bronze'!$A$1:$E$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Colunas - Silver'!$A$1:$E$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Linhagem'!$A$1:$D$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Actors Apify'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Glossário de Métricas'!$A$1:$E$14</definedName>
   </definedNames>
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -799,7 +799,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/post_cleaner.py (PostCleaner.clean_posts)</t>
+          <t>src/features/silver/post_cleaner.py (PostCleaner.clean_posts), src/features/silver/comment_cleaner.py (CommentCleaner(origem='post').clean)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Não tem campo de comentário embutido (latestComments) -- por isso governor_sentiment/comments_clean só cobrem comentário de Reels, nunca de post de feed. Payload bruto arquivado em data/landing/&lt;run_id&gt;/posts.json (ou /tmp/landing/... na Lambda) ANTES desta escrita -- ver aba Linhagem. Perfil sem NENHUM post próprio (0 itens, não confundir com perfil sem `id`) gera item de erro `{"error": "no_items", "errorDescription": "Empty or private data..."}` -- caso real (2026-09): claudiocastrorj (verificado, 2M+ seguidores) tinha só marcações de terceiros na grade, zero posts/reels próprios publicados.</t>
+          <t>Desde a issue #212 guarda `latestComments` (comentários mais recentes do post, JSON string), fonte de post_comments_clean -- antes a coluna era descartada aqui e só havia comentário de Reels no projeto. Bronzes antigas recebem a coluna no append (schema_mode=merge), com linhas antigas nulas. Payload bruto arquivado em data/landing/&lt;run_id&gt;/posts.json (ou /tmp/landing/... na Lambda) ANTES desta escrita -- ver aba Linhagem. Perfil sem NENHUM post próprio (0 itens, não confundir com perfil sem `id`) gera item de erro `{"error": "no_items", "errorDescription": "Empty or private data..."}` -- caso real (2026-09): claudiocastrorj (verificado, 2M+ seguidores) tinha só marcações de terceiros na grade, zero posts/reels próprios publicados.</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/bronze_writer.py (BronzeWriter.write_ugc_mentions), chamado por scripts/run_ugc_mentions.py</t>
+          <t>src/data_extract/bronze_writer.py (BronzeWriter.write_ugc_mentions), chamado por src/data_extract/ingestion.py::extract_and_land (pipeline.py, scripts/run_apify_backfill.py, lambdas/extract) -- issue #211</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Produção -- `scripts/run_ugc_mentions.py` rodou contra a Apify de produção pela 1a vez em 2026-09-19 (achado no PR #140), materializando esta tabela com dado real</t>
+          <t>Produção -- coletada a cada extração do pipeline.py desde a issue #211 (antes, pelo script standalone scripts/run_ugc_mentions.py, removido; 1a execução real em 2026-09-19, PR #140)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>O piloto obrigatório da issue #93 (scripts/run_apify_mentions_pilot.py) rodou de verdade em 2026-09-19 contra os 26 perfis com Instagram rastreável (119 posts, data/pilot/mentions_pilot_20260919T030401Z.json) -- grava em data/pilot/*.json, FORA do Delta Lake, não passa pela landing zone nem por BronzeWriter. O schema abaixo foi CORRIGIDO a partir desse resultado real: `authorUsername`/`authorIsVerified`/`isPaidPartnership`/`isAd`/`isAffiliate`/`matchTypes` da especificação original (issue #93) NÃO existem no retorno do actor -- removidos/substituídos por `ownerUsername`/`ownerFullName`/`ownerId`/`paidPartnership`/`taggedUsers` (nomes reais). `scripts/run_ugc_mentions.py` (novo, 2026-09-19) fecha o loop Bronze-&gt;Silver-&gt;Gold sob o mesmo run_id, mesmo padrão de scripts/run_apify_backfill.py -- rodou de verdade contra a Apify de produção em 2026-09-19 (o FutureWarning de downcast do PR #140 só apareceu ao processar esse dado real).</t>
+          <t>O piloto obrigatório da issue #93 (scripts/run_apify_mentions_pilot.py) rodou de verdade em 2026-09-19 contra os 26 perfis com Instagram rastreável (119 posts, data/pilot/mentions_pilot_20260919T030401Z.json) -- grava em data/pilot/*.json, FORA do Delta Lake, não passa pela landing zone nem por BronzeWriter. O schema abaixo foi CORRIGIDO a partir desse resultado real: `authorUsername`/`authorIsVerified`/`isPaidPartnership`/`isAd`/`isAffiliate`/`matchTypes` da especificação original (issue #93) NÃO existem no retorno do actor -- removidos/substituídos por `ownerUsername`/`ownerFullName`/`ownerId`/`paidPartnership`/`taggedUsers` (nomes reais). Desde a issue #211 a coleta de UGC é a ÚLTIMA etapa de extract_and_land e é tolerante a falha (actor com erro ou lista vazia não descarta perfis/posts/reels já gravados); com --days, recebe o mesmo onlyPostsNewerThan (aceitação pelo actor não confirmada -- o pipeline filtra a Silver pela janela como salvaguarda).</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Deriva EXCLUSIVAMENTE de Reels -- posts de feed não carregam comentário embutido no dado coletado, então não existe 'comentário de post' em nenhuma tabela do projeto. `clean()` também filtra por `governor_usernames`, pelo `ownerUsername` do REEL (o governador) ANTES do explode -- depois dele, `ownerUsername` passa a se referir ao autor do comentário, não ao governador (achado original: PR #137).</t>
+          <t>Só comentários de Reels (`id_reel`); os de posts de feed ficam na tabela separada post_comments_clean (issue #212) e as duas origens só se juntam na modelagem (governor_sentiment.origem_comentario). `clean()` também filtra por `governor_usernames`, pelo `ownerUsername` do REEL (o governador) ANTES do explode -- depois dele, `ownerUsername` passa a se referir ao autor do comentário, não ao governador (achado original: PR #137).</t>
         </is>
       </c>
     </row>
@@ -1173,52 +1173,52 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>governors_metadata</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>data/silver/governors_metadata</t>
+          <t>config/settings.py::SILVER_POST_COMMENTS (data/silver/post_comments_clean)</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por governador COM Instagram rastreável, deduplicada por `inputUrl` -- governador sem `Link` na planilha (célula em branco) não gera linha aqui.</t>
+          <t>Uma linha por comentário de post de feed, explodido de `latestComments` (Bronze instagram_posts) e deduplicado por `id_comment`.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>overwrite</t>
+          <t>overwrite (não gravada quando não há nenhum comentário de post na Bronze)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/governors_metadata_cleaner.py (GovernorsMetadataCleaner.clean/write)</t>
+          <t>src/features/silver/comment_cleaner.py (CommentCleaner(origem='post').clean/write), chamado por pipeline.py</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>dashboard/core/data.py::load_governors_metadata (nome/UF/partido, seletor de governador em todas as telas)</t>
+          <t>src/repositories/delta_repository.py::load_post_comments (scripts/run_modeling.py); pipeline.py repassa direto à modelagem (src/modeling/comment_sources.py::combine_comment_sources)</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Produção (26 de 27 governadores -- ver notas)</t>
+          <t>Produção (issue #212)</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ADR 0033</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Dimensão de governador (nome, UF, partido) ingerida de reference/governadores.xlsx -- fonte única de verdade para o dashboard em vez de ler a planilha bruta a cada carregamento.</t>
+          <t>Comentários de posts de feed, em tabela SEPARADA de comments_clean (reels) para as duas origens poderem ser analisadas à parte.</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>`reference/governadores.xlsx` é mantido manualmente, fora do pipeline (ADR 0013) -- esta é a ÚNICA leitura de Excel que resta no projeto, e é de configuração, não de dado coletado. Governador sem Instagram rastreável (`Link` em branco) é descartado ANTES do cast para string, para não virar o texto literal 'nan' em `inputUrl` (NOT NULL, chave de junção do pipeline inteiro) -- mesmo filtro em scripts/apify_backfill_shared.py::load_links(). Caso real (2026-09): Rio de Janeiro fica sem Instagram rastreável desde a renúncia de Cláudio Castro (2026-03-23) -- o titular interino (desembargador Ricardo Couto, presidente do TJ-RJ) não tem perfil público de gestão. governors_metadata/Bronze/Silver/Gold refletem 26 governadores enquanto essa situação persistir.</t>
+          <t>Mesmas regras de comments_clean (filtro do governador pelo `ownerUsername` do POST antes do explode, &lt; 512 caracteres, dedup por id_comment). `id_post` inclui reels capturados no grid de posts (issue #152): o mesmo comentário pode existir aqui e em comments_clean -- a modelagem deduplica por id_comment preferindo a linha de reel.</t>
         </is>
       </c>
     </row>
@@ -1230,17 +1230,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>governors_metadata</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>config/settings.py::SILVER_UGC_MENTIONS (data/silver/ugc_mentions)</t>
+          <t>data/silver/governors_metadata</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por post de UGC, com `governor_username` já resolvido e `authorUsername` já normalizado.</t>
+          <t>Uma linha por governador COM Instagram rastreável, deduplicada por `inputUrl` -- governador sem `Link` na planilha (célula em branco) não gera linha aqui.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1250,54 +1250,54 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/ugc_mention_cleaner.py (UGCMentionCleaner), chamado por scripts/run_ugc_mentions.py</t>
+          <t>src/features/silver/governors_metadata_cleaner.py (GovernorsMetadataCleaner.clean/write)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/ugc_mentions_aggregator.py, chamado por scripts/run_ugc_mentions.py</t>
+          <t>dashboard/core/data.py::load_governors_metadata (nome/UF/partido, seletor de governador em todas as telas)</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Produção -- mesma execução real de 2026-09-19 da Bronze ugc_mentions</t>
+          <t>Produção (26 de 27 governadores -- ver notas)</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 8 / issue #93</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>UGC de terceiros já limpo: `governor_username` derivado de `mentions` E `taggedUsers` (Bronze) cruzados com a lista de usernames conhecidos; `authorUsername` normaliza o handle do autor terceiro (na prática, sempre a partir de `ownerUsername` -- ver Bronze).</t>
+          <t>Dimensão de governador (nome, UF, partido) ingerida de reference/governadores.xlsx -- fonte única de verdade para o dashboard em vez de ler a planilha bruta a cada carregamento.</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>`id`/`shortCode` são nullable aqui (ao contrário do padrão NOT NULL de profiles/posts/reels) porque o piloto ainda não confirmou presença garantida de `id` no actor escolhido -- o cleaner descarta linha sem os dois. Piloto real (2026-09-19) confirmou que checar só `mentions` perderia ~69% dos posts correlacionáveis -- a maioria só tem a marcação visual em `taggedUsers`, não @-menção em texto.</t>
+          <t>`reference/governadores.xlsx` é mantido manualmente, fora do pipeline (ADR 0013) -- esta é a ÚNICA leitura de Excel que resta no projeto, e é de configuração, não de dado coletado. Governador sem Instagram rastreável (`Link` em branco) é descartado ANTES do cast para string, para não virar o texto literal 'nan' em `inputUrl` (NOT NULL, chave de junção do pipeline inteiro) -- mesmo filtro em scripts/apify_backfill_shared.py::load_links(). Caso real (2026-09): Rio de Janeiro fica sem Instagram rastreável desde a renúncia de Cláudio Castro (2026-03-23) -- o titular interino (desembargador Ricardo Couto, presidente do TJ-RJ) não tem perfil público de gestão. governors_metadata/Bronze/Silver/Gold refletem 26 governadores enquanto essa situação persistir.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>governor_engagement</t>
+          <t>ugc_mentions</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_engagement</t>
+          <t>config/settings.py::SILVER_UGC_MENTIONS (data/silver/ugc_mentions)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por perfil de governador -- snapshot agregado da execução mais recente.</t>
+          <t>Uma linha por post de UGC, com `governor_username` já resolvido e `authorUsername` já normalizado.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/engagement_aggregator.py (EngagementAggregator)</t>
+          <t>src/features/silver/ugc_mention_cleaner.py (UGCMentionCleaner), chamado por pipeline.py (estágio Silver, a cada execução, inclusive com Bronze reaproveitada)</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>pages/*; src/modeling/post_performance.py; src/features/gold/nsm_scorer.py</t>
+          <t>src/features/gold/ugc_mentions_aggregator.py, chamado por pipeline.py</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Produção</t>
+          <t>Produção -- mesma execução real de 2026-09-19 da Bronze ugc_mentions</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>ADR 0018</t>
+          <t>ADR 0020 Ficha 8 / issue #93</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Métricas de engajamento por perfil: total ponderado, taxa sobre seguidores, recência e frequência de publicação.</t>
+          <t>UGC de terceiros já limpo: `governor_username` derivado de `mentions` E `taggedUsers` (Bronze) cruzados com a lista de usernames conhecidos; `authorUsername` normaliza o handle do autor terceiro (na prática, sempre a partir de `ownerUsername` -- ver Bronze).</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Sempre sobrescrita por completo a cada execução -- para série temporal, ver governor_engagement_history. LIMITAÇÃO CORRIGIDA (2026-09-19): profiles_clean/posts_clean/reels_clean/comments_clean agora filtram contra governor_usernames (scripts.apify_backfill_shared.load_governor_usernames(), a partir de governadores.xlsx atual) ANTES de qualquer Gold -- um governador removido da planilha (ex.: Rio de Janeiro/claudiocastrorj até 2026-09, ver PR #136) some de profiles_clean e, em cascata, desta tabela e de todas as demais Gold derivadas, em vez de continuar reaparecendo indefinidamente com dado cada vez mais desatualizado (achado original: PR #137).</t>
+          <t>`id`/`shortCode` são nullable aqui (ao contrário do padrão NOT NULL de profiles/posts/reels) porque o piloto ainda não confirmou presença garantida de `id` no actor escolhido -- o cleaner descarta linha sem os dois. Piloto real (2026-09-19) confirmou que checar só `mentions` perderia ~69% dos posts correlacionáveis -- a maioria só tem a marcação visual em `taggedUsers`, não @-menção em texto.</t>
         </is>
       </c>
     </row>
@@ -1344,52 +1344,52 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>governor_engagement_history</t>
+          <t>governor_engagement</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_engagement_history</t>
+          <t>data/gold/governor_engagement</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por perfil POR EXECUÇÃO do pipeline (mesmo schema de governor_engagement, mas em modo append) -- histórico acumulado ao longo do tempo.</t>
+          <t>Uma linha por perfil de governador -- snapshot agregado da execução mais recente.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>append</t>
+          <t>overwrite</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/engagement_aggregator.py (mesmo EngagementAggregator, path diferente)</t>
+          <t>src/features/gold/engagement_aggregator.py (EngagementAggregator)</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/growth_history.py (CMGR); dashboard/core/data.py::load_engagement_history (comparação vs. média histórica no Resumo, ADR 0025)</t>
+          <t>pages/*; src/modeling/post_performance.py; src/features/gold/nsm_scorer.py</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Produção (histórico ainda curto -- ver governor_growth_metrics)</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>ADR 0016</t>
+          <t>ADR 0018</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Base de série temporal de engajamento -- permite calcular tendência/crescimento sem reprocessar Bronze/Silver.</t>
+          <t>Métricas de engajamento por perfil: total ponderado, taxa sobre seguidores, recência e frequência de publicação.</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Nunca sobrescrita nem deduplicada por execução -- cresce indefinidamente; governor_engagement (sem sufixo) continua em overwrite para não quebrar consumidores existentes.</t>
+          <t>Sempre sobrescrita por completo a cada execução -- para série temporal, ver governor_engagement_history. LIMITAÇÃO CORRIGIDA (2026-09-19): profiles_clean/posts_clean/reels_clean/comments_clean agora filtram contra governor_usernames (scripts.apify_backfill_shared.load_governor_usernames(), a partir de governadores.xlsx atual) ANTES de qualquer Gold -- um governador removido da planilha (ex.: Rio de Janeiro/claudiocastrorj até 2026-09, ver PR #136) some de profiles_clean e, em cascata, desta tabela e de todas as demais Gold derivadas, em vez de continuar reaparecendo indefinidamente com dado cada vez mais desatualizado (achado original: PR #137).</t>
         </is>
       </c>
     </row>
@@ -1401,52 +1401,52 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>governor_sentiment</t>
+          <t>governor_engagement_history</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_sentiment</t>
+          <t>data/gold/governor_engagement_history</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por texto avaliado (comentário, legenda ou transcrição) -- granularidade mista, discriminada pela coluna `fonte`.</t>
+          <t>Uma linha por perfil POR EXECUÇÃO do pipeline (mesmo schema de governor_engagement, mas em modo append) -- histórico acumulado ao longo do tempo.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>overwrite</t>
+          <t>append</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (ModelEnricher.write_sentiment), a partir de src/modeling/sentiment.py + BERTopic</t>
+          <t>src/features/gold/engagement_aggregator.py (mesmo EngagementAggregator, path diferente)</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>dashboard/core/data.py::load_sentiment (Resumo [sub-abas NSM e Funil], O que produzir, Radar, Comparar perfis, Discurso x reação); src/features/gold/nsm_scorer.py; src/features/gold/topic_priority_scorer.py; src/features/gold/content_topic_priority_scorer.py; src/modeling/governor_scorecard.py; scripts/refine_topics.py</t>
+          <t>src/modeling/growth_history.py (CMGR); dashboard/core/data.py::load_engagement_history (comparação vs. média histórica no Resumo, ADR 0025)</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Produção</t>
+          <t>Produção (histórico ainda curto -- ver governor_growth_metrics)</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>ADR 0019 (Topic/Name determinístico); ADR 0020 Ficha 3 / issue #88 (coluna fonte)</t>
+          <t>ADR 0016</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Sentimento (cardiffnlp/twitter-xlm-roberta-base-sentiment) e tópico BERTopic por texto avaliado.</t>
+          <t>Base de série temporal de engajamento -- permite calcular tendência/crescimento sem reprocessar Bronze/Silver.</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>`scripts/refine_topics.py` reescreve os rótulos de `Name` via Gemini sobre esta MESMA tabela (não gera nova medição de sentimento) -- ver ADR 0001. A escrita do refino (issue #186) é overwrite SÓ das linhas `fonte == 'comentario'`: as linhas de legenda e transcrição gravadas pela modelagem determinística são PRESERVADAS (antes do #186 o refino apagava essas linhas). NSM, Score ICE (comentário e pauta) e Escore composto (dimensão Qualidade) filtram só `fonte == 'comentario'`; linhas de legenda/transcrição não entram nessas métricas.</t>
+          <t>Nunca sobrescrita nem deduplicada por execução -- cresce indefinidamente; governor_engagement (sem sufixo) continua em overwrite para não quebrar consumidores existentes.</t>
         </is>
       </c>
     </row>
@@ -1458,52 +1458,52 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>governor_sentiment_history</t>
+          <t>governor_sentiment</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_sentiment_history</t>
+          <t>data/gold/governor_sentiment</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por comentário/legenda/transcrição POR EXECUÇÃO de modelagem (mesmo schema de governor_sentiment, em modo append).</t>
+          <t>Uma linha por texto avaliado (comentário, legenda ou transcrição) -- granularidade mista, discriminada pela coluna `fonte`.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>append</t>
+          <t>overwrite</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (mesmo ModelEnricher, path diferente)</t>
+          <t>src/features/gold/model_enricher.py (ModelEnricher.write_sentiment), a partir de src/modeling/sentiment.py + BERTopic</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/growth_history.py (retenção de sentimento positivo)</t>
+          <t>dashboard/core/data.py::load_sentiment (Resumo [sub-abas NSM e Funil], O que produzir, Radar, Comparar perfis, Discurso x reação); src/features/gold/nsm_scorer.py; src/features/gold/topic_priority_scorer.py; src/features/gold/content_topic_priority_scorer.py; src/modeling/governor_scorecard.py; scripts/refine_topics.py</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Produção (histórico ainda curto)</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>ADR 0017 / issue #52</t>
+          <t>ADR 0019 (Topic/Name determinístico); ADR 0020 Ficha 3 / issue #88 (coluna fonte)</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Base de série temporal de sentimento -- alimenta a retenção de sentimento positivo do CMGR/Ficha 7.</t>
+          <t>Sentimento (cardiffnlp/twitter-xlm-roberta-base-sentiment) e tópico BERTopic por texto avaliado.</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Mesma ressalva de granularidade mista de governor_sentiment (comentário/legenda/transcrição via `fonte`).</t>
+          <t>Comentários de reels e de posts de feed (issue #212) convivem nas linhas `fonte == 'comentario'`, discriminados por `origem_comentario` ('reel'/'post'); `id_reel` significa 'id da publicação comentada' (reel ou post). Um comentário presente nas duas origens entra uma vez, como 'reel'. `scripts/refine_topics.py` reescreve os rótulos de `Name` via Gemini sobre esta MESMA tabela (não gera nova medição de sentimento) -- ver ADR 0001. A escrita do refino (issue #186) é overwrite SÓ das linhas `fonte == 'comentario'`: as linhas de legenda e transcrição gravadas pela modelagem determinística são PRESERVADAS (antes do #186 o refino apagava essas linhas). NSM, Score ICE (comentário e pauta) e Escore composto (dimensão Qualidade) filtram só `fonte == 'comentario'`; linhas de legenda/transcrição não entram nessas métricas.</t>
         </is>
       </c>
     </row>
@@ -1515,52 +1515,52 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>governor_discourse_topics</t>
+          <t>governor_sentiment_history</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_discourse_topics</t>
+          <t>data/gold/governor_sentiment_history</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por legenda/transcrição avaliada pelo BERTopic de discurso oficial.</t>
+          <t>Uma linha por comentário/legenda/transcrição POR EXECUÇÃO de modelagem (mesmo schema de governor_sentiment, em modo append).</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>overwrite</t>
+          <t>append</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (ModelEnricher.write_discourse_topics)</t>
+          <t>src/features/gold/model_enricher.py (mesmo ModelEnricher, path diferente)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/{produzir,discurso_reacao}.py (ADR 0021); src/features/gold/content_topic_priority_scorer.py (pauta de cada reel pela legenda)</t>
+          <t>src/modeling/growth_history.py (retenção de sentimento positivo)</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Produção</t>
+          <t>Produção (histórico ainda curto)</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 4 / issue #89; issue #186 (refino Gemini do discurso)</t>
+          <t>ADR 0017 / issue #52</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Tópicos do que a ASSESSORIA publica (legenda de post/reel + transcrição de fala) -- BERTopic próprio, não misturado ao de comentário. Cada tópico de legenda é uma PAUTA (assunto do conteúdo) na fila de "O que produzir".</t>
+          <t>Base de série temporal de sentimento -- alimenta a retenção de sentimento positivo do CMGR/Ficha 7.</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Conceitualmente distinta de governor_sentiment: fala da assessoria (aqui) vs. reação do público (lá). Nunca comparar os `Topic`/`Name` das duas tabelas como se fossem o mesmo espaço de tópicos. RÓTULOS REFINADOS (issue #186): `Name` sai do modelo determinístico como `&lt;id&gt;_kw1_kw2...` (ou `1____` quando o tópico não tem palavra alguma); o refino manual (`scripts/refine_topics.py --target all|discourse`, fora do pipeline automático) troca por `&lt;id&gt;_&lt;rótulo legível&gt;_&lt;kw...&gt;`. O tópico de ruído (`-1`) nunca é refinado e mantém o `Name` que já tinha; o tópico degenerado (sem palavra alguma) recebe o rótulo fixo "sem assunto definido" em vez de um nome inventado. O refino escreve nesta MESMA tabela (overwrite) e recalcula `content_topic_priority_score`. Enquanto o refino real não for rodado, os rótulos são os provisórios do estágio determinístico.</t>
+          <t>Mesma ressalva de granularidade mista de governor_sentiment (comentário/legenda/transcrição via `fonte`).</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters_reels</t>
+          <t>governor_discourse_topics</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_clusters_reels</t>
+          <t>data/gold/governor_discourse_topics</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por Reel -- clusterização de CONTEÚDO, não de perfil.</t>
+          <t>Uma linha por legenda/transcrição avaliada pelo BERTopic de discurso oficial.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (ModelEnricher.write_clusters), a partir de src/modeling/clustering.py (AutoClusterHPO)</t>
+          <t>src/features/gold/model_enricher.py (ModelEnricher.write_discourse_topics)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/{produzir,comparar_clusters,resumo_funil}.py (ADR 0021; análise de clusters de reels em Comparar perfis, issue #189)</t>
+          <t>dashboard/screens/{produzir,discurso_reacao}.py (ADR 0021); src/features/gold/content_topic_priority_scorer.py (pauta de cada reel pela legenda)</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1607,17 +1607,17 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 2 / issue #87 (content_type); issue #152 (tabela separada de governor_clusters_posts)</t>
+          <t>ADR 0020 Ficha 4 / issue #89; issue #186 (refino Gemini do discurso)</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Cluster de engajamento/duração por reel (PCA -&gt; KMeans/DBSCAN/Agglomerative via AutoClusterHPO, algoritmo eleito por score CVI combinado).</t>
+          <t>Tópicos do que a ASSESSORIA publica (legenda de post/reel + transcrição de fala) -- BERTopic próprio, não misturado ao de comentário. Cada tópico de legenda é uma PAUTA (assunto do conteúdo) na fila de "O que produzir".</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>`cluster_label = -1` é ruído do DBSCAN, não um cluster de negócio (ver seção 2.2 do README) -- nunca a mesma coisa que clusterização de PERFIL (governor_profile_clusters_engagement, tabela separada). Antes da issue #152, coexistia com os posts de feed numa única tabela `governor_clusters` discriminada por `content_type` -- separada porque `posts_clean`/`reels_clean` (Silver) se sobrepõem (mesmo Reel capturado por dois actors Apify distintos), o que duplicava posts sob os dois `content_type`.</t>
+          <t>Conceitualmente distinta de governor_sentiment: fala da assessoria (aqui) vs. reação do público (lá). Nunca comparar os `Topic`/`Name` das duas tabelas como se fossem o mesmo espaço de tópicos. RÓTULOS REFINADOS (issue #186): `Name` sai do modelo determinístico como `&lt;id&gt;_kw1_kw2...` (ou `1____` quando o tópico não tem palavra alguma); o refino manual (`scripts/refine_topics.py --target all|discourse`, fora do pipeline automático) troca por `&lt;id&gt;_&lt;rótulo legível&gt;_&lt;kw...&gt;`. O tópico de ruído (`-1`) nunca é refinado e mantém o `Name` que já tinha; o tópico degenerado (sem palavra alguma) recebe o rótulo fixo "sem assunto definido" em vez de um nome inventado. O refino escreve nesta MESMA tabela (overwrite) e recalcula `content_topic_priority_score`. Enquanto o refino real não for rodado, os rótulos são os provisórios do estágio determinístico.</t>
         </is>
       </c>
     </row>
@@ -1629,17 +1629,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters_posts</t>
+          <t>governor_clusters_reels</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_clusters_posts</t>
+          <t>data/gold/governor_clusters_reels</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por post de feed -- clusterização de CONTEÚDO, não de perfil.</t>
+          <t>Uma linha por Reel -- clusterização de CONTEÚDO, não de perfil.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Nenhum consumidor de produção hoje (Tela de "Padrões de conteúdo" do feed ainda não existe no dashboard atual, ADR 0021).</t>
+          <t>dashboard/screens/{produzir,comparar_clusters,resumo_funil}.py (ADR 0021; análise de clusters de reels em Comparar perfis, issue #189)</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1664,17 +1664,17 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 2 / issue #87 (content_type); issue #152 (tabela separada de governor_clusters_reels)</t>
+          <t>ADR 0020 Ficha 2 / issue #87 (content_type); issue #152 (tabela separada de governor_clusters_posts)</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Cluster de engajamento por post de feed (PCA -&gt; KMeans/DBSCAN/Agglomerative via AutoClusterHPO, algoritmo eleito por score CVI combinado).</t>
+          <t>Cluster de engajamento/duração por reel (PCA -&gt; KMeans/DBSCAN/Agglomerative via AutoClusterHPO, algoritmo eleito por score CVI combinado).</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Mesmo schema de `governor_clusters_reels` (`content_type` constante = 'feed' dentro desta tabela) -- separada por causa da mesma sobreposição Silver descrita lá.</t>
+          <t>`cluster_label = -1` é ruído do DBSCAN, não um cluster de negócio (ver seção 2.2 do README) -- nunca a mesma coisa que clusterização de PERFIL (governor_profile_clusters_engagement, tabela separada). Antes da issue #152, coexistia com os posts de feed numa única tabela `governor_clusters` discriminada por `content_type` -- separada porque `posts_clean`/`reels_clean` (Silver) se sobrepõem (mesmo Reel capturado por dois actors Apify distintos), o que duplicava posts sob os dois `content_type`.</t>
         </is>
       </c>
     </row>
@@ -1686,17 +1686,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>governor_profile_clusters_engagement</t>
+          <t>governor_clusters_posts</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_profile_clusters_engagement</t>
+          <t>data/gold/governor_clusters_posts</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por GOVERNADOR (não por post) -- clusterização de PERFIL por padrão de engajamento.</t>
+          <t>Uma linha por post de feed -- clusterização de CONTEÚDO, não de perfil.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (ModelEnricher.write_profile_clusters_engagement), via src/modeling/orchestration.py::run_deterministic_modeling (pipeline.py --run-modeling / scripts/run_modeling.py) ou, isoladamente, via scripts/run_profile_clustering_engagement.py</t>
+          <t>src/features/gold/model_enricher.py (ModelEnricher.write_clusters), a partir de src/modeling/clustering.py (AutoClusterHPO)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/comparar.py (Tela 4 "Comparar perfis", ADR 0021 -- comparação de perfil vs. pares do mesmo cluster)</t>
+          <t>Nenhum consumidor de produção hoje (Tela de "Padrões de conteúdo" do feed ainda não existe no dashboard atual, ADR 0021).</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Fase 2 / issue #86; ADR 0004/0005 (schema próprio, não genérico)</t>
+          <t>ADR 0020 Ficha 2 / issue #87 (content_type); issue #152 (tabela separada de governor_clusters_reels)</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Agrupa governadores por semelhança de padrão de engajamento (mesma pipeline PCA-&gt;AutoClusterHPO do nível de conteúdo, mas features agregadas por perfil).</t>
+          <t>Cluster de engajamento por post de feed (PCA -&gt; KMeans/DBSCAN/Agglomerative via AutoClusterHPO, algoritmo eleito por score CVI combinado).</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Roda pós-Gold-de-engajamento (lê governor_engagement), dentro do mesmo estágio determinístico das demais tabelas de modelagem -- na Lambda serverless, é a etapa `model`, disparada depois de `load` (ver seção 3 do README). LIMITAÇÃO CORRIGIDA (2026-09-19): herdava o vazamento de governor_engagement (ver notas daquela tabela) -- agora que profiles_clean/posts_clean/reels_clean filtram contra governadores.xlsx atual, um governador removido nunca chega a ter governor_engagement calculado, então também não aparece mais aqui nem como 'par' na Tela 4 (Comparar perfis).</t>
+          <t>Mesmo schema de `governor_clusters_reels` (`content_type` constante = 'feed' dentro desta tabela) -- separada por causa da mesma sobreposição Silver descrita lá.</t>
         </is>
       </c>
     </row>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>post_performance_coefficients</t>
+          <t>governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>data/gold/post_performance_coefficients</t>
+          <t>data/gold/governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por preditor por grupo (vídeo/estático) por execução -- formato longo.</t>
+          <t>Uma linha por GOVERNADOR (não por post) -- clusterização de PERFIL por padrão de engajamento.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (write_post_performance_coefficients), a partir de src/modeling/post_performance.py (LassoCV)</t>
+          <t>src/features/gold/model_enricher.py (ModelEnricher.write_profile_clusters_engagement), via src/modeling/orchestration.py::run_deterministic_modeling (pipeline.py --run-modeling / scripts/run_modeling.py) ou, isoladamente, via scripts/run_profile_clustering_engagement.py</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Nenhum consumidor de produção hoje -- antigo consumidor (pages/03_performance.py, comparação entre governadores/coeficientes da regressão) era órfão desde a ADR 0021 e foi removido do repositório (cleanup pós-auditoria do dashboard, 2026-10)</t>
+          <t>dashboard/screens/comparar.py (Tela 4 "Comparar perfis", ADR 0021 -- comparação de perfil vs. pares do mesmo cluster)</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1778,17 +1778,17 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>ADR 0019 parte C</t>
+          <t>ADR 0020 Fase 2 / issue #86; ADR 0004/0005 (schema próprio, não genérico)</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Coeficientes e R² (treino/holdout) da regressão Lasso que explica performance-por-post, separada em grupo vídeo (Reels) e estático (posts de imagem/carrossel) por terem preditores distintos (ex.: duração de vídeo só existe no grupo vídeo).</t>
+          <t>Agrupa governadores por semelhança de padrão de engajamento (mesma pipeline PCA-&gt;AutoClusterHPO do nível de conteúdo, mas features agregadas por perfil).</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>`preditor` inclui, entre outros: hora_do_dia, dia_da_semana, tem_duracao, videoDuration (grupo vídeo), comprimento_legenda e Tema/Topic do BERTopic sobre legenda (grupo estático), paidPartnership (grupo vídeo). `r2_holdout` é nulo só no caso degenerado de um grupo sem governador em holdout.</t>
+          <t>Roda pós-Gold-de-engajamento (lê governor_engagement), dentro do mesmo estágio determinístico das demais tabelas de modelagem -- na Lambda serverless, é a etapa `model`, disparada depois de `load` (ver seção 3 do README). LIMITAÇÃO CORRIGIDA (2026-09-19): herdava o vazamento de governor_engagement (ver notas daquela tabela) -- agora que profiles_clean/posts_clean/reels_clean filtram contra governadores.xlsx atual, um governador removido nunca chega a ter governor_engagement calculado, então também não aparece mais aqui nem como 'par' na Tela 4 (Comparar perfis).</t>
         </is>
       </c>
     </row>
@@ -1800,17 +1800,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>post_performance_predictions</t>
+          <t>post_performance_coefficients</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>data/gold/post_performance_predictions</t>
+          <t>data/gold/post_performance_coefficients</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por post individual (treino + holdout juntos, discriminados implicitamente pelo pipeline que os gerou).</t>
+          <t>Uma linha por preditor por grupo (vídeo/estático) por execução -- formato longo.</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (write_post_performance_predictions)</t>
+          <t>src/features/gold/model_enricher.py (write_post_performance_coefficients), a partir de src/modeling/post_performance.py (LassoCV)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Nenhum consumidor de produção hoje -- antigo consumidor (pages/03_performance.py, dispersão previsto vs. real/resíduos) era órfão desde a ADR 0021 e foi removido do repositório (cleanup pós-auditoria do dashboard, 2026-10)</t>
+          <t>Nenhum consumidor de produção hoje -- antigo consumidor (pages/03_performance.py, comparação entre governadores/coeficientes da regressão) era órfão desde a ADR 0021 e foi removido do repositório (cleanup pós-auditoria do dashboard, 2026-10)</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>ADR 0019 parte C, decisão 9</t>
+          <t>ADR 0019 parte C</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Y real, Y previsto e resíduo por post -- Y = (likesCount + commentsCount × _WC_COMENTARIO) / followersCount, a mesma lógica de taxa ponderada de governor_engagement.% ENGAJAMENTO, mas por post em vez de agregada por perfil.</t>
+          <t>Coeficientes e R² (treino/holdout) da regressão Lasso que explica performance-por-post, separada em grupo vídeo (Reels) e estático (posts de imagem/carrossel) por terem preditores distintos (ex.: duração de vídeo só existe no grupo vídeo).</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Habilita a 'lacuna de execução' do dashboard (issue E da ADR 0019) sem precisar de uma tabela extra só para holdout.</t>
+          <t>`preditor` inclui, entre outros: hora_do_dia, dia_da_semana, tem_duracao, videoDuration (grupo vídeo), comprimento_legenda e Tema/Topic do BERTopic sobre legenda (grupo estático), paidPartnership (grupo vídeo). `r2_holdout` é nulo só no caso degenerado de um grupo sem governador em holdout.</t>
         </is>
       </c>
     </row>
@@ -1857,17 +1857,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>topic_priority_score</t>
+          <t>post_performance_predictions</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>data/gold/topic_priority_score</t>
+          <t>data/gold/post_performance_predictions</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por tópico de COMENTÁRIO (ranking global, não por governador).</t>
+          <t>Uma linha por post individual (treino + holdout juntos, discriminados implicitamente pelo pipeline que os gerou).</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/topic_priority_scorer.py (TopicPriorityScorer)</t>
+          <t>src/features/gold/model_enricher.py (write_post_performance_predictions)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/radar.py (tópicos de comentário em alerta). Desde a issue #191 a fila de "O que produzir" lê `content_topic_priority_score` (pautas), não esta tabela</t>
+          <t>Nenhum consumidor de produção hoje -- antigo consumidor (pages/03_performance.py, dispersão previsto vs. real/resíduos) era órfão desde a ADR 0021 e foi removido do repositório (cleanup pós-auditoria do dashboard, 2026-10)</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 6 / issue #91</t>
+          <t>ADR 0019 parte C, decisão 9</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Score ICE (Impacto x Confiança x Facilidade) de priorização de tópicos de COMENTÁRIO (grupos de comentários) -- não confundir com `content_topic_priority_score`, o ICE por PAUTA (assunto do conteúdo) que alimenta a fila de "O que produzir".</t>
+          <t>Y real, Y previsto e resíduo por post -- Y = (likesCount + commentsCount × _WC_COMENTARIO) / followersCount, a mesma lógica de taxa ponderada de governor_engagement.% ENGAJAMENTO, mas por post em vez de agregada por perfil.</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>'Facilidade' é fixa em 1.0 nesta v1 (FACILIDADE_V1) -- não há dado de custo de produção real para calibrar, decisão deliberada em vez de inventar uma heurística sem lastro. 'alcance_topico' é proxy (likes+replies do comentário), não alcance/views real.</t>
+          <t>Habilita a 'lacuna de execução' do dashboard (issue E da ADR 0019) sem precisar de uma tabela extra só para holdout.</t>
         </is>
       </c>
     </row>
@@ -1914,17 +1914,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm</t>
+          <t>topic_priority_score</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_nsm</t>
+          <t>data/gold/topic_priority_score</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por perfil de governador.</t>
+          <t>Uma linha por tópico de COMENTÁRIO (ranking global, não por governador).</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1934,32 +1934,32 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/nsm_scorer.py (NsmScorer)</t>
+          <t>src/features/gold/topic_priority_scorer.py (TopicPriorityScorer)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/resumo_nsm.py (Resumo, sub-aba NSM, ADR 0031 / issue #187)</t>
+          <t>dashboard/screens/radar.py (tópicos de comentário em alerta). Desde a issue #191 a fila de "O que produzir" lê `content_topic_priority_score` (pautas), não esta tabela</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Produção -- verificado com dado real dos 27 perfis (ver notas)</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 5 / issue #90</t>
+          <t>ADR 0020 Ficha 6 / issue #91</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>North Star Metric: (comentários positivos / comentários totais) × alcance médio -- engajamento qualificado por QUALIDADE de reação, não só volume.</t>
+          <t>Score ICE (Impacto x Confiança x Facilidade) de priorização de tópicos de COMENTÁRIO (grupos de comentários) -- não confundir com `content_topic_priority_score`, o ICE por PAUTA (assunto do conteúdo) que alimenta a fila de "O que produzir".</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>'alcance_medio' é proxy (TOTAL ENGAJAMENTO / count de governor_engagement), não alcance/views real -- Instagram não expõe alcance real para posts estáticos. Critério de aceite da issue #90 (ranking NSM inverter o ranking por engajamento bruto em pelo menos 1 caso real) confirmado em 2026-09-19 contra os 27 perfis reais: 25 dos 27 mudam de posição entre os dois rankings, inclusive o 1º lugar (tarcisiogdf ultrapassa romeuzemaoficial). Ver ADR 0020, Ficha 5, para o detalhe completo.</t>
+          <t>'Facilidade' é fixa em 1.0 nesta v1 (FACILIDADE_V1) -- não há dado de custo de produção real para calibrar, decisão deliberada em vez de inventar uma heurística sem lastro. 'alcance_topico' é proxy (likes+replies do comentário), não alcance/views real.</t>
         </is>
       </c>
     </row>
@@ -1971,52 +1971,52 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_nsm</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_nsm_history</t>
+          <t>data/gold/governor_nsm</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por perfil POR EXECUÇÃO do pipeline (mesmo schema de governor_nsm, mas em modo append) -- histórico acumulado ao longo do tempo.</t>
+          <t>Uma linha por perfil de governador.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>append</t>
+          <t>overwrite</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/nsm_scorer.py (mesmo NsmScorer, path diferente)</t>
+          <t>src/features/gold/nsm_scorer.py (NsmScorer)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>dashboard/core/data.py::load_nsm_history() -&gt; dashboard/screens/resumo_nsm.py (Resumo, sub-aba NSM, delta "vs. média histórica" do KPI Engajamento qualificado)</t>
+          <t>dashboard/screens/resumo_nsm.py (Resumo, sub-aba NSM, ADR 0031 / issue #187)</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Produção -- fecha lacuna que a ADR 0025 previu e adiou (ADR 0027 / issue #160)</t>
+          <t>Produção -- verificado com dado real dos 27 perfis (ver notas)</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 5 / ADR 0025 / ADR 0027 / issue #90 / issue #160</t>
+          <t>ADR 0020 Ficha 5 / issue #90</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Base de série temporal de NSM -- permite comparar o NSM da execução mais recente contra a média histórica de execuções anteriores, mesmo raciocínio de governor_engagement_history (ADR 0016).</t>
+          <t>North Star Metric: (comentários positivos / comentários totais) × alcance médio -- engajamento qualificado por QUALIDADE de reação, não só volume.</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Nunca sobrescrita nem deduplicada por execução -- cresce indefinidamente; governor_nsm (sem sufixo) continua em overwrite para não quebrar consumidores existentes. Precisa de &gt;= 2 execuções acumuladas para o primeiro delta aparecer no dashboard (mesmo critério de compare_vs_historical_average já usado por % engajamento/Seguidores).</t>
+          <t>'alcance_medio' é proxy (TOTAL ENGAJAMENTO / count de governor_engagement), não alcance/views real -- Instagram não expõe alcance real para posts estáticos. Critério de aceite da issue #90 (ranking NSM inverter o ranking por engajamento bruto em pelo menos 1 caso real) confirmado em 2026-09-19 contra os 27 perfis reais: 25 dos 27 mudam de posição entre os dois rankings, inclusive o 1º lugar (tarcisiogdf ultrapassa romeuzemaoficial). Ver ADR 0020, Ficha 5, para o detalhe completo.</t>
         </is>
       </c>
     </row>
@@ -2028,52 +2028,52 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>config/settings.py::GOLD_UGC_MENTIONS (data/gold/governor_ugc_mentions)</t>
+          <t>data/gold/governor_nsm_history</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por post de UGC (grão fino -- agregação por governador é uma view em memória, não persistida).</t>
+          <t>Uma linha por perfil POR EXECUÇÃO do pipeline (mesmo schema de governor_nsm, mas em modo append) -- histórico acumulado ao longo do tempo.</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>overwrite</t>
+          <t>append</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/ugc_mentions_aggregator.py (GovernorUGCAggregator), chamado por scripts/run_ugc_mentions.py</t>
+          <t>src/features/gold/nsm_scorer.py (mesmo NsmScorer, path diferente)</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/resumo_funil.py (sub-aba Funil do Resumo) via dashboard/core/data.py::load_ugc_mentions: o estágio Engage·Criar mostra o número de posts de UGC orgânico de cada governador, com selo 'piloto' (ADR 0032, que revisa a proibição original da issue #114). Limitação: o piloto atual é uma amostra de teste que coletou no máximo 5 posts por governador (a tela esconde o comparativo do Engage enquanto o máximo for &lt;= 5).</t>
+          <t>dashboard/core/data.py::load_nsm_history() -&gt; dashboard/screens/resumo_nsm.py (Resumo, sub-aba NSM, delta "vs. média histórica" do KPI Engajamento qualificado)</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Produção -- mesma execução real de 2026-09-19 de Bronze/Silver ugc_mentions</t>
+          <t>Produção -- fecha lacuna que a ADR 0025 previu e adiou (ADR 0027 / issue #160)</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 8 / issue #93</t>
+          <t>ADR 0020 Ficha 5 / ADR 0025 / ADR 0027 / issue #90 / issue #160</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>UGC orgânico vs. publi paga por post, com `is_organic` derivado de `paidPartnership` -- separa apoio espontâneo de publi paga ANTES de qualquer agregação.</t>
+          <t>Base de série temporal de NSM -- permite comparar o NSM da execução mais recente contra a média histórica de execuções anteriores, mesmo raciocínio de governor_engagement_history (ADR 0016).</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>`GovernorUGCAggregator.aggregate_by_governor` (a 'view' de contagem/engajamento médio por governador) nunca expõe `authorUsername` individual no agregado, por desenho -- privacidade de quem menciona o governador, não só do próprio governador. Piloto real (2026-09-19) confirmou que `paidPartnership` é o único campo de publi que o actor expõe -- `isAd`/`isAffiliate` não existem como conceitos distintos, removidos do schema.</t>
+          <t>Nunca sobrescrita nem deduplicada por execução -- cresce indefinidamente; governor_nsm (sem sufixo) continua em overwrite para não quebrar consumidores existentes. Precisa de &gt;= 2 execuções acumuladas para o primeiro delta aparecer no dashboard (mesmo critério de compare_vs_historical_average já usado por % engajamento/Seguidores).</t>
         </is>
       </c>
     </row>
@@ -2085,17 +2085,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_growth_metrics</t>
+          <t>config/settings.py::GOLD_UGC_MENTIONS (data/gold/governor_ugc_mentions)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por perfil de governador -- snapshot recalculável a partir do histórico acumulado (sempre overwrite, nunca append).</t>
+          <t>Uma linha por post de UGC (grão fino -- agregação por governador é uma view em memória, não persistida).</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2105,32 +2105,32 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (write_growth_metrics), via scripts/run_growth_metrics.py e src/modeling/growth_history.py</t>
+          <t>src/features/gold/ugc_mentions_aggregator.py (GovernorUGCAggregator), chamado por pipeline.py (estágio Gold, issue #211)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/resumo_nsm.py (KPIs de crescimento CMGR e retenção, Resumo sub-aba NSM) via dashboard/core/data.py::load_growth_metrics()</t>
+          <t>dashboard/screens/resumo_funil.py (sub-aba Funil do Resumo) via dashboard/core/data.py::load_ugc_mentions: o estágio Engage·Criar mostra o número de posts de UGC orgânico de cada governador, com selo 'piloto' (ADR 0032, que revisa a proibição original da issue #114). Com o teto padrão do pipeline.py (30 por coleção, issue #211) a contagem deixa de saturar no teto do piloto (5) e o comparativo do Engage passa a aparecer (a tela o esconde enquanto o máximo for &lt;= 5).</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>PRODUÇÃO, mas resultado marcado ILUSTRATIVO (ver notas) -- não sustenta conclusão definitiva ainda</t>
+          <t>Produção -- mesma execução real de 2026-09-19 de Bronze/Silver ugc_mentions</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 7 / issue #92</t>
+          <t>ADR 0020 Ficha 8 / issue #93</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>CMGR (crescimento mensal composto de seguidores) e retenção de sentimento positivo, calculados sobre governor_engagement_history/governor_sentiment_history.</t>
+          <t>UGC orgânico vs. publi paga por post, com `is_organic` derivado de `paidPartnership` -- separa apoio espontâneo de publi paga ANTES de qualquer agregação.</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>`cmgr_confiavel`/`retencao_confiavel` são False sempre que houver menos de MIN_PERIODS_CONFIAVEL=6 execuções mensais acumuladas -- em 2026-09 o pipeline ainda não acumulou histórico suficiente, então os valores validam a FÓRMULA, não sustentam conclusão real sobre crescimento dos perfis. `motivo`/`nota` explicam o porquê sempre que o valor for NaN ou não confiável.</t>
+          <t>`GovernorUGCAggregator.aggregate_by_governor` (a 'view' de contagem/engajamento médio por governador) nunca expõe `authorUsername` individual no agregado, por desenho -- privacidade de quem menciona o governador, não só do próprio governador. Piloto real (2026-09-19) confirmou que `paidPartnership` é o único campo de publi que o actor expõe -- `isAd`/`isAffiliate` não existem como conceitos distintos, removidos do schema.</t>
         </is>
       </c>
     </row>
@@ -2142,17 +2142,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_scorecard</t>
+          <t>data/gold/governor_growth_metrics</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por governador (um perfil por `inputUrl` normalizado) -- snapshot recalculável a partir da Silver/Gold atual, sempre overwrite.</t>
+          <t>Uma linha por perfil de governador -- snapshot recalculável a partir do histórico acumulado (sempre overwrite, nunca append).</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2162,32 +2162,32 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/governor_scorecard.py (GovernorScorecardScorer), via src/modeling/orchestration.py::run_deterministic_modeling (pipeline.py --run-modeling / scripts/run_modeling.py) ou, isoladamente, scripts/run_governor_scorecard.py</t>
+          <t>src/features/gold/model_enricher.py (write_growth_metrics), via scripts/run_growth_metrics.py e src/modeling/growth_history.py</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/resumo_scorecard.py (Resumo, sub-aba Scorecard) via dashboard/core/data.py::load_governor_scorecard() -- o dashboard só lê, nada é recalculado</t>
+          <t>dashboard/screens/resumo_nsm.py (KPIs de crescimento CMGR e retenção, Resumo sub-aba NSM) via dashboard/core/data.py::load_growth_metrics()</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Produção -- com selo de confiabilidade: dimensão Consistência pendente nos 26 governadores no dado de 2026-10-04 (ver notas)</t>
+          <t>PRODUÇÃO, mas resultado marcado ILUSTRATIVO (ver notas) -- não sustenta conclusão definitiva ainda</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>ADR 0030 / issue #184 (spec #182)</t>
+          <t>ADR 0020 Ficha 7 / issue #92</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Escore composto (0 a 100) dos governadores: soma ponderada de cinco dimensões normalizadas min-máx entre os perfis (Alcance, Ativação, Qualidade, Profundidade, Consistência), seguindo a lógica de indicadores compostos do OECD Handbook (indicador bruto -&gt; normalização -&gt; ponderação -&gt; agregação). Relativo ao grupo: mede posição entre pares, não desempenho absoluto.</t>
+          <t>CMGR (crescimento mensal composto de seguidores) e retenção de sentimento positivo, calculados sobre governor_engagement_history/governor_sentiment_history.</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>SELOS DE CONFIABILIDADE. (1) Alcance é medido em REPRODUÇÕES (plays: `videoPlayCount` dos reels), nunca em "visualizações únicas"; posts de feed não têm plays, então só reels entram em Alcance e Profundidade. (2) Consistência mede a TENDÊNCIA do engajamento médio por post por mês de publicação (CMGR de engajamento), NÃO crescimento de audiência -- o CMGR de audiência (seguidores entre coletas, `governor_growth_metrics.cmgr`) continua pendente e fora do escore. (3) Consistência exige &gt;= 4 meses completos com &gt;= 3 posts maduros (&gt;= 7 dias de vida); no dado de 2026-10-04 a Silver só tem ~226 posts de ago/set-2026 e NENHUM dos 26 governadores atinge isso, então `consistencia_pendente = True` e `consistencia`/`consistencia_norm` são nulas em todos: o escore usa as 4 dimensões restantes com peso 0,25 cada (com as 5, 0,20 cada) e `n_dimensoes = 4`. Isso muda sozinho conforme a Silver acumular histórico. (4) Perfil com menos de 4 dimensões disponíveis fica com `escore` e `ranking` nulos. (5) São 26 governadores (a Silver filtra governadores removidos de governadores.xlsx), não 27. Amplitude zero numa dimensão (todos iguais) normaliza para 50.</t>
+          <t>`cmgr_confiavel`/`retencao_confiavel` são False sempre que houver menos de MIN_PERIODS_CONFIAVEL=6 execuções mensais acumuladas -- em 2026-09 o pipeline ainda não acumulou histórico suficiente, então os valores validam a FÓRMULA, não sustentam conclusão real sobre crescimento dos perfis. `motivo`/`nota` explicam o porquê sempre que o valor for NaN ou não confiável.</t>
         </is>
       </c>
     </row>
@@ -2199,57 +2199,114 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
+          <t>governor_scorecard</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>data/gold/governor_scorecard</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Uma linha por governador (um perfil por `inputUrl` normalizado) -- snapshot recalculável a partir da Silver/Gold atual, sempre overwrite.</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>overwrite</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>src/modeling/governor_scorecard.py (GovernorScorecardScorer), via src/modeling/orchestration.py::run_deterministic_modeling (pipeline.py --run-modeling / scripts/run_modeling.py) ou, isoladamente, scripts/run_governor_scorecard.py</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>dashboard/screens/resumo_scorecard.py (Resumo, sub-aba Scorecard) via dashboard/core/data.py::load_governor_scorecard() -- o dashboard só lê, nada é recalculado</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Produção -- com selo de confiabilidade: dimensão Consistência pendente nos 26 governadores no dado de 2026-10-04 (ver notas)</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>ADR 0030 / issue #184 (spec #182)</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Escore composto (0 a 100) dos governadores: soma ponderada de cinco dimensões normalizadas min-máx entre os perfis (Alcance, Ativação, Qualidade, Profundidade, Consistência), seguindo a lógica de indicadores compostos do OECD Handbook (indicador bruto -&gt; normalização -&gt; ponderação -&gt; agregação). Relativo ao grupo: mede posição entre pares, não desempenho absoluto.</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>SELOS DE CONFIABILIDADE. (1) Alcance é medido em REPRODUÇÕES (plays: `videoPlayCount` dos reels), nunca em "visualizações únicas"; posts de feed não têm plays, então só reels entram em Alcance e Profundidade. (2) Consistência mede a TENDÊNCIA do engajamento médio por post por mês de publicação (CMGR de engajamento), NÃO crescimento de audiência -- o CMGR de audiência (seguidores entre coletas, `governor_growth_metrics.cmgr`) continua pendente e fora do escore. (3) Consistência exige &gt;= 4 meses completos com &gt;= 3 posts maduros (&gt;= 7 dias de vida); no dado de 2026-10-04 a Silver só tem ~226 posts de ago/set-2026 e NENHUM dos 26 governadores atinge isso, então `consistencia_pendente = True` e `consistencia`/`consistencia_norm` são nulas em todos: o escore usa as 4 dimensões restantes com peso 0,25 cada (com as 5, 0,20 cada) e `n_dimensoes = 4`. Isso muda sozinho conforme a Silver acumular histórico. (4) Perfil com menos de 4 dimensões disponíveis fica com `escore` e `ranking` nulos. (5) São 26 governadores (a Silver filtra governadores removidos de governadores.xlsx), não 27. Amplitude zero numa dimensão (todos iguais) normaliza para 50.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
           <t>content_topic_priority_score</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>data/gold/content_topic_priority_score</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Uma linha por PAUTA (tópico de discurso da legenda do reel) -- ranking global, todos os perfis combinados, não por governador.</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>overwrite</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>src/features/gold/content_topic_priority_scorer.py (ContentTopicPriorityScorer), via src/modeling/orchestration.py::run_deterministic_modeling (provisório, rótulos brutos) e refine_discourse_topics_with_gemini (recalculado com os rótulos refinados)</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>dashboard/screens/produzir.py (fila de pautas de "O que produzir") via dashboard/core/data.py::load_content_topic_priority()</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Produção -- com selo de confiabilidade: rótulos de pauta ainda provisórios até o refino manual via Gemini ser rodado de verdade (ver notas)</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>ADR 0020 Ficha 6 (fórmula); ADR 0028; issue #190 / #191 (spec #182)</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>Score ICE (Impacto x Confiança x Facilidade) por PAUTA: sobre qual assunto de conteúdo o público reagiu bem. Pauta = tópico de discurso da LEGENDA do reel; os comentários são ligados à pauta pelo reel (`id_reel`).</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>Cada reel pertence a uma única pauta (a da legenda; `governor_discourse_topics` tem reels duplicados, deduplicados por `id_reel`); comentários de reels sem pauta de legenda ficam de fora; o tópico de ruído (-1) não é pauta; a transcrição não define pauta (exige plano pago do coletor). `alcance_pauta` é PROXY por engajamento (soma de likesCount + repliesCount dos comentários), nunca "visualizações". `facilidade` fixa em 1,0 (v1, sem dado de custo de produção). O selo de prioridade do dashboard (Alta/Média/Cuidado) vem dos tercis de `score` sobre o ranking global de pautas; o score bruto nunca é exibido. SELO DE CONFIABILIDADE: o refino real dos rótulos via Gemini ainda não foi rodado -- até lá `Name` traz os rótulos provisórios do BERTopic (palavras-chave) e o tópico sem palavra alguma aparece como "sem assunto definido". O ICE é recalculado quando o refino do discurso roda (`scripts/refine_topics.py --target all|discourse`).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K28"/>
+  <autoFilter ref="A1:K29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2260,7 +2317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3142,22 +3199,22 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>latestComments</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Lista bruta (JSON) dos comentários mais recentes do reel ou post, retornada pelo Apify -- fonte de comments_clean (reels) e de post_comments_clean (posts de feed, issue #212).</t>
         </is>
       </c>
     </row>
@@ -3169,12 +3226,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -3184,7 +3241,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3253,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>_source</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -3211,19 +3268,19 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>instagram_reels</t>
+          <t>instagram_posts</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>_source</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3233,12 +3290,12 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3307,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ownerId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3265,7 +3322,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3334,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>ownerId</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3292,7 +3349,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil que publicou o post/reel/comentário.</t>
+          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3361,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3319,7 +3376,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Username do perfil que publicou o post/reel/comentário.</t>
         </is>
       </c>
     </row>
@@ -3331,12 +3388,12 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -3346,7 +3403,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3415,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3373,7 +3430,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3442,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>videoViewCount</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3400,7 +3457,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Número de views do vídeo (métrica bruta do Apify, distinta de videoPlayCount).</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3469,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>videoViewCount</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3427,7 +3484,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
+          <t>Número de views do vídeo (métrica bruta do Apify, distinta de videoPlayCount).</t>
         </is>
       </c>
     </row>
@@ -3439,12 +3496,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>videoDuration</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -3454,7 +3511,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Duração do vídeo em segundos.</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3523,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>videoDuration</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -3481,7 +3538,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
+          <t>Duração do vídeo em segundos.</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3550,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3508,7 +3565,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
+          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3577,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3535,7 +3592,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
         </is>
       </c>
     </row>
@@ -3547,12 +3604,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>isSponsored</t>
+          <t>shortCode</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -3562,7 +3619,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Flag de conteúdo patrocinado no Reel (bruto do Apify).</t>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3631,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>isCommentsDisabled</t>
+          <t>isSponsored</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3589,7 +3646,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Se os comentários estão desabilitados no post/reel.</t>
+          <t>Flag de conteúdo patrocinado no Reel (bruto do Apify).</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3658,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>isPinned</t>
+          <t>isCommentsDisabled</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3616,7 +3673,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Se o reel está fixado no perfil.</t>
+          <t>Se os comentários estão desabilitados no post/reel.</t>
         </is>
       </c>
     </row>
@@ -3628,12 +3685,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>latestComments</t>
+          <t>isPinned</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -3643,7 +3700,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Lista bruta (JSON) dos comentários mais recentes do reel, retornada pelo Apify -- fonte de comments_clean.</t>
+          <t>Se o reel está fixado no perfil.</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3712,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>transcript</t>
+          <t>latestComments</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -3670,7 +3727,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Transcrição de fala do reel, via flag paga includeTranscript do actor -- nullable (vídeo mudo/flag desligada).</t>
+          <t>Lista bruta (JSON) dos comentários mais recentes do reel ou post, retornada pelo Apify -- fonte de comments_clean (reels) e de post_comments_clean (posts de feed, issue #212).</t>
         </is>
       </c>
     </row>
@@ -3682,22 +3739,22 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>transcript</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Transcrição de fala do reel, via flag paga includeTranscript do actor -- nullable (vídeo mudo/flag desligada).</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3766,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -3724,7 +3781,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3793,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>_source</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3751,19 +3808,19 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>instagram_reels</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>_source</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -3773,12 +3830,12 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3847,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3805,7 +3862,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3874,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>shortCode</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3832,7 +3889,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3901,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>caption</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3859,7 +3916,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Legenda/texto do post ou reel.</t>
+          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3928,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>mentions</t>
+          <t>caption</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3886,7 +3943,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Lista de usernames @-mencionados em legenda/comentário do post de UGC, serializada como JSON string -- só ~31% dos posts reais têm este campo preenchido.</t>
+          <t>Legenda/texto do post ou reel.</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3955,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>taggedUsers</t>
+          <t>mentions</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3913,7 +3970,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Lista de objetos (um por pessoa marcada visualmente na foto/vídeo, com `username`/`full_name`/`is_verified`/`is_private`) do post de UGC, serializada como JSON string -- substitui o campo `matchTypes` (não existe no actor real); presente em ~69% dos posts, mais frequente que `mentions`.</t>
+          <t>Lista de usernames @-mencionados em legenda/comentário do post de UGC, serializada como JSON string -- só ~31% dos posts reais têm este campo preenchido.</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3982,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>taggedUsers</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -3940,7 +3997,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Lista de objetos (um por pessoa marcada visualmente na foto/vídeo, com `username`/`full_name`/`is_verified`/`is_private`) do post de UGC, serializada como JSON string -- substitui o campo `matchTypes` (não existe no actor real); presente em ~69% dos posts, mais frequente que `mentions`.</t>
         </is>
       </c>
     </row>
@@ -3952,7 +4009,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -3967,7 +4024,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -3979,7 +4036,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -3994,7 +4051,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
@@ -4006,12 +4063,12 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -4021,7 +4078,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4090,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -4048,7 +4105,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Username de quem publicou o post de UGC (autor terceiro que marcou/mencionou o governador -- Bronze, nome real do actor apify/instagram-tagged-scraper). Normalizado para `authorUsername` na Silver.</t>
+          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4117,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>ownerFullName</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -4075,7 +4132,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Nome completo de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
+          <t>Username de quem publicou o post de UGC (autor terceiro que marcou/mencionou o governador -- Bronze, nome real do actor apify/instagram-tagged-scraper). Normalizado para `authorUsername` na Silver.</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4144,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>ownerId</t>
+          <t>ownerFullName</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -4102,7 +4159,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil de quem publicou o post de UGC (autor terceiro, Bronze, confirmado pelo piloto real) -- distinto do `ownerId` de posts/reels, que é o próprio governador.</t>
+          <t>Nome completo de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
         </is>
       </c>
     </row>
@@ -4114,12 +4171,12 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>paidPartnership</t>
+          <t>ownerId</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -4129,7 +4186,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Flag de parceria paga (publi) declarada pelo Instagram no post de UGC -- único campo de publi que o actor real expõe (piloto 2026-09-19); `isAd`/`isAffiliate` da especificação original não existem.</t>
+          <t>Id do perfil de quem publicou o post de UGC (autor terceiro, Bronze, confirmado pelo piloto real) -- distinto do `ownerId` de posts/reels, que é o próprio governador.</t>
         </is>
       </c>
     </row>
@@ -4141,22 +4198,22 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>paidPartnership</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Flag de parceria paga (publi) declarada pelo Instagram no post de UGC -- único campo de publi que o actor real expõe (piloto 2026-09-19); `isAd`/`isAffiliate` da especificação original não existem.</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4225,12 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -4183,7 +4240,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
@@ -4195,27 +4252,54 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
+          <t>_run_id</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
           <t>_source</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E72"/>
+  <autoFilter ref="A1:E73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4226,7 +4310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5636,7 +5720,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Id do reel/post de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean.</t>
+          <t>Id da publicação (reel ou post) de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean; em governor_sentiment, comentários de posts (origem_comentario == 'post') também usam esta coluna.</t>
         </is>
       </c>
     </row>
@@ -5940,12 +6024,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>governors_metadata</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>id_post</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -5955,24 +6039,24 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Id do post de feed comentado (inclui reels capturados no grid de posts, issue #152) -- vira `id_reel` ao entrar em governor_sentiment.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>governors_metadata</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>nome</t>
+          <t>id_comment</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -5982,24 +6066,24 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Nome do governador (reference/governadores.xlsx, coluna 'Governador').</t>
+          <t>Id único do comentário individual (pós-explosão de latestComments).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>governors_metadata</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>uf</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -6014,127 +6098,127 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Unidade Federativa do governador (reference/governadores.xlsx, coluna 'Unidade Federativa').</t>
+          <t>Texto avaliado -- comentário, legenda ou transcrição, dependendo da tabela/coluna `fonte`.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>governors_metadata</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>partido</t>
+          <t>comprimento texto</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Partido do governador (reference/governadores.xlsx, coluna 'Partido').</t>
+          <t>Número de caracteres de `text` -- usado para filtrar comentários &gt;= 512 caracteres (CommentCleaner.MAX_TEXT_LENGTH).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>governors_metadata</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Username do perfil que publicou o post/reel/comentário.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>governors_metadata</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>governors_metadata</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>_source_layer</t>
+          <t>repliesCount</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
+          <t>Número de respostas a um comentário.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -6149,19 +6233,19 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -6176,46 +6260,46 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>caption</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -6225,24 +6309,24 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Legenda/texto do post ou reel.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>governor_username</t>
+          <t>_source_layer</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -6252,24 +6336,24 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
+          <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>governors_metadata</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>authorUsername</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -6279,29 +6363,29 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>governors_metadata</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>paidPartnership</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -6311,105 +6395,105 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Flag de parceria paga (publi) declarada pelo Instagram no post de UGC -- único campo de publi que o actor real expõe (piloto 2026-09-19); `isAd`/`isAffiliate` da especificação original não existem.</t>
+          <t>Nome do governador (reference/governadores.xlsx, coluna 'Governador').</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>governors_metadata</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>uf</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Unidade Federativa do governador (reference/governadores.xlsx, coluna 'Unidade Federativa').</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>governors_metadata</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>partido</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>Partido do governador (reference/governadores.xlsx, coluna 'Partido').</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>governors_metadata</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>governors_metadata</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -6419,24 +6503,24 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>governors_metadata</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>_source_layer</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -6446,7 +6530,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6542,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -6468,12 +6552,12 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
@@ -6485,27 +6569,351 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
+          <t>shortCode</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>caption</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Legenda/texto do post ou reel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>governor_username</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>authorUsername</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>paidPartnership</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>Flag de parceria paga (publi) declarada pelo Instagram no post de UGC -- único campo de publi que o actor real expõe (piloto 2026-09-19); `isAd`/`isAffiliate` da especificação original não existem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>likesCount</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Número de curtidas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>commentsCount</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Número de comentários.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>videoPlayCount</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>data_hora</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>timestamp[us]</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>_ingested_at</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>timestamp[us, tz=UTC]</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>_run_id</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
           <t>_source_layer</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E84"/>
+  <autoFilter ref="A1:E96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6516,7 +6924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E215"/>
+  <dimension ref="A1:E217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7602,7 +8010,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Id do reel/post de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean.</t>
+          <t>Id da publicação (reel ou post) de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean; em governor_sentiment, comentários de posts (origem_comentario == 'post') também usam esta coluna.</t>
         </is>
       </c>
     </row>
@@ -7830,7 +8238,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>sentiment_label</t>
+          <t>origem_comentario</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -7845,7 +8253,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Rótulo de sentimento previsto: positive / neutral / negative (cardiffnlp/twitter-xlm-roberta-base-sentiment).</t>
+          <t>Publicação em que o comentário foi feito: 'reel' (comments_clean) ou 'post' (post_comments_clean) -- só nas linhas fonte == 'comentario'; nula em legenda/transcrição (issue #212, ADR 0033). Não confundir com `fonte`.</t>
         </is>
       </c>
     </row>
@@ -7857,12 +8265,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>sentiment_score</t>
+          <t>sentiment_label</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -7872,7 +8280,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Confiança do classificador na label prevista (NÃO 'o quão positivo/negativo') -- src/modeling/sentiment.py.</t>
+          <t>Rótulo de sentimento previsto: positive / neutral / negative (cardiffnlp/twitter-xlm-roberta-base-sentiment).</t>
         </is>
       </c>
     </row>
@@ -7884,12 +8292,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>sentiment_score</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -7899,7 +8307,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Id numérico do tópico BERTopic (-1 = ruído/sem tópico atribuído).</t>
+          <t>Confiança do classificador na label prevista (NÃO 'o quão positivo/negativo') -- src/modeling/sentiment.py.</t>
         </is>
       </c>
     </row>
@@ -7911,12 +8319,12 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -7926,7 +8334,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Rótulo textual do tópico BERTopic -- determinístico (KeyBERTInspired) por padrão, ou refinado manualmente via Gemini (scripts/refine_topics.py).</t>
+          <t>Id numérico do tópico BERTopic (-1 = ruído/sem tópico atribuído).</t>
         </is>
       </c>
     </row>
@@ -7938,7 +8346,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -7948,12 +8356,12 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Rótulo textual do tópico BERTopic -- determinístico (KeyBERTInspired) por padrão, ou refinado manualmente via Gemini (scripts/refine_topics.py).</t>
         </is>
       </c>
     </row>
@@ -7965,12 +8373,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -7980,34 +8388,34 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>governor_sentiment_history</t>
+          <t>governor_sentiment</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>id_reel</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Id do reel/post de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8427,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>id_comment</t>
+          <t>id_reel</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -8034,7 +8442,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Id único do comentário individual (pós-explosão de latestComments).</t>
+          <t>Id da publicação (reel ou post) de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean; em governor_sentiment, comentários de posts (origem_comentario == 'post') também usam esta coluna.</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8454,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>id_comment</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -8061,7 +8469,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Texto avaliado -- comentário, legenda ou transcrição, dependendo da tabela/coluna `fonte`.</t>
+          <t>Id único do comentário individual (pós-explosão de latestComments).</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8481,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -8088,7 +8496,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Texto avaliado -- comentário, legenda ou transcrição, dependendo da tabela/coluna `fonte`.</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8508,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -8115,7 +8523,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil que publicou o post/reel/comentário.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8535,12 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -8142,7 +8550,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Username do perfil que publicou o post/reel/comentário.</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8562,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>repliesCount</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -8169,7 +8577,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Número de respostas a um comentário.</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -8181,12 +8589,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>repliesCount</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -8196,7 +8604,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
+          <t>Número de respostas a um comentário.</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8616,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>fonte</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -8218,12 +8626,12 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Granularidade da linha dentro da tabela: 'comentario', 'legenda' ou 'transcricao' -- ver ADR 0020 Ficha 3 / issue #88.</t>
+          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8643,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>sentiment_label</t>
+          <t>fonte</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -8245,12 +8653,12 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Rótulo de sentimento previsto: positive / neutral / negative (cardiffnlp/twitter-xlm-roberta-base-sentiment).</t>
+          <t>Granularidade da linha dentro da tabela: 'comentario', 'legenda' ou 'transcricao' -- ver ADR 0020 Ficha 3 / issue #88.</t>
         </is>
       </c>
     </row>
@@ -8262,12 +8670,12 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>sentiment_score</t>
+          <t>origem_comentario</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -8277,7 +8685,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Confiança do classificador na label prevista (NÃO 'o quão positivo/negativo') -- src/modeling/sentiment.py.</t>
+          <t>Publicação em que o comentário foi feito: 'reel' (comments_clean) ou 'post' (post_comments_clean) -- só nas linhas fonte == 'comentario'; nula em legenda/transcrição (issue #212, ADR 0033). Não confundir com `fonte`.</t>
         </is>
       </c>
     </row>
@@ -8289,12 +8697,12 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>sentiment_label</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -8304,7 +8712,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Id numérico do tópico BERTopic (-1 = ruído/sem tópico atribuído).</t>
+          <t>Rótulo de sentimento previsto: positive / neutral / negative (cardiffnlp/twitter-xlm-roberta-base-sentiment).</t>
         </is>
       </c>
     </row>
@@ -8316,12 +8724,12 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>sentiment_score</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -8331,7 +8739,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Rótulo textual do tópico BERTopic -- determinístico (KeyBERTInspired) por padrão, ou refinado manualmente via Gemini (scripts/refine_topics.py).</t>
+          <t>Confiança do classificador na label prevista (NÃO 'o quão positivo/negativo') -- src/modeling/sentiment.py.</t>
         </is>
       </c>
     </row>
@@ -8343,22 +8751,22 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Id numérico do tópico BERTopic (-1 = ruído/sem tópico atribuído).</t>
         </is>
       </c>
     </row>
@@ -8370,34 +8778,34 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Rótulo textual do tópico BERTopic -- determinístico (KeyBERTInspired) por padrão, ou refinado manualmente via Gemini (scripts/refine_topics.py).</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>governor_discourse_topics</t>
+          <t>governor_sentiment_history</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>id_reel</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -8407,39 +8815,39 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Id do reel/post de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>governor_discourse_topics</t>
+          <t>governor_sentiment_history</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Texto avaliado -- comentário, legenda ou transcrição, dependendo da tabela/coluna `fonte`.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8859,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>id_reel</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -8466,7 +8874,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Id da publicação (reel ou post) de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean; em governor_sentiment, comentários de posts (origem_comentario == 'post') também usam esta coluna.</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8886,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -8493,7 +8901,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil que publicou o post/reel/comentário.</t>
+          <t>Texto avaliado -- comentário, legenda ou transcrição, dependendo da tabela/coluna `fonte`.</t>
         </is>
       </c>
     </row>
@@ -8505,7 +8913,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -8520,7 +8928,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -8532,7 +8940,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>fonte</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -8542,12 +8950,12 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Granularidade da linha dentro da tabela: 'comentario', 'legenda' ou 'transcricao' -- ver ADR 0020 Ficha 3 / issue #88.</t>
+          <t>Username do perfil que publicou o post/reel/comentário.</t>
         </is>
       </c>
     </row>
@@ -8559,12 +8967,12 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -8574,7 +8982,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Id numérico do tópico BERTopic (-1 = ruído/sem tópico atribuído).</t>
+          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8994,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>fonte</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -8596,12 +9004,12 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Rótulo textual do tópico BERTopic -- determinístico (KeyBERTInspired) por padrão, ou refinado manualmente via Gemini (scripts/refine_topics.py).</t>
+          <t>Granularidade da linha dentro da tabela: 'comentario', 'legenda' ou 'transcricao' -- ver ADR 0020 Ficha 3 / issue #88.</t>
         </is>
       </c>
     </row>
@@ -8613,22 +9021,22 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Id numérico do tópico BERTopic (-1 = ruído/sem tópico atribuído).</t>
         </is>
       </c>
     </row>
@@ -8640,34 +9048,34 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Rótulo textual do tópico BERTopic -- determinístico (KeyBERTInspired) por padrão, ou refinado manualmente via Gemini (scripts/refine_topics.py).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters_reels</t>
+          <t>governor_discourse_topics</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>id_reel</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -8682,24 +9090,24 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Id do reel/post de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters_reels</t>
+          <t>governor_discourse_topics</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -8709,7 +9117,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil que publicou o post/reel/comentário.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -8721,12 +9129,12 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>cluster_label</t>
+          <t>id_reel</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -8736,7 +9144,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Rótulo do cluster atribuído pelo AutoClusterHPO (-1 = ruído do DBSCAN).</t>
+          <t>Id da publicação (reel ou post) de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean; em governor_sentiment, comentários de posts (origem_comentario == 'post') também usam esta coluna.</t>
         </is>
       </c>
     </row>
@@ -8748,7 +9156,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>cluster_algo</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -8763,7 +9171,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Nome do algoritmo eleito pelo AutoClusterHPO para esta execução (KMeans/DBSCAN/Agglomerative).</t>
+          <t>Username do perfil que publicou o post/reel/comentário.</t>
         </is>
       </c>
     </row>
@@ -8775,22 +9183,22 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>cluster_score</t>
+          <t>cluster_label</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Score CVI combinado (Silhouette + Calinski-Harabasz normalizado + Davies-Bouldin invertido) do algoritmo eleito -- ver src/modeling/clustering.py.</t>
+          <t>Rótulo do cluster atribuído pelo AutoClusterHPO (-1 = ruído do DBSCAN).</t>
         </is>
       </c>
     </row>
@@ -8802,7 +9210,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>content_type</t>
+          <t>cluster_algo</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -8817,7 +9225,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Valor constante por tabela ('reel' em governor_clusters_reels, 'feed' em governor_clusters_posts) -- mantido no schema das duas para permitir recombinação futura via pd.concat sem precisar re-derivar o rótulo (ADR 0020 Ficha 2 / issue #87; tabelas separadas desde a issue #152).</t>
+          <t>Nome do algoritmo eleito pelo AutoClusterHPO para esta execução (KMeans/DBSCAN/Agglomerative).</t>
         </is>
       </c>
     </row>
@@ -8829,22 +9237,22 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>cluster_score</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Score CVI combinado (Silhouette + Calinski-Harabasz normalizado + Davies-Bouldin invertido) do algoritmo eleito -- ver src/modeling/clustering.py.</t>
         </is>
       </c>
     </row>
@@ -8856,12 +9264,12 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>content_type</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -8871,19 +9279,19 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Valor constante por tabela ('reel' em governor_clusters_reels, 'feed' em governor_clusters_posts) -- mantido no schema das duas para permitir recombinação futura via pd.concat sem precisar re-derivar o rótulo (ADR 0020 Ficha 2 / issue #87; tabelas separadas desde a issue #152).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters_posts</t>
+          <t>governor_clusters_reels</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>id_reel</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -8898,24 +9306,24 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Id do reel/post de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>governor_clusters_posts</t>
+          <t>governor_clusters_reels</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -8925,7 +9333,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil que publicou o post/reel/comentário.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -8937,12 +9345,12 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>cluster_label</t>
+          <t>id_reel</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -8952,7 +9360,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Rótulo do cluster atribuído pelo AutoClusterHPO (-1 = ruído do DBSCAN).</t>
+          <t>Id da publicação (reel ou post) de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean; em governor_sentiment, comentários de posts (origem_comentario == 'post') também usam esta coluna.</t>
         </is>
       </c>
     </row>
@@ -8964,7 +9372,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>cluster_algo</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -8979,7 +9387,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Nome do algoritmo eleito pelo AutoClusterHPO para esta execução (KMeans/DBSCAN/Agglomerative).</t>
+          <t>Username do perfil que publicou o post/reel/comentário.</t>
         </is>
       </c>
     </row>
@@ -8991,22 +9399,22 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>cluster_score</t>
+          <t>cluster_label</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Score CVI combinado (Silhouette + Calinski-Harabasz normalizado + Davies-Bouldin invertido) do algoritmo eleito -- ver src/modeling/clustering.py.</t>
+          <t>Rótulo do cluster atribuído pelo AutoClusterHPO (-1 = ruído do DBSCAN).</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9426,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>content_type</t>
+          <t>cluster_algo</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -9033,7 +9441,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Valor constante por tabela ('reel' em governor_clusters_reels, 'feed' em governor_clusters_posts) -- mantido no schema das duas para permitir recombinação futura via pd.concat sem precisar re-derivar o rótulo (ADR 0020 Ficha 2 / issue #87; tabelas separadas desde a issue #152).</t>
+          <t>Nome do algoritmo eleito pelo AutoClusterHPO para esta execução (KMeans/DBSCAN/Agglomerative).</t>
         </is>
       </c>
     </row>
@@ -9045,22 +9453,22 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>cluster_score</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Score CVI combinado (Silhouette + Calinski-Harabasz normalizado + Davies-Bouldin invertido) do algoritmo eleito -- ver src/modeling/clustering.py.</t>
         </is>
       </c>
     </row>
@@ -9072,12 +9480,12 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>content_type</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -9087,19 +9495,19 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Valor constante por tabela ('reel' em governor_clusters_reels, 'feed' em governor_clusters_posts) -- mantido no schema das duas para permitir recombinação futura via pd.concat sem precisar re-derivar o rótulo (ADR 0020 Ficha 2 / issue #87; tabelas separadas desde a issue #152).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>governor_profile_clusters_engagement</t>
+          <t>governor_clusters_posts</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -9114,24 +9522,24 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>governor_profile_clusters_engagement</t>
+          <t>governor_clusters_posts</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>cluster_label</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -9141,7 +9549,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Rótulo do cluster atribuído pelo AutoClusterHPO (-1 = ruído do DBSCAN).</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9561,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>cluster_algo</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -9168,7 +9576,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Nome do algoritmo eleito pelo AutoClusterHPO para esta execução (KMeans/DBSCAN/Agglomerative).</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -9180,22 +9588,22 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>cluster_score</t>
+          <t>cluster_label</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Score CVI combinado (Silhouette + Calinski-Harabasz normalizado + Davies-Bouldin invertido) do algoritmo eleito -- ver src/modeling/clustering.py.</t>
+          <t>Rótulo do cluster atribuído pelo AutoClusterHPO (-1 = ruído do DBSCAN).</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9615,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>cluster_algo</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -9222,7 +9630,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Nome do algoritmo eleito pelo AutoClusterHPO para esta execução (KMeans/DBSCAN/Agglomerative).</t>
         </is>
       </c>
     </row>
@@ -9234,34 +9642,34 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>cluster_score</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Score CVI combinado (Silhouette + Calinski-Harabasz normalizado + Davies-Bouldin invertido) do algoritmo eleito -- ver src/modeling/clustering.py.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>post_performance_coefficients</t>
+          <t>governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>grupo</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -9276,24 +9684,24 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Discrimina o grupo da regressão de performance-por-post: 'video' (Reels) ou 'estatico' (posts de imagem/carrossel).</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>post_performance_coefficients</t>
+          <t>governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>preditor</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -9303,7 +9711,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Nome do preditor da regressão (varia por grupo -- ver coluna Notas da aba Tabelas).</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -9315,12 +9723,12 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>coeficiente</t>
+          <t>grupo</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -9330,7 +9738,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>Coeficiente estimado pelo LassoCV para este preditor (0.0 = preditor descartado pela regularização L1).</t>
+          <t>Discrimina o grupo da regressão de performance-por-post: 'video' (Reels) ou 'estatico' (posts de imagem/carrossel).</t>
         </is>
       </c>
     </row>
@@ -9342,12 +9750,12 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>r2_treino</t>
+          <t>preditor</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -9357,7 +9765,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>R² do modelo no conjunto de treino.</t>
+          <t>Nome do preditor da regressão (varia por grupo -- ver coluna Notas da aba Tabelas).</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9777,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>r2_holdout</t>
+          <t>coeficiente</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -9379,12 +9787,12 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>R² do modelo no conjunto de holdout -- nulo só no caso degenerado de um grupo sem governador em holdout.</t>
+          <t>Coeficiente estimado pelo LassoCV para este preditor (0.0 = preditor descartado pela regularização L1).</t>
         </is>
       </c>
     </row>
@@ -9396,12 +9804,12 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>n_treino</t>
+          <t>r2_treino</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -9411,7 +9819,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Número de posts no conjunto de treino deste grupo.</t>
+          <t>R² do modelo no conjunto de treino.</t>
         </is>
       </c>
     </row>
@@ -9423,22 +9831,22 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>n_holdout</t>
+          <t>r2_holdout</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>Número de posts no conjunto de holdout deste grupo.</t>
+          <t>R² do modelo no conjunto de holdout -- nulo só no caso degenerado de um grupo sem governador em holdout.</t>
         </is>
       </c>
     </row>
@@ -9450,12 +9858,12 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>n_treino</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -9465,7 +9873,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Hiperparâmetro de regularização (força da penalização L1) escolhido pelo LassoCV via validação cruzada.</t>
+          <t>Número de posts no conjunto de treino deste grupo.</t>
         </is>
       </c>
     </row>
@@ -9477,12 +9885,12 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>n_holdout</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -9492,7 +9900,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Número de posts no conjunto de holdout deste grupo.</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9912,12 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -9519,19 +9927,19 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Hiperparâmetro de regularização (força da penalização L1) escolhido pelo LassoCV via validação cruzada.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>post_performance_predictions</t>
+          <t>post_performance_coefficients</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -9546,34 +9954,34 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>post_performance_predictions</t>
+          <t>post_performance_coefficients</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -9585,7 +9993,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>grupo</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -9600,7 +10008,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>Discrimina o grupo da regressão de performance-por-post: 'video' (Reels) ou 'estatico' (posts de imagem/carrossel).</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
@@ -9612,22 +10020,22 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>y_real</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Valor real de Y = (likesCount + commentsCount × _WC_COMENTARIO) / followersCount para este post.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -9639,12 +10047,12 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>y_previsto</t>
+          <t>grupo</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -9654,7 +10062,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>Valor de Y previsto pela regressão Lasso treinada para o grupo (vídeo/estático) deste post.</t>
+          <t>Discrimina o grupo da regressão de performance-por-post: 'video' (Reels) ou 'estatico' (posts de imagem/carrossel).</t>
         </is>
       </c>
     </row>
@@ -9666,7 +10074,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>residuo</t>
+          <t>y_real</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -9681,7 +10089,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>y_real - y_previsto -- posts com resíduo muito positivo performaram acima do esperado pelo modelo, e vice-versa.</t>
+          <t>Valor real de Y = (likesCount + commentsCount × _WC_COMENTARIO) / followersCount para este post.</t>
         </is>
       </c>
     </row>
@@ -9693,12 +10101,12 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>y_previsto</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -9708,7 +10116,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Valor de Y previsto pela regressão Lasso treinada para o grupo (vídeo/estático) deste post.</t>
         </is>
       </c>
     </row>
@@ -9720,12 +10128,12 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>residuo</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -9735,24 +10143,24 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>y_real - y_previsto -- posts com resíduo muito positivo performaram acima do esperado pelo modelo, e vice-versa.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>topic_priority_score</t>
+          <t>post_performance_predictions</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -9762,34 +10170,34 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Id numérico do tópico BERTopic (-1 = ruído/sem tópico atribuído).</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>topic_priority_score</t>
+          <t>post_performance_predictions</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Rótulo textual do tópico BERTopic -- determinístico (KeyBERTInspired) por padrão, ou refinado manualmente via Gemini (scripts/refine_topics.py).</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -9801,7 +10209,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -9816,7 +10224,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários atribuídos a este tópico pelo BERTopic.</t>
+          <t>Id numérico do tópico BERTopic (-1 = ruído/sem tópico atribuído).</t>
         </is>
       </c>
     </row>
@@ -9828,22 +10236,22 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>alcance_topico</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Soma de (likesCount + repliesCount) dos comentários do tópico -- PROXY de visibilidade/ressonância, não alcance/views real.</t>
+          <t>Rótulo textual do tópico BERTopic -- determinístico (KeyBERTInspired) por padrão, ou refinado manualmente via Gemini (scripts/refine_topics.py).</t>
         </is>
       </c>
     </row>
@@ -9855,12 +10263,12 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>alcance_normalizado</t>
+          <t>n_comentarios</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -9870,7 +10278,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>alcance_topico / (alcance_topico + 1) -- normalização que satura suavemente em [0,1), nunca divide por zero, e não depende de quais outros tópicos existem na mesma execução.</t>
+          <t>Número de comentários atribuídos a este tópico pelo BERTopic.</t>
         </is>
       </c>
     </row>
@@ -9882,12 +10290,12 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>proporcao_sentimento_positivo</t>
+          <t>alcance_topico</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -9897,7 +10305,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Fração de comentários do tópico com sentiment_label == 'positive'.</t>
+          <t>Soma de (likesCount + repliesCount) dos comentários do tópico -- PROXY de visibilidade/ressonância, não alcance/views real.</t>
         </is>
       </c>
     </row>
@@ -9909,7 +10317,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>alcance_normalizado</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -9924,7 +10332,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>Média de sentiment_score (confiança do classificador, não polaridade) dos comentários do tópico.</t>
+          <t>alcance_topico / (alcance_topico + 1) -- normalização que satura suavemente em [0,1), nunca divide por zero, e não depende de quais outros tópicos existem na mesma execução.</t>
         </is>
       </c>
     </row>
@@ -9936,7 +10344,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>impacto</t>
+          <t>proporcao_sentimento_positivo</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -9951,7 +10359,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>alcance_normalizado × proporcao_sentimento_positivo.</t>
+          <t>Fração de comentários do tópico com sentiment_label == 'positive'.</t>
         </is>
       </c>
     </row>
@@ -9963,7 +10371,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -9978,7 +10386,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>Fixa em 1.0 nesta v1 (FACILIDADE_V1) -- sem dado de custo de produção real para calibrar; o ranking de Score reduz-se, na prática, a Impacto × Confiança.</t>
+          <t>Média de sentiment_score (confiança do classificador, não polaridade) dos comentários do tópico.</t>
         </is>
       </c>
     </row>
@@ -9990,7 +10398,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>impacto</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -10005,7 +10413,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Impacto × Confiança × Facilidade -- ranking final de priorização de produção de conteúdo.</t>
+          <t>alcance_normalizado × proporcao_sentimento_positivo.</t>
         </is>
       </c>
     </row>
@@ -10017,12 +10425,12 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>facilidade</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -10032,7 +10440,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Fixa em 1.0 nesta v1 (FACILIDADE_V1) -- sem dado de custo de produção real para calibrar; o ranking de Score reduz-se, na prática, a Impacto × Confiança.</t>
         </is>
       </c>
     </row>
@@ -10044,12 +10452,12 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>score</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -10059,19 +10467,19 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Impacto × Confiança × Facilidade -- ranking final de priorização de produção de conteúdo.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm</t>
+          <t>topic_priority_score</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -10081,39 +10489,39 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm</t>
+          <t>topic_priority_score</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Nome de usuário do perfil de Instagram.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -10125,22 +10533,22 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_positivos</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários (fonte == 'comentario') com sentiment_label == 'positive' deste perfil.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -10152,22 +10560,22 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_totais</t>
+          <t>username</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Número total de comentários (fonte == 'comentario') deste perfil.</t>
+          <t>Nome de usuário do perfil de Instagram.</t>
         </is>
       </c>
     </row>
@@ -10179,12 +10587,12 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>proporcao_positivos</t>
+          <t>n_comentarios_positivos</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -10194,7 +10602,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_positivos / n_comentarios_totais -- 0.0 quando o perfil não tem nenhum comentário (nunca NaN/erro).</t>
+          <t>Número de comentários (fonte == 'comentario') com sentiment_label == 'positive' deste perfil.</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10614,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>total_engajamento</t>
+          <t>n_comentarios_totais</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -10221,7 +10629,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Cópia de governor_engagement['TOTAL ENGAJAMENTO'] para este perfil, mantida para auditoria/contraste no dashboard.</t>
+          <t>Número total de comentários (fonte == 'comentario') deste perfil.</t>
         </is>
       </c>
     </row>
@@ -10233,12 +10641,12 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>count_posts</t>
+          <t>proporcao_positivos</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -10248,7 +10656,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>Cópia de governor_engagement['count'] para este perfil.</t>
+          <t>n_comentarios_positivos / n_comentarios_totais -- 0.0 quando o perfil não tem nenhum comentário (nunca NaN/erro).</t>
         </is>
       </c>
     </row>
@@ -10260,12 +10668,12 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>alcance_medio</t>
+          <t>total_engajamento</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -10275,7 +10683,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>total_engajamento / count_posts -- PROXY de alcance (intensidade de engajamento por post), não alcance/views real. 0.0 quando count_posts == 0.</t>
+          <t>Cópia de governor_engagement['TOTAL ENGAJAMENTO'] para este perfil, mantida para auditoria/contraste no dashboard.</t>
         </is>
       </c>
     </row>
@@ -10287,12 +10695,12 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>nsm</t>
+          <t>count_posts</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -10302,7 +10710,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>proporcao_positivos × alcance_medio -- North Star Metric de engajamento QUALIFICADO (pondera qualidade de reação, não só volume).</t>
+          <t>Cópia de governor_engagement['count'] para este perfil.</t>
         </is>
       </c>
     </row>
@@ -10314,12 +10722,12 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>alcance_medio</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -10329,7 +10737,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>total_engajamento / count_posts -- PROXY de alcance (intensidade de engajamento por post), não alcance/views real. 0.0 quando count_posts == 0.</t>
         </is>
       </c>
     </row>
@@ -10341,12 +10749,12 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>nsm</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -10356,19 +10764,19 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>proporcao_positivos × alcance_medio -- North Star Metric de engajamento QUALIFICADO (pondera qualidade de reação, não só volume).</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_nsm</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -10378,39 +10786,39 @@
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_nsm</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Nome de usuário do perfil de Instagram.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -10422,22 +10830,22 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_positivos</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários (fonte == 'comentario') com sentiment_label == 'positive' deste perfil.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -10449,22 +10857,22 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_totais</t>
+          <t>username</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Número total de comentários (fonte == 'comentario') deste perfil.</t>
+          <t>Nome de usuário do perfil de Instagram.</t>
         </is>
       </c>
     </row>
@@ -10476,12 +10884,12 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>proporcao_positivos</t>
+          <t>n_comentarios_positivos</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -10491,7 +10899,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_positivos / n_comentarios_totais -- 0.0 quando o perfil não tem nenhum comentário (nunca NaN/erro).</t>
+          <t>Número de comentários (fonte == 'comentario') com sentiment_label == 'positive' deste perfil.</t>
         </is>
       </c>
     </row>
@@ -10503,7 +10911,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>total_engajamento</t>
+          <t>n_comentarios_totais</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -10518,7 +10926,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Cópia de governor_engagement['TOTAL ENGAJAMENTO'] para este perfil, mantida para auditoria/contraste no dashboard.</t>
+          <t>Número total de comentários (fonte == 'comentario') deste perfil.</t>
         </is>
       </c>
     </row>
@@ -10530,12 +10938,12 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>count_posts</t>
+          <t>proporcao_positivos</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -10545,7 +10953,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Cópia de governor_engagement['count'] para este perfil.</t>
+          <t>n_comentarios_positivos / n_comentarios_totais -- 0.0 quando o perfil não tem nenhum comentário (nunca NaN/erro).</t>
         </is>
       </c>
     </row>
@@ -10557,12 +10965,12 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>alcance_medio</t>
+          <t>total_engajamento</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -10572,7 +10980,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>total_engajamento / count_posts -- PROXY de alcance (intensidade de engajamento por post), não alcance/views real. 0.0 quando count_posts == 0.</t>
+          <t>Cópia de governor_engagement['TOTAL ENGAJAMENTO'] para este perfil, mantida para auditoria/contraste no dashboard.</t>
         </is>
       </c>
     </row>
@@ -10584,12 +10992,12 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>nsm</t>
+          <t>count_posts</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -10599,7 +11007,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>proporcao_positivos × alcance_medio -- North Star Metric de engajamento QUALIFICADO (pondera qualidade de reação, não só volume).</t>
+          <t>Cópia de governor_engagement['count'] para este perfil.</t>
         </is>
       </c>
     </row>
@@ -10611,12 +11019,12 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>alcance_medio</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -10626,7 +11034,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>total_engajamento / count_posts -- PROXY de alcance (intensidade de engajamento por post), não alcance/views real. 0.0 quando count_posts == 0.</t>
         </is>
       </c>
     </row>
@@ -10638,12 +11046,12 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>nsm</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -10653,19 +11061,19 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>proporcao_positivos × alcance_medio -- North Star Metric de engajamento QUALIFICADO (pondera qualidade de reação, não só volume).</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -10675,39 +11083,39 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_nsm_history</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -10719,7 +11127,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>governor_username</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -10734,7 +11142,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
@@ -10746,7 +11154,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>authorUsername</t>
+          <t>shortCode</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -10761,7 +11169,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
         </is>
       </c>
     </row>
@@ -10773,7 +11181,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>caption</t>
+          <t>governor_username</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -10788,7 +11196,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Legenda do post de UGC (do autor terceiro, não do governador).</t>
+          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
         </is>
       </c>
     </row>
@@ -10800,22 +11208,22 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>authorUsername</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
         </is>
       </c>
     </row>
@@ -10827,22 +11235,22 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>caption</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>Legenda do post de UGC (do autor terceiro, não do governador).</t>
         </is>
       </c>
     </row>
@@ -10854,7 +11262,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -10864,12 +11272,12 @@
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -10881,12 +11289,12 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>is_organic</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -10896,7 +11304,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Derivado de `paidPartnership`: True quando ausente/False -- separa apoio espontâneo de publi paga.</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
@@ -10908,22 +11316,22 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us]</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -10935,12 +11343,12 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>is_organic</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -10950,7 +11358,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Derivado de `paidPartnership`: True quando ausente/False -- separa apoio espontâneo de publi paga.</t>
         </is>
       </c>
     </row>
@@ -10962,12 +11370,12 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>timestamp[us]</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -10977,19 +11385,19 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -10999,39 +11407,39 @@
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>valor_inicial</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Valor da métrica-base (followersCount) no primeiro mês-calendário com execução registrada.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -11043,12 +11451,12 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>valor_final</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -11058,7 +11466,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Valor da métrica-base (followersCount) no último mês-calendário com execução registrada.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11478,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>cmgr</t>
+          <t>valor_inicial</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -11085,7 +11493,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>(valor_final / valor_inicial) ** (1 / n_meses) - 1 -- crescimento mensal composto. NaN quando não calculável (ver cmgr_motivo).</t>
+          <t>Valor da métrica-base (followersCount) no primeiro mês-calendário com execução registrada.</t>
         </is>
       </c>
     </row>
@@ -11097,22 +11505,22 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>cmgr_n_periodos</t>
+          <t>valor_final</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>Número de meses-calendário com execução registrada usados no cálculo do CMGR.</t>
+          <t>Valor da métrica-base (followersCount) no último mês-calendário com execução registrada.</t>
         </is>
       </c>
     </row>
@@ -11124,22 +11532,22 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>cmgr_confiavel</t>
+          <t>cmgr</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>False sempre que cmgr_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL) -- sinaliza resultado ilustrativo, não conclusivo.</t>
+          <t>(valor_final / valor_inicial) ** (1 / n_meses) - 1 -- crescimento mensal composto. NaN quando não calculável (ver cmgr_motivo).</t>
         </is>
       </c>
     </row>
@@ -11151,22 +11559,22 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>cmgr_motivo</t>
+          <t>cmgr_n_periodos</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Motivo do CMGR ser NaN, quando aplicável: historico_insuficiente / periodo_zero / valor_inicial_invalido.</t>
+          <t>Número de meses-calendário com execução registrada usados no cálculo do CMGR.</t>
         </is>
       </c>
     </row>
@@ -11178,22 +11586,22 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>retencao</t>
+          <t>cmgr_confiavel</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Média de valor_t/valor_(t-1) (capada em 1.0) do share mensal de sentimento positivo entre meses consecutivos -- 1.0 = manteve 100% (ou mais); mede o quanto do período anterior foi retido, não crescimento.</t>
+          <t>False sempre que cmgr_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL) -- sinaliza resultado ilustrativo, não conclusivo.</t>
         </is>
       </c>
     </row>
@@ -11205,22 +11613,22 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>retencao_n_periodos</t>
+          <t>cmgr_motivo</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>Número de meses-calendário com execução registrada usados no cálculo da retenção.</t>
+          <t>Motivo do CMGR ser NaN, quando aplicável: historico_insuficiente / periodo_zero / valor_inicial_invalido.</t>
         </is>
       </c>
     </row>
@@ -11232,22 +11640,22 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>retencao_n_pares_validos</t>
+          <t>retencao</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Número de pares de meses consecutivos válidos usados na média da retenção.</t>
+          <t>Média de valor_t/valor_(t-1) (capada em 1.0) do share mensal de sentimento positivo entre meses consecutivos -- 1.0 = manteve 100% (ou mais); mede o quanto do período anterior foi retido, não crescimento.</t>
         </is>
       </c>
     </row>
@@ -11259,12 +11667,12 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>retencao_confiavel</t>
+          <t>retencao_n_periodos</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -11274,7 +11682,7 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>False sempre que retencao_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL).</t>
+          <t>Número de meses-calendário com execução registrada usados no cálculo da retenção.</t>
         </is>
       </c>
     </row>
@@ -11286,22 +11694,22 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>retencao_motivo</t>
+          <t>retencao_n_pares_validos</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Motivo da retenção ser NaN, quando aplicável (mesmas categorias do cmgr_motivo).</t>
+          <t>Número de pares de meses consecutivos válidos usados na média da retenção.</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11721,7 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>ilustrativo</t>
+          <t>retencao_confiavel</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -11328,7 +11736,7 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>True enquanto o pipeline não tiver acumulado histórico real suficiente -- sinaliza que o valor valida a FÓRMULA, não sustenta conclusão definitiva no TCC.</t>
+          <t>False sempre que retencao_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL).</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11748,7 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>retencao_motivo</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -11350,12 +11758,12 @@
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Texto explicando por que o resultado é (ou não) ilustrativo, para exibição direta em dashboard/relatório sem reprocessar nada.</t>
+          <t>Motivo da retenção ser NaN, quando aplicável (mesmas categorias do cmgr_motivo).</t>
         </is>
       </c>
     </row>
@@ -11367,12 +11775,12 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>ilustrativo</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -11382,7 +11790,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>True enquanto o pipeline não tiver acumulado histórico real suficiente -- sinaliza que o valor valida a FÓRMULA, não sustenta conclusão definitiva no TCC.</t>
         </is>
       </c>
     </row>
@@ -11394,12 +11802,12 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -11409,19 +11817,19 @@
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Texto explicando por que o resultado é (ou não) ilustrativo, para exibição direta em dashboard/relatório sem reprocessar nada.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -11436,34 +11844,34 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil do governador (chave de junção; normalizada em minúsculas, sem espaços e sem barra final para cruzar Silver e Gold).</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil (de governor_engagement); pode ser nulo.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -11475,22 +11883,22 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>alcance</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>Dimensão Alcance bruta: média de videoPlayCount (REPRODUÇÕES / plays, nunca "visualizações únicas") dos reels do perfil. Posts de feed não têm plays e não entram. Nulo sem reels com plays.</t>
+          <t>URL do perfil do governador (chave de junção; normalizada em minúsculas, sem espaços e sem barra final para cruzar Silver e Gold).</t>
         </is>
       </c>
     </row>
@@ -11502,12 +11910,12 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>ativacao</t>
+          <t>username</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -11517,7 +11925,7 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Dimensão Ativação bruta: média de likesCount dos reels / followersCount do perfil. Nulo sem reels ou sem seguidores.</t>
+          <t>Username do perfil (de governor_engagement); pode ser nulo.</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11937,7 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>qualidade</t>
+          <t>alcance</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -11544,7 +11952,7 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Dimensão Qualidade bruta: comentários positivos / comentários totais do perfil (só governor_sentiment com fonte == 'comentario'). Nulo sem comentários.</t>
+          <t>Dimensão Alcance bruta: média de videoPlayCount (REPRODUÇÕES / plays, nunca "visualizações únicas") dos reels do perfil. Posts de feed não têm plays e não entram. Nulo sem reels com plays.</t>
         </is>
       </c>
     </row>
@@ -11556,7 +11964,7 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>profundidade</t>
+          <t>ativacao</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -11571,7 +11979,7 @@
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Dimensão Profundidade bruta: média de commentsCount / média de videoPlayCount, ambas sobre os reels com plays (mesma base do Alcance). Nulo sem reels com plays.</t>
+          <t>Dimensão Ativação bruta: média de likesCount dos reels / followersCount do perfil. Nulo sem reels ou sem seguidores.</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11991,7 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>consistencia</t>
+          <t>qualidade</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -11598,7 +12006,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Dimensão Consistência bruta: CMGR de engajamento por data de publicação = exp(inclinação) - 1 da regressão log-linear sobre o engajamento médio por post (curtidas + comentários) de cada mês de publicação. Janela de até 12 meses completos (mês corrente excluído), mês válido com &gt;= 3 posts, posts com &lt; 7 dias de vida excluídos. Nula (pendente) com &lt; 4 meses válidos. NÃO é crescimento de audiência.</t>
+          <t>Dimensão Qualidade bruta: comentários positivos / comentários totais do perfil (só governor_sentiment com fonte == 'comentario'). Nulo sem comentários.</t>
         </is>
       </c>
     </row>
@@ -11610,7 +12018,7 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>alcance_norm</t>
+          <t>profundidade</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -11625,7 +12033,7 @@
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>alcance normalizado min-máx 0-100 entre os perfis com a dimensão (100 = maior). Amplitude zero -&gt; 50. Nulo quando a dimensão bruta é nula.</t>
+          <t>Dimensão Profundidade bruta: média de commentsCount / média de videoPlayCount, ambas sobre os reels com plays (mesma base do Alcance). Nulo sem reels com plays.</t>
         </is>
       </c>
     </row>
@@ -11637,7 +12045,7 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>ativacao_norm</t>
+          <t>consistencia</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -11652,7 +12060,7 @@
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>ativacao normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
+          <t>Dimensão Consistência bruta: CMGR de engajamento por data de publicação = exp(inclinação) - 1 da regressão log-linear sobre o engajamento médio por post (curtidas + comentários) de cada mês de publicação. Janela de até 12 meses completos (mês corrente excluído), mês válido com &gt;= 3 posts, posts com &lt; 7 dias de vida excluídos. Nula (pendente) com &lt; 4 meses válidos. NÃO é crescimento de audiência.</t>
         </is>
       </c>
     </row>
@@ -11664,7 +12072,7 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>qualidade_norm</t>
+          <t>alcance_norm</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -11679,7 +12087,7 @@
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>qualidade normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
+          <t>alcance normalizado min-máx 0-100 entre os perfis com a dimensão (100 = maior). Amplitude zero -&gt; 50. Nulo quando a dimensão bruta é nula.</t>
         </is>
       </c>
     </row>
@@ -11691,7 +12099,7 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>profundidade_norm</t>
+          <t>ativacao_norm</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -11706,7 +12114,7 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>profundidade normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
+          <t>ativacao normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
         </is>
       </c>
     </row>
@@ -11718,7 +12126,7 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>consistencia_norm</t>
+          <t>qualidade_norm</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -11733,7 +12141,7 @@
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>consistencia normalizada min-máx 0-100 entre os perfis com a dimensão. Nula quando Consistência está pendente (hoje, todos os 26 governadores).</t>
+          <t>qualidade normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
         </is>
       </c>
     </row>
@@ -11745,22 +12153,22 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>consistencia_pendente</t>
+          <t>profundidade_norm</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>True quando a Consistência não pôde ser calculada (&lt; 4 meses válidos). Selo de confiabilidade: o escore daquele perfil usa só as outras dimensões, com os pesos renormalizados.</t>
+          <t>profundidade normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
         </is>
       </c>
     </row>
@@ -11772,22 +12180,22 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>consistencia_n_meses</t>
+          <t>consistencia_norm</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Número de meses de publicação válidos (&gt;= 3 posts maduros, dentro da janela) que entraram, ou entrariam, no cálculo da Consistência.</t>
+          <t>consistencia normalizada min-máx 0-100 entre os perfis com a dimensão. Nula quando Consistência está pendente (hoje, todos os 26 governadores).</t>
         </is>
       </c>
     </row>
@@ -11799,12 +12207,12 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>n_dimensoes</t>
+          <t>consistencia_pendente</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -11814,7 +12222,7 @@
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Quantas das 5 dimensões normalizadas entraram no escore deste perfil (5, ou 4 com Consistência pendente). Perfil com &lt; 4 fica sem escore.</t>
+          <t>True quando a Consistência não pôde ser calculada (&lt; 4 meses válidos). Selo de confiabilidade: o escore daquele perfil usa só as outras dimensões, com os pesos renormalizados.</t>
         </is>
       </c>
     </row>
@@ -11826,22 +12234,22 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>escore</t>
+          <t>consistencia_n_meses</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Escore composto 0-100: média simples das dimensões normalizadas disponíveis (soma ponderada com pesos iguais: 0,20 com 5 dimensões, 0,25 com 4). Nulo com &lt; 4 dimensões. Relativo ao grupo de perfis.</t>
+          <t>Número de meses de publicação válidos (&gt;= 3 posts maduros, dentro da janela) que entraram, ou entrariam, no cálculo da Consistência.</t>
         </is>
       </c>
     </row>
@@ -11853,7 +12261,7 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>ranking</t>
+          <t>n_dimensoes</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -11863,12 +12271,12 @@
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Posição do perfil pelo escore (1 = maior; desempate por inputUrl). Nulo quando o perfil não tem escore.</t>
+          <t>Quantas das 5 dimensões normalizadas entraram no escore deste perfil (5, ou 4 com Consistência pendente). Perfil com &lt; 4 fica sem escore.</t>
         </is>
       </c>
     </row>
@@ -11880,22 +12288,22 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>escore</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Escore composto 0-100: média simples das dimensões normalizadas disponíveis (soma ponderada com pesos iguais: 0,20 com 5 dimensões, 0,25 com 4). Nulo com &lt; 4 dimensões. Relativo ao grupo de perfis.</t>
         </is>
       </c>
     </row>
@@ -11907,39 +12315,39 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>ranking</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Posição do perfil pelo escore (1 = maior; desempate por inputUrl). Nulo quando o perfil não tem escore.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>content_topic_priority_score</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -11949,34 +12357,34 @@
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Id numérico do tópico de DISCURSO (BERTopic de legendas) que define a pauta -- espaço de ids distinto do tópico de comentário. O ruído (-1) nunca é pauta.</t>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>content_topic_priority_score</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>Rótulo da pauta: tópico de discurso sem o prefixo de id; rótulo refinado via Gemini quando o refino do discurso rodou, palavras-chave separadas por vírgula quando provisório, ou "sem assunto definido" quando o tópico é degenerado.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
@@ -11988,7 +12396,7 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>n_reels</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -12003,7 +12411,7 @@
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Número de reels distintos cuja legenda pertence à pauta e que receberam ao menos um comentário.</t>
+          <t>Id numérico do tópico de DISCURSO (BERTopic de legendas) que define a pauta -- espaço de ids distinto do tópico de comentário. O ruído (-1) nunca é pauta.</t>
         </is>
       </c>
     </row>
@@ -12015,22 +12423,22 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários (fonte == 'comentario') dos reels da pauta -- cada reel conta numa única pauta, então os totais somam o total real de comentários com pauta.</t>
+          <t>Rótulo da pauta: tópico de discurso sem o prefixo de id; rótulo refinado via Gemini quando o refino do discurso rodou, palavras-chave separadas por vírgula quando provisório, ou "sem assunto definido" quando o tópico é degenerado.</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12450,7 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_positivos</t>
+          <t>n_reels</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -12057,7 +12465,7 @@
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Comentários da pauta com sentiment_label == 'positive'.</t>
+          <t>Número de reels distintos cuja legenda pertence à pauta e que receberam ao menos um comentário.</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12477,7 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_negativos</t>
+          <t>n_comentarios</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -12084,7 +12492,7 @@
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>Comentários da pauta com sentiment_label == 'negative'.</t>
+          <t>Número de comentários (fonte == 'comentario') dos reels da pauta -- cada reel conta numa única pauta, então os totais somam o total real de comentários com pauta.</t>
         </is>
       </c>
     </row>
@@ -12096,12 +12504,12 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>proporcao_sentimento_positivo</t>
+          <t>n_comentarios_positivos</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -12111,7 +12519,7 @@
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_positivos / n_comentarios.</t>
+          <t>Comentários da pauta com sentiment_label == 'positive'.</t>
         </is>
       </c>
     </row>
@@ -12123,7 +12531,7 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>alcance_pauta</t>
+          <t>n_comentarios_negativos</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
@@ -12138,7 +12546,7 @@
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>Soma de (likesCount + repliesCount) dos comentários da pauta -- PROXY por engajamento, não alcance nem visualizações reais.</t>
+          <t>Comentários da pauta com sentiment_label == 'negative'.</t>
         </is>
       </c>
     </row>
@@ -12150,7 +12558,7 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>alcance_normalizado</t>
+          <t>proporcao_sentimento_positivo</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
@@ -12165,7 +12573,7 @@
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>alcance_pauta / (alcance_pauta + 1) -- satura suavemente em [0,1), estável entre execuções.</t>
+          <t>n_comentarios_positivos / n_comentarios.</t>
         </is>
       </c>
     </row>
@@ -12177,12 +12585,12 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>alcance_pauta</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -12192,7 +12600,7 @@
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>Média de sentiment_score (confiança do classificador, não polaridade) dos comentários da pauta.</t>
+          <t>Soma de (likesCount + repliesCount) dos comentários da pauta -- PROXY por engajamento, não alcance nem visualizações reais.</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12612,7 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>impacto</t>
+          <t>alcance_normalizado</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
@@ -12219,7 +12627,7 @@
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>alcance_normalizado x proporcao_sentimento_positivo.</t>
+          <t>alcance_pauta / (alcance_pauta + 1) -- satura suavemente em [0,1), estável entre execuções.</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12639,7 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>facilidade</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
@@ -12246,7 +12654,7 @@
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>Fixa em 1,0 (v1) -- sem dado de custo de produção real.</t>
+          <t>Média de sentiment_score (confiança do classificador, não polaridade) dos comentários da pauta.</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12666,7 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>impacto</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
@@ -12273,7 +12681,7 @@
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>Impacto x Confiança x Facilidade -- base do selo de prioridade (Alta/Média/Cuidado por tercis do ranking global de pautas) na fila de "O que produzir".</t>
+          <t>alcance_normalizado x proporcao_sentimento_positivo.</t>
         </is>
       </c>
     </row>
@@ -12285,12 +12693,12 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>facilidade</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -12300,7 +12708,7 @@
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Fixa em 1,0 (v1) -- sem dado de custo de produção real.</t>
         </is>
       </c>
     </row>
@@ -12312,27 +12720,81 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>Impacto x Confiança x Facilidade -- base do selo de prioridade (Alta/Média/Cuidado por tercis do ranking global de pautas) na fila de "O que produzir".</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>_run_id</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>content_topic_priority_score</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
           <t>_generated_at</t>
         </is>
       </c>
-      <c r="C215" s="3" t="inlineStr">
+      <c r="C217" s="3" t="inlineStr">
         <is>
           <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
-      <c r="D215" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="inlineStr">
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
         <is>
           <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E215"/>
+  <autoFilter ref="A1:E217"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12343,7 +12805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12597,335 +13059,357 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>reference/governadores.xlsx</t>
+          <t>Bronze: instagram_posts (campo latestComments)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Silver: governors_metadata</t>
+          <t>Silver: post_comments_clean</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Renomeia colunas (Governador-&gt;nome, Unidade Federativa-&gt;uf, Partido-&gt;partido, Link-&gt;inputUrl); dedup por inputUrl.</t>
+          <t>Mesma explosão de comments_clean (CommentCleaner(origem='post')), com `id_post` no lugar de `id_reel` -- tabela separada (issue #212).</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/governors_metadata_cleaner.py</t>
+          <t>src/features/silver/comment_cleaner.py</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Silver: profiles_clean + posts_clean + reels_clean</t>
+          <t>reference/governadores.xlsx</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_engagement / governor_engagement_history</t>
+          <t>Silver: governors_metadata</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Agrega posts+reels por perfil; calcula TOTAL ENGAJAMENTO, % ENGAJAMENTO (ponderado por _WC_COMENTARIO), RECENCIA e FREQUENCIA.</t>
+          <t>Renomeia colunas (Governador-&gt;nome, Unidade Federativa-&gt;uf, Partido-&gt;partido, Link-&gt;inputUrl); dedup por inputUrl.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/engagement_aggregator.py</t>
+          <t>src/features/silver/governors_metadata_cleaner.py</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Silver: comments_clean + reels_clean/posts_clean (legenda/transcrição)</t>
+          <t>Silver: profiles_clean + posts_clean + reels_clean</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment / governor_sentiment_history</t>
+          <t>Gold: governor_engagement / governor_engagement_history</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Classificação de sentimento (cardiffnlp/twitter-xlm-roberta-base-sentiment) + tópico BERTopic determinístico, por comentário/legenda/transcrição.</t>
+          <t>Agrega posts+reels por perfil; calcula TOTAL ENGAJAMENTO, % ENGAJAMENTO (ponderado por _WC_COMENTARIO), RECENCIA e FREQUENCIA.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/sentiment.py + src/modeling/topics.py, gravado por src/features/gold/model_enricher.py</t>
+          <t>src/features/gold/engagement_aggregator.py</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment</t>
+          <t>Silver: comments_clean + post_comments_clean (unidas por combine_comment_sources, dedup por id_comment preferindo reel) + reels_clean/posts_clean (legenda/transcrição)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>governor_sentiment (rótulos atualizados)</t>
+          <t>Gold: governor_sentiment / governor_sentiment_history</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Refinamento manual dos rótulos de tópico (Name) via Gemini -- reescreve a mesma tabela, não gera nova medição de sentimento.</t>
+          <t>Classificação de sentimento (cardiffnlp/twitter-xlm-roberta-base-sentiment) + tópico BERTopic determinístico, por comentário/legenda/transcrição.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>scripts/refine_topics.py + src/modeling/gemini_refiner.py</t>
+          <t>src/modeling/sentiment.py + src/modeling/topics.py, gravado por src/features/gold/model_enricher.py</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Silver: reels_clean + posts_clean</t>
+          <t>Gold: governor_sentiment</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_clusters_reels + governor_clusters_posts</t>
+          <t>governor_sentiment (rótulos atualizados)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>PCA (engajamento/duração) + AutoClusterHPO (KMeans/DBSCAN/Agglomerative eleito por score CVI) por post; duas tabelas separadas (uma por formato, issue #152) em vez de uma combinada, porque reels_clean/posts_clean se sobrepõem (mesmo Reel capturado por dois actors Apify distintos).</t>
+          <t>Refinamento manual dos rótulos de tópico (Name) via Gemini -- reescreve a mesma tabela, não gera nova medição de sentimento.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/clustering.py, gravado por src/features/gold/model_enricher.py</t>
+          <t>scripts/refine_topics.py + src/modeling/gemini_refiner.py</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_engagement</t>
+          <t>Silver: reels_clean + posts_clean</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_profile_clusters_engagement</t>
+          <t>Gold: governor_clusters_reels + governor_clusters_posts</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Mesma pipeline PCA-&gt;AutoClusterHPO, mas com features agregadas por PERFIL em vez de por post.</t>
+          <t>PCA (engajamento/duração) + AutoClusterHPO (KMeans/DBSCAN/Agglomerative eleito por score CVI) por post; duas tabelas separadas (uma por formato, issue #152) em vez de uma combinada, porque reels_clean/posts_clean se sobrepõem (mesmo Reel capturado por dois actors Apify distintos).</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/profile_clustering.py, via src/modeling/orchestration.py::run_deterministic_modeling (ou isoladamente via scripts/run_profile_clustering_engagement.py)</t>
+          <t>src/modeling/clustering.py, gravado por src/features/gold/model_enricher.py</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Silver: posts_clean (caption/hashtags/Topic) + reels_clean + Gold: governor_engagement</t>
+          <t>Gold: governor_engagement</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Gold: post_performance_coefficients / post_performance_predictions</t>
+          <t>Gold: governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Regressão Lasso de Y = (likes+comentários×Wc)/seguidores sobre preditores temporais/de formato/conteúdo, separada em grupo vídeo/estático; checagem de circularidade antes de treinar.</t>
+          <t>Mesma pipeline PCA-&gt;AutoClusterHPO, mas com features agregadas por PERFIL em vez de por post.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/post_performance.py</t>
+          <t>src/modeling/profile_clustering.py, via src/modeling/orchestration.py::run_deterministic_modeling (ou isoladamente via scripts/run_profile_clustering_engagement.py)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment (fonte='comentario')</t>
+          <t>Silver: posts_clean (caption/hashtags/Topic) + reels_clean + Gold: governor_engagement</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Gold: topic_priority_score</t>
+          <t>Gold: post_performance_coefficients / post_performance_predictions</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Score ICE = Impacto(alcance_normalizado×%positivo) × Confiança(sentiment_score médio) × Facilidade(fixa=1.0), agregado por Topic.</t>
+          <t>Regressão Lasso de Y = (likes+comentários×Wc)/seguidores sobre preditores temporais/de formato/conteúdo, separada em grupo vídeo/estático; checagem de circularidade antes de treinar.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/topic_priority_scorer.py</t>
+          <t>src/modeling/post_performance.py</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment (fonte='comentario') + governor_engagement</t>
+          <t>Gold: governor_sentiment (fonte='comentario')</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_nsm</t>
+          <t>Gold: topic_priority_score</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>NSM = (%comentários positivos) × (TOTAL ENGAJAMENTO / count, como proxy de alcance), merge outer por inputUrl.</t>
+          <t>Score ICE = Impacto(alcance_normalizado×%positivo) × Confiança(sentiment_score médio) × Facilidade(fixa=1.0), agregado por Topic.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/nsm_scorer.py</t>
+          <t>src/features/gold/topic_priority_scorer.py</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment (fonte='comentario') + governor_discourse_topics (fonte='legenda')</t>
+          <t>Gold: governor_sentiment (fonte='comentario') + governor_engagement</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Gold: content_topic_priority_score</t>
+          <t>Gold: governor_nsm</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Score ICE por pauta: comentários ligados à pauta do reel (legenda) via id_reel; Impacto(alcance_normalizado x %positivo) x Confiança(sentiment_score médio) x Facilidade(fixa=1,0), agregado por Topic de discurso. Calculado de forma provisória no estágio determinístico e recalculado após o refino Gemini do discurso.</t>
+          <t>NSM = (%comentários positivos) × (TOTAL ENGAJAMENTO / count, como proxy de alcance), merge outer por inputUrl.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/content_topic_priority_scorer.py (orchestration.py::run_deterministic_modeling e refine_discourse_topics_with_gemini)</t>
+          <t>src/features/gold/nsm_scorer.py</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_discourse_topics</t>
+          <t>Gold: governor_sentiment (fonte='comentario') + governor_discourse_topics (fonte='legenda')</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>governor_discourse_topics (rótulos refinados)</t>
+          <t>Gold: content_topic_priority_score</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Refinamento manual dos rótulos de tópico de discurso (Name) via Gemini; ruído (-1) mantido, tópico degenerado vira "sem assunto definido". Reescreve a mesma tabela e recalcula content_topic_priority_score.</t>
+          <t>Score ICE por pauta: comentários ligados à pauta do reel (legenda) via id_reel; Impacto(alcance_normalizado x %positivo) x Confiança(sentiment_score médio) x Facilidade(fixa=1,0), agregado por Topic de discurso. Calculado de forma provisória no estágio determinístico e recalculado após o refino Gemini do discurso.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>scripts/refine_topics.py (--target all|discourse) + src/modeling/orchestration.py::refine_discourse_topics_with_gemini</t>
+          <t>src/features/gold/content_topic_priority_scorer.py (orchestration.py::run_deterministic_modeling e refine_discourse_topics_with_gemini)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_engagement (seguidores) + Silver: reels_clean + posts_clean + Gold: governor_sentiment (fonte='comentario')</t>
+          <t>Gold: governor_discourse_topics</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_scorecard</t>
+          <t>governor_discourse_topics (rótulos refinados)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Escore composto: 5 dimensões por governador (Alcance, Ativação, Qualidade, Profundidade, Consistência), normalização min-máx 0-100 entre os perfis, média simples das dimensões disponíveis (pesos iguais renormalizados), ranking. Consistência = CMGR de engajamento por data de publicação (pendente sem &gt;= 4 meses válidos).</t>
+          <t>Refinamento manual dos rótulos de tópico de discurso (Name) via Gemini; ruído (-1) mantido, tópico degenerado vira "sem assunto definido". Reescreve a mesma tabela e recalcula content_topic_priority_score.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/governor_scorecard.py (orchestration.py::run_deterministic_modeling ou scripts/run_governor_scorecard.py)</t>
+          <t>scripts/refine_topics.py (--target all|discourse) + src/modeling/orchestration.py::refine_discourse_topics_with_gemini</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_engagement_history + governor_sentiment_history</t>
+          <t>Gold: governor_engagement (seguidores) + Silver: reels_clean + posts_clean + Gold: governor_sentiment (fonte='comentario')</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_growth_metrics</t>
+          <t>Gold: governor_scorecard</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>CMGR sobre followersCount mensal + retenção sobre share mensal de sentimento positivo; marca ilustrativo/confiavel conforme volume de histórico.</t>
+          <t>Escore composto: 5 dimensões por governador (Alcance, Ativação, Qualidade, Profundidade, Consistência), normalização min-máx 0-100 entre os perfis, média simples das dimensões disponíveis (pesos iguais renormalizados), ranking. Consistência = CMGR de engajamento por data de publicação (pendente sem &gt;= 4 meses válidos).</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/growth_history.py + scripts/run_growth_metrics.py</t>
+          <t>src/modeling/governor_scorecard.py (orchestration.py::run_deterministic_modeling ou scripts/run_governor_scorecard.py)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Apify (apify/instagram-tagged-scraper -- ver aba Actors Apify)</t>
+          <t>Gold: governor_engagement_history + governor_sentiment_history</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Bronze/Silver/Gold: ugc_mentions / governor_ugc_mentions</t>
+          <t>Gold: governor_growth_metrics</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Coleta -&gt; landing zone -&gt; Bronze -&gt; Silver (dedup id/shortCode, normalização de handle, resolução de governor_username via mentions+taggedUsers) -&gt; Gold (is_organic a partir de paidPartnership), tudo sob o mesmo run_id -- mesmo padrão de scripts/run_apify_backfill.py. Schema corrigido contra o piloto real (scripts/run_apify_mentions_pilot.py, 2026-09-19, data/pilot/*.json, fora do Delta Lake). Writer de produção rodou contra a Apify de produção pela 1a vez em 2026-09-19 (achado no PR #140, que corrigiu um FutureWarning de pandas revelado por esse dado real).</t>
+          <t>CMGR sobre followersCount mensal + retenção sobre share mensal de sentimento positivo; marca ilustrativo/confiavel conforme volume de histórico.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>scripts/run_ugc_mentions.py + src/data_extract/bronze_writer.py + src/features/silver/ugc_mention_cleaner.py + src/features/gold/ugc_mentions_aggregator.py</t>
+          <t>src/modeling/growth_history.py + scripts/run_growth_metrics.py</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>Apify (apify/instagram-tagged-scraper -- ver aba Actors Apify)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Bronze/Silver/Gold: ugc_mentions / governor_ugc_mentions</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Coleta -&gt; landing zone -&gt; Bronze -&gt; Silver (dedup id/shortCode, normalização de handle, resolução de governor_username via mentions+taggedUsers) -&gt; Gold (is_organic a partir de paidPartnership), tudo sob o mesmo run_id da extração principal (coleta de UGC é a última etapa de extract_and_land, tolerante a falha). Schema corrigido contra o piloto real (scripts/run_apify_mentions_pilot.py, 2026-09-19, data/pilot/*.json, fora do Delta Lake). Writer de produção rodou contra a Apify de produção pela 1a vez em 2026-09-19 (achado no PR #140, que corrigiu um FutureWarning de pandas revelado por esse dado real).</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>src/data_extract/ingestion.py::extract_and_land + src/data_extract/bronze_writer.py + src/features/silver/ugc_mention_cleaner.py + src/features/gold/ugc_mentions_aggregator.py, orquestrados por pipeline.py (issue #211)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
           <t>Gold (todas as tabelas acima)</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Dashboard Streamlit (dashboard/app.py + dashboard/screens/*.py, ADR 0021) e notebooks/03-07</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Leitura read-only via src/repositories/delta_repository.py (DeltaRepository) -- nunca escreve, save() levanta NotImplementedError deliberadamente.</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>src/repositories/delta_repository.py + dashboard/core/*</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D26"/>
+  <autoFilter ref="A1:D27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13140,7 +13624,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Produção -- scripts/run_ugc_mentions.py rodou contra a Apify de produção em 2026-09-19 (achado no PR #140), gravando Bronze/Silver/Gold com dado real; o piloto isolado (scripts/run_apify_mentions_pilot.py, data/pilot/*.json) continua existindo à parte, para confirmar campo/schema antes de qualquer mudança futura de contrato.</t>
+          <t>Produção -- coletado a cada extração do pipeline.py (extract_and_land, issue #211); primeira execução real em 2026-09-19 (PR #140); o piloto isolado (scripts/run_apify_mentions_pilot.py, data/pilot/*.json) continua existindo à parte, para confirmar campo/schema antes de qualquer mudança futura de contrato.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>ADR 0033</t>
+          <t>ADR 0034</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Publicação em que o comentário foi feito: 'reel' (comments_clean) ou 'post' (post_comments_clean) -- só nas linhas fonte == 'comentario'; nula em legenda/transcrição (issue #212, ADR 0033). Não confundir com `fonte`.</t>
+          <t>Publicação em que o comentário foi feito: 'reel' (comments_clean) ou 'post' (post_comments_clean) -- só nas linhas fonte == 'comentario'; nula em legenda/transcrição (issue #212, ADR 0034). Não confundir com `fonte`.</t>
         </is>
       </c>
     </row>
@@ -8685,7 +8685,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Publicação em que o comentário foi feito: 'reel' (comments_clean) ou 'post' (post_comments_clean) -- só nas linhas fonte == 'comentario'; nula em legenda/transcrição (issue #212, ADR 0033). Não confundir com `fonte`.</t>
+          <t>Publicação em que o comentário foi feito: 'reel' (comments_clean) ou 'post' (post_comments_clean) -- só nas linhas fonte == 'comentario'; nula em legenda/transcrição (issue #212, ADR 0034). Não confundir com `fonte`.</t>
         </is>
       </c>
     </row>

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -17,10 +17,10 @@
     <sheet name="Glossário de Métricas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabelas'!$A$1:$K$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Colunas - Bronze'!$A$1:$E$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabelas'!$A$1:$K$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Colunas - Bronze'!$A$1:$E$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Colunas - Silver'!$A$1:$E$96</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$206</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Linhagem'!$A$1:$D$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Actors Apify'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Glossário de Métricas'!$A$1:$E$14</definedName>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -514,14 +514,14 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Bronze -- append-only, fidelidade total ao retorno bruto do Apify (data/bronze/).</t>
+          <t>Bronze -- FIEL ao retorno da Apify (ADR 0039): o item completo vai na coluna `_raw`, além das colunas tipadas e dos metadados de ingestão; overwrite por Coleta, sem landing zone (data/bronze/).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Silver -- limpo e conformado a um contrato de tipos fechado; overwrite por execução (data/silver/).</t>
+          <t>Silver -- limpo e conformado a um contrato de tipos fechado; overwrite por Coleta, sem deduplicação entre execuções (data/silver/).</t>
         </is>
       </c>
     </row>
@@ -533,93 +533,100 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Coleta, Recorte e Snapshot (ADR 0039, módulo src/coleta/, CLI coleta.py) -- uma Coleta é uma extração segundo um Recorte; o Snapshot é a Coleta vigente com Bronze, Silver, Gold e manifesto.json, publicado num único commit do dataset privado do Hugging Face. Coletas anteriores ficam em tags. Não há landing zone nem histórico entre execuções (governor_nsm_history foi removida).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Legenda de Status (aba Tabelas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Produção -- escrita e lida por pelo menos um caminho de código de produção, com dado real esperado em data/.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Produção (ressalva) -- em produção, mas com uma limitação declarada explicitamente pelo próprio código-fonte (ex.: histórico curto demais para ser conclusivo) -- ver coluna Notas.</t>
+          <t>Produção -- escrita e lida por pelo menos um caminho de código de produção, com dado real esperado em data/.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Produção (ressalva) -- em produção, mas com uma limitação declarada explicitamente pelo próprio código-fonte (ex.: histórico curto demais para ser conclusivo) -- ver coluna Notas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>PILOTO -- contrato de schema definido e cobertura de teste com dado sintético, mas SEM caminho de escrita de produção ainda; nenhuma linha real esperada em data/ hoje. Nenhuma tabela está neste status no momento -- UGC de menções (ADR 0020 Ficha 8 / issue #93) saiu de PILOTO para Produção em 2026-09-19.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Contagem de tabelas</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Bronze: 4  |  Silver: 6  |  Gold: 17  |  Total: 27</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Bronze: 4  |  Silver: 7  |  Gold: 16  |  Total: 27</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Como navegar</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>1. Aba 'Tabelas' -- visão de 1 linha por tabela (grão, escrita, leitura, status, ADR).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2. Abas 'Colunas - Bronze/Silver/Gold' -- 1 linha por coluna de cada tabela da camada.</t>
+          <t>1. Aba 'Tabelas' -- visão de 1 linha por tabela (grão, escrita, leitura, status, ADR).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>3. Aba 'Linhagem' -- de onde cada tabela vem e o que a transformação aplica, incluindo o hop pela landing zone (data/landing/&lt;run_id&gt;/*.json) ANTES de qualquer escrita Bronze.</t>
+          <t>2. Abas 'Colunas - Bronze/Silver/Gold' -- 1 linha por coluna de cada tabela da camada.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>4. Aba 'Actors Apify' -- qual actor (slug + ID técnico) raspa cada entidade Bronze, com quais parâmetros REALMENTE usados em produção (src/data_extract/scraper.py), status produção/piloto e confiabilidade da fonte (cruzado com docs/research/apify-instagram-actors-cobra-mapping.md).</t>
+          <t>3. Aba 'Linhagem' -- de onde cada tabela vem e o que a transformação aplica, incluindo o Snapshot publicado no Hugging Face e a reconstrução na Lambda rebuild (não há landing zone).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>4. Aba 'Actors Apify' -- qual actor (slug + ID técnico) raspa cada entidade Bronze, com quais parâmetros REALMENTE usados em produção (src/data_extract/scraper.py), status produção/piloto e confiabilidade da fonte (cruzado com docs/research/apify-instagram-actors-cobra-mapping.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>5. Aba 'Glossário de Métricas' -- fórmula completa de cada métrica derivada (% ENGAJAMENTO, NSM, Score ICE, CMGR, retenção, Y da regressão, cluster_score, Escore composto, Score ICE por pauta).</t>
         </is>
@@ -636,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -727,17 +734,17 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por resultado bruto do scraper Apify para um perfil de governador, por execução -- append-only, nada é sobrescrito nem deduplicado nesta camada.</t>
+          <t>Uma linha por item do scraper Apify para um perfil de governador, de UMA Coleta -- a Bronze é gravada em overwrite por Coleta; nada se acumula entre Coletas.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>append</t>
+          <t>overwrite (por Coleta)</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/bronze_writer.py (BronzeWriter.write_profiles), chamado por pipeline.py</t>
+          <t>src/data_extract/bronze_writer.py (BronzeWriter.write_profiles), chamado por src/coleta/coletar.py via src/data_extract/ingestion.py::extract_and_land (CLI `coleta.py coletar`)</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -752,7 +759,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>ADR 0011 (landing zone/Bronze)</t>
+          <t>ADR 0039 (Bronze fiel); ADR 0011</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -762,7 +769,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Fidelidade total ao retorno do Apify -- nenhuma limpeza aqui; campos list/dict do Apify são serializados como JSON string (BronzeWriter._add_ingestion_metadata). Payload bruto arquivado em data/landing/&lt;run_id&gt;/profiles.json (ou /tmp/landing/... na Lambda) ANTES desta escrita -- ver aba Linhagem.</t>
+          <t>Bronze fiel (ADR 0039): a coluna `_raw` guarda o item COMPLETO da Apify como JSON string, inclusive campos que o schema tipado não modela -- nada é descartado; parsing e validação ficam na Silver. Nenhuma limpeza aqui; campos list/dict do Apify são serializados como JSON string nas colunas tipadas (BronzeWriter._add_ingestion_metadata). NÃO existe landing zone: o JSON bruto não é mais arquivado à parte (data/landing/ foi removida). Cada Coleta sobrescreve a Bronze da anterior; as Coletas antigas ficam em tags do dataset privado no Hugging Face (ver aba Linhagem).</t>
         </is>
       </c>
     </row>
@@ -784,17 +791,17 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por post de feed (imagem/vídeo/carrossel) retornado pelo scraper, por execução -- append-only.</t>
+          <t>Uma linha por post de feed (imagem/vídeo/carrossel) retornado pelo scraper, de UMA Coleta -- overwrite por Coleta.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>append</t>
+          <t>overwrite (por Coleta)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/bronze_writer.py (BronzeWriter.write_posts), chamado por pipeline.py</t>
+          <t>src/data_extract/bronze_writer.py (BronzeWriter.write_posts), chamado por src/coleta/coletar.py via src/data_extract/ingestion.py::extract_and_land (CLI `coleta.py coletar`)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -809,7 +816,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>ADR 0011</t>
+          <t>ADR 0039; ADR 0011</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -819,7 +826,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Desde a issue #212 guarda `latestComments` (comentários mais recentes do post, JSON string), fonte de post_comments_clean -- antes a coluna era descartada aqui e só havia comentário de Reels no projeto. Bronzes antigas recebem a coluna no append (schema_mode=merge), com linhas antigas nulas. Payload bruto arquivado em data/landing/&lt;run_id&gt;/posts.json (ou /tmp/landing/... na Lambda) ANTES desta escrita -- ver aba Linhagem. Perfil sem NENHUM post próprio (0 itens, não confundir com perfil sem `id`) gera item de erro `{"error": "no_items", "errorDescription": "Empty or private data..."}` -- caso real (2026-09): claudiocastrorj (verificado, 2M+ seguidores) tinha só marcações de terceiros na grade, zero posts/reels próprios publicados.</t>
+          <t>Desde a issue #212 guarda `latestComments` (comentários mais recentes do post, JSON string), fonte de post_comments_clean -- antes a coluna era descartada aqui e só havia comentário de Reels no projeto. Item completo da Apify preservado em `_raw` (Bronze fiel, ADR 0039); não há landing zone. Perfil sem NENHUM post próprio (0 itens, não confundir com perfil sem `id`) gera item de erro `{"error": "no_items", "errorDescription": "Empty or private data..."}` -- caso real (2026-09): claudiocastrorj (verificado, 2M+ seguidores) tinha só marcações de terceiros na grade, zero posts/reels próprios publicados.</t>
         </is>
       </c>
     </row>
@@ -841,17 +848,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por Reel retornado pelo scraper, por execução -- append-only.</t>
+          <t>Uma linha por Reel retornado pelo scraper, de UMA Coleta -- overwrite por Coleta.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>append</t>
+          <t>overwrite (por Coleta)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/bronze_writer.py (BronzeWriter.write_reels), chamado por pipeline.py</t>
+          <t>src/data_extract/bronze_writer.py (BronzeWriter.write_reels), chamado por src/coleta/coletar.py via src/data_extract/ingestion.py::extract_and_land (CLI `coleta.py coletar`)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -866,7 +873,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>ADR 0011; ADR 0020 Ficha 3 / issue #88 (transcript)</t>
+          <t>ADR 0039; ADR 0011; ADR 0020 Ficha 3 / issue #88 (transcript)</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -876,7 +883,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>`transcript` é nullable e só vem preenchido quando a execução ligou explicitamente a flag paga do actor (custo por minuto de vídeo) -- não confundir ausência com 'sem fala'. Payload bruto arquivado em data/landing/&lt;run_id&gt;/reels.json (ou /tmp/landing/... na Lambda) ANTES desta escrita -- ver aba Linhagem. Mesma ressalva de instagram_posts sobre perfil com zero itens próprios (`error: 'no_items'`).</t>
+          <t>`transcript` é nullable e só vem preenchido quando a execução ligou explicitamente a flag paga do actor (custo por minuto de vídeo) -- não confundir ausência com 'sem fala'. Item completo da Apify preservado em `_raw` (Bronze fiel, ADR 0039); não há landing zone. Mesma ressalva de instagram_posts sobre perfil com zero itens próprios (`error: 'no_items'`).</t>
         </is>
       </c>
     </row>
@@ -898,17 +905,17 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por post de TERCEIROS que marca/menciona o perfil do governador (nível 'Creating' do COBRA), por execução.</t>
+          <t>Uma linha por post de TERCEIROS que marca/menciona o perfil do governador (nível 'Creating' do COBRA), de UMA Coleta -- overwrite por Coleta.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>append</t>
+          <t>overwrite (por Coleta)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/bronze_writer.py (BronzeWriter.write_ugc_mentions), chamado por src/data_extract/ingestion.py::extract_and_land (pipeline.py, scripts/run_apify_backfill.py, lambdas/extract) -- issue #211</t>
+          <t>src/data_extract/bronze_writer.py (BronzeWriter.write_ugc_mentions), chamado por src/coleta/coletar.py via src/data_extract/ingestion.py::extract_and_land (CLI `coleta.py coletar`) -- issue #211</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -918,12 +925,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Produção -- coletada a cada extração do pipeline.py desde a issue #211 (antes, pelo script standalone scripts/run_ugc_mentions.py, removido; 1a execução real em 2026-09-19, PR #140)</t>
+          <t>Produção -- coletada a cada Coleta (`coleta.py coletar`, issue #211); 1a execução real em 2026-09-19 (PR #140). Na amostra de teste atual são poucos posts por governador; a coleta completa vem depois.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 8 / issue #93</t>
+          <t>ADR 0039; ADR 0020 Ficha 8 / issue #93</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -933,7 +940,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>O piloto obrigatório da issue #93 (scripts/run_apify_mentions_pilot.py) rodou de verdade em 2026-09-19 contra os 26 perfis com Instagram rastreável (119 posts, data/pilot/mentions_pilot_20260919T030401Z.json) -- grava em data/pilot/*.json, FORA do Delta Lake, não passa pela landing zone nem por BronzeWriter. O schema abaixo foi CORRIGIDO a partir desse resultado real: `authorUsername`/`authorIsVerified`/`isPaidPartnership`/`isAd`/`isAffiliate`/`matchTypes` da especificação original (issue #93) NÃO existem no retorno do actor -- removidos/substituídos por `ownerUsername`/`ownerFullName`/`ownerId`/`paidPartnership`/`taggedUsers` (nomes reais). Desde a issue #211 a coleta de UGC é a ÚLTIMA etapa de extract_and_land e é tolerante a falha (actor com erro ou lista vazia não descarta perfis/posts/reels já gravados); com --days, recebe o mesmo onlyPostsNewerThan (aceitação pelo actor não confirmada -- o pipeline filtra a Silver pela janela como salvaguarda).</t>
+          <t>O piloto obrigatório da issue #93 (script run_apify_mentions_pilot.py, removido na ADR 0039) rodou de verdade em 2026-09-19 contra os 26 perfis com Instagram rastreável (119 posts, data/pilot/mentions_pilot_20260919T030401Z.json) -- gravou em data/pilot/*.json, FORA do Delta Lake, sem passar por BronzeWriter. O schema abaixo foi CORRIGIDO a partir desse resultado real: `authorUsername`/`authorIsVerified`/`isPaidPartnership`/`isAd`/`isAffiliate`/`matchTypes` da especificação original (issue #93) NÃO existem no retorno do actor -- removidos/substituídos por `ownerUsername`/`ownerFullName`/`ownerId`/`paidPartnership`/`taggedUsers` (nomes reais). Desde a issue #211 a coleta de UGC é a ÚLTIMA etapa de extract_and_land e é tolerante a falha (actor com erro ou lista vazia não descarta perfis/posts/reels já gravados); com --days, recebe o mesmo onlyPostsNewerThan (aceitação pelo actor não confirmada -- o pipeline filtra a Silver pela janela como salvaguarda).</t>
         </is>
       </c>
     </row>
@@ -990,7 +997,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Linha sem `id` é descartada (não quebra a escrita da tabela inteira) E gera um `logger.warning` com o(s) username(s) afetado(s) -- achado real: o link morto do Espírito Santo (PR #132) gerava esse descarte silenciosamente até ser descoberto manualmente; `fullName` ausente cai para `username`, depois `inputUrl`, nunca fica nulo por acidente. `clean()` também filtra por `governor_usernames` (opcional, passado por pipeline.py via scripts.apify_backfill_shared.load_governor_usernames()) -- governador removido de governadores.xlsx some daqui e, em cascata, de toda a Gold derivada (achado original: PR #137).</t>
+          <t>Linha sem `id` é descartada (não quebra a escrita da tabela inteira) E gera um `logger.warning` com o(s) username(s) afetado(s) -- achado real: o link morto do Espírito Santo (PR #132) gerava esse descarte silenciosamente até ser descoberto manualmente; `fullName` ausente cai para `username`, depois `inputUrl`, nunca fica nulo por acidente. `clean()` também filtra por `governor_usernames` (opcional, passado por src/coleta via scripts.apify_backfill_shared.load_governor_usernames()) -- governador removido de governadores.xlsx some daqui e, em cascata, de toda a Gold derivada (achado original: PR #137).</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1200,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/comment_cleaner.py (CommentCleaner(origem='post').clean/write), chamado por pipeline.py</t>
+          <t>src/features/silver/comment_cleaner.py (CommentCleaner(origem='post').clean/write), chamado por src/coleta/derivacao.py (derivar_silver_gold)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>src/repositories/delta_repository.py::load_post_comments (scripts/run_modeling.py); pipeline.py repassa direto à modelagem (src/modeling/comment_sources.py::combine_comment_sources)</t>
+          <t>src/repositories/delta_repository.py::load_post_comments (scripts/run_modeling.py); `coleta.py coletar --modelar` repassa direto à modelagem (src/modeling/comment_sources.py::combine_comment_sources)</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1307,12 +1314,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/ugc_mention_cleaner.py (UGCMentionCleaner), chamado por pipeline.py (estágio Silver, a cada execução, inclusive com Bronze reaproveitada)</t>
+          <t>src/features/silver/ugc_mention_cleaner.py (UGCMentionCleaner), chamado por src/coleta/derivacao.py (derivar_silver_gold), a cada Coleta e na reconstrução da Lambda `rebuild`</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/ugc_mentions_aggregator.py, chamado por pipeline.py</t>
+          <t>src/features/gold/ugc_mentions_aggregator.py, chamado por src/coleta/derivacao.py</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1354,7 +1361,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por perfil de governador -- snapshot agregado da execução mais recente.</t>
+          <t>Uma linha por perfil de governador -- snapshot agregado da Coleta mais recente.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1411,17 +1418,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por perfil POR EXECUÇÃO do pipeline (mesmo schema de governor_engagement, mas em modo append) -- histórico acumulado ao longo do tempo.</t>
+          <t>Uma linha por perfil POR execução de derivação na mesma pasta de dados (mesmo schema de governor_engagement).</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>append</t>
+          <t>append em `coleta.py coletar`; overwrite na reconstrução (Lambda `rebuild`)</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/engagement_aggregator.py (mesmo EngagementAggregator, path diferente)</t>
+          <t>src/features/gold/engagement_aggregator.py (mesmo EngagementAggregator, path diferente), via src/coleta/derivacao.py (derivar_silver_gold, modo_historico)</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1446,7 +1453,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Nunca sobrescrita nem deduplicada por execução -- cresce indefinidamente; governor_engagement (sem sufixo) continua em overwrite para não quebrar consumidores existentes.</t>
+          <t>Em `coleta.py coletar` é gravada em append, mas a pasta de destino precisa estar vazia, então o Snapshot de uma Coleta nova começa com uma única execução; na reconstrução (Lambda `rebuild`) é overwrite, para ser idempotente (ADR 0039). A comparação entre Coletas distintas foi removida (ADR 0039, decisão 7); a comparação temporal vem das datas das publicações dentro de uma Coleta. governor_engagement (sem sufixo) é sempre overwrite.</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1770,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (ModelEnricher.write_profile_clusters_engagement), via src/modeling/orchestration.py::run_deterministic_modeling (pipeline.py --run-modeling / scripts/run_modeling.py) ou, isoladamente, via scripts/run_profile_clustering_engagement.py</t>
+          <t>src/features/gold/model_enricher.py (ModelEnricher.write_profile_clusters_engagement), via src/modeling/orchestration.py::run_deterministic_modeling (`coleta.py coletar --modelar` / scripts/run_modeling.py) ou, isoladamente, via scripts/run_profile_clustering_engagement.py</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1788,7 +1795,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Roda pós-Gold-de-engajamento (lê governor_engagement), dentro do mesmo estágio determinístico das demais tabelas de modelagem -- na Lambda serverless, é a etapa `model`, disparada depois de `load` (ver seção 3 do README). LIMITAÇÃO CORRIGIDA (2026-09-19): herdava o vazamento de governor_engagement (ver notas daquela tabela) -- agora que profiles_clean/posts_clean/reels_clean filtram contra governadores.xlsx atual, um governador removido nunca chega a ter governor_engagement calculado, então também não aparece mais aqui nem como 'par' na Tela 4 (Comparar perfis).</t>
+          <t>Roda pós-Gold-de-engajamento (lê governor_engagement), dentro do mesmo estágio determinístico das demais tabelas de modelagem -- a Lambda `model`, que também a rodava, foi removida (ADR 0039): a modelagem pesada é sempre local. LIMITAÇÃO CORRIGIDA (2026-09-19): herdava o vazamento de governor_engagement (ver notas daquela tabela) -- agora que profiles_clean/posts_clean/reels_clean filtram contra governadores.xlsx atual, um governador removido nunca chega a ter governor_engagement calculado, então também não aparece mais aqui nem como 'par' na Tela 4 (Comparar perfis).</t>
         </is>
       </c>
     </row>
@@ -2028,52 +2035,52 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_nsm_history</t>
+          <t>config/settings.py::GOLD_UGC_MENTIONS (data/gold/governor_ugc_mentions)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por perfil POR EXECUÇÃO do pipeline (mesmo schema de governor_nsm, mas em modo append) -- histórico acumulado ao longo do tempo.</t>
+          <t>Uma linha por post de UGC (grão fino -- agregação por governador é uma view em memória, não persistida).</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>append</t>
+          <t>overwrite</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/nsm_scorer.py (mesmo NsmScorer, path diferente)</t>
+          <t>src/features/gold/ugc_mentions_aggregator.py (GovernorUGCAggregator), chamado por src/coleta/derivacao.py (issue #211)</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>dashboard/core/data.py::load_nsm_history() -&gt; dashboard/screens/resumo_nsm.py (Resumo, sub-aba NSM, delta "vs. média histórica" do KPI Engajamento qualificado)</t>
+          <t>dashboard/screens/resumo_funil.py (sub-aba Funil do Resumo) via dashboard/core/data.py::load_ugc_mentions: o estágio Engage·Criar mostra o número de posts de UGC orgânico de cada governador, com selo 'piloto' (ADR 0032, que revisa a proibição original da issue #114). Com o teto padrão da Coleta (30 por coleção, issue #211) a contagem deixa de saturar no teto do piloto (5) e o comparativo do Engage passa a aparecer (a tela o esconde enquanto o máximo for &lt;= 5).</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Produção -- fecha lacuna que a ADR 0025 previu e adiou (ADR 0027 / issue #160)</t>
+          <t>Produção -- mesma execução real de 2026-09-19 de Bronze/Silver ugc_mentions</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 5 / ADR 0025 / ADR 0027 / issue #90 / issue #160</t>
+          <t>ADR 0020 Ficha 8 / issue #93</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Base de série temporal de NSM -- permite comparar o NSM da execução mais recente contra a média histórica de execuções anteriores, mesmo raciocínio de governor_engagement_history (ADR 0016).</t>
+          <t>UGC orgânico vs. publi paga por post, com `is_organic` derivado de `paidPartnership` -- separa apoio espontâneo de publi paga ANTES de qualquer agregação.</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Nunca sobrescrita nem deduplicada por execução -- cresce indefinidamente; governor_nsm (sem sufixo) continua em overwrite para não quebrar consumidores existentes. Precisa de &gt;= 2 execuções acumuladas para o primeiro delta aparecer no dashboard (mesmo critério de compare_vs_historical_average já usado por % engajamento/Seguidores).</t>
+          <t>`GovernorUGCAggregator.aggregate_by_governor` (a 'view' de contagem/engajamento médio por governador) nunca expõe `authorUsername` individual no agregado, por desenho -- privacidade de quem menciona o governador, não só do próprio governador. Piloto real (2026-09-19) confirmou que `paidPartnership` é o único campo de publi que o actor expõe -- `isAd`/`isAffiliate` não existem como conceitos distintos, removidos do schema.</t>
         </is>
       </c>
     </row>
@@ -2085,17 +2092,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>config/settings.py::GOLD_UGC_MENTIONS (data/gold/governor_ugc_mentions)</t>
+          <t>data/gold/governor_growth_metrics</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por post de UGC (grão fino -- agregação por governador é uma view em memória, não persistida).</t>
+          <t>Uma linha por perfil de governador -- snapshot recalculável a partir do histórico acumulado (sempre overwrite, nunca append).</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2105,32 +2112,32 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/ugc_mentions_aggregator.py (GovernorUGCAggregator), chamado por pipeline.py (estágio Gold, issue #211)</t>
+          <t>src/features/gold/model_enricher.py (write_growth_metrics), via scripts/run_growth_metrics.py e src/modeling/growth_history.py</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/resumo_funil.py (sub-aba Funil do Resumo) via dashboard/core/data.py::load_ugc_mentions: o estágio Engage·Criar mostra o número de posts de UGC orgânico de cada governador, com selo 'piloto' (ADR 0032, que revisa a proibição original da issue #114). Com o teto padrão do pipeline.py (30 por coleção, issue #211) a contagem deixa de saturar no teto do piloto (5) e o comparativo do Engage passa a aparecer (a tela o esconde enquanto o máximo for &lt;= 5).</t>
+          <t>dashboard/screens/resumo_nsm.py (KPIs de crescimento CMGR e retenção, Resumo sub-aba NSM) via dashboard/core/data.py::load_growth_metrics()</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Produção -- mesma execução real de 2026-09-19 de Bronze/Silver ugc_mentions</t>
+          <t>PRODUÇÃO, mas resultado marcado ILUSTRATIVO (ver notas) -- não sustenta conclusão definitiva ainda</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 8 / issue #93</t>
+          <t>ADR 0020 Ficha 7 / issue #92</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>UGC orgânico vs. publi paga por post, com `is_organic` derivado de `paidPartnership` -- separa apoio espontâneo de publi paga ANTES de qualquer agregação.</t>
+          <t>CMGR (crescimento mensal composto de seguidores) e retenção de sentimento positivo, calculados sobre governor_engagement_history/governor_sentiment_history.</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>`GovernorUGCAggregator.aggregate_by_governor` (a 'view' de contagem/engajamento médio por governador) nunca expõe `authorUsername` individual no agregado, por desenho -- privacidade de quem menciona o governador, não só do próprio governador. Piloto real (2026-09-19) confirmou que `paidPartnership` é o único campo de publi que o actor expõe -- `isAd`/`isAffiliate` não existem como conceitos distintos, removidos do schema.</t>
+          <t>`cmgr_confiavel`/`retencao_confiavel` são False sempre que houver menos de MIN_PERIODS_CONFIAVEL=6 execuções mensais acumuladas -- em 2026-09 o histórico ainda não acumulou o suficiente, então os valores validam a FÓRMULA, não sustentam conclusão real sobre crescimento dos perfis. `motivo`/`nota` explicam o porquê sempre que o valor for NaN ou não confiável.</t>
         </is>
       </c>
     </row>
@@ -2142,17 +2149,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_growth_metrics</t>
+          <t>data/gold/governor_scorecard</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por perfil de governador -- snapshot recalculável a partir do histórico acumulado (sempre overwrite, nunca append).</t>
+          <t>Uma linha por governador (um perfil por `inputUrl` normalizado) -- snapshot recalculável a partir da Silver/Gold atual, sempre overwrite.</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2162,32 +2169,32 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/model_enricher.py (write_growth_metrics), via scripts/run_growth_metrics.py e src/modeling/growth_history.py</t>
+          <t>src/modeling/governor_scorecard.py (GovernorScorecardScorer), via src/modeling/orchestration.py::run_deterministic_modeling (`coleta.py coletar --modelar` / scripts/run_modeling.py) ou, isoladamente, scripts/run_governor_scorecard.py</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/resumo_nsm.py (KPIs de crescimento CMGR e retenção, Resumo sub-aba NSM) via dashboard/core/data.py::load_growth_metrics()</t>
+          <t>dashboard/screens/resumo_scorecard.py (Resumo, sub-aba Scorecard) via dashboard/core/data.py::load_governor_scorecard() -- o dashboard só lê, nada é recalculado</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>PRODUÇÃO, mas resultado marcado ILUSTRATIVO (ver notas) -- não sustenta conclusão definitiva ainda</t>
+          <t>Produção -- com selo de confiabilidade: dimensão Consistência pendente nos 26 governadores no dado de 2026-10-04 (ver notas)</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>ADR 0020 Ficha 7 / issue #92</t>
+          <t>ADR 0030 / issue #184 (spec #182)</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>CMGR (crescimento mensal composto de seguidores) e retenção de sentimento positivo, calculados sobre governor_engagement_history/governor_sentiment_history.</t>
+          <t>Escore composto (0 a 100) dos governadores: soma ponderada de cinco dimensões normalizadas min-máx entre os perfis (Alcance, Ativação, Qualidade, Profundidade, Consistência), seguindo a lógica de indicadores compostos do OECD Handbook (indicador bruto -&gt; normalização -&gt; ponderação -&gt; agregação). Relativo ao grupo: mede posição entre pares, não desempenho absoluto.</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>`cmgr_confiavel`/`retencao_confiavel` são False sempre que houver menos de MIN_PERIODS_CONFIAVEL=6 execuções mensais acumuladas -- em 2026-09 o pipeline ainda não acumulou histórico suficiente, então os valores validam a FÓRMULA, não sustentam conclusão real sobre crescimento dos perfis. `motivo`/`nota` explicam o porquê sempre que o valor for NaN ou não confiável.</t>
+          <t>SELOS DE CONFIABILIDADE. (1) Alcance é medido em REPRODUÇÕES (plays: `videoPlayCount` dos reels), nunca em "visualizações únicas"; posts de feed não têm plays, então só reels entram em Alcance e Profundidade. (2) Consistência mede a TENDÊNCIA do engajamento médio por post por mês de publicação (CMGR de engajamento), NÃO crescimento de audiência -- o CMGR de audiência (seguidores entre coletas, `governor_growth_metrics.cmgr`) continua pendente e fora do escore. (3) Consistência exige &gt;= 4 meses completos com &gt;= 3 posts maduros (&gt;= 7 dias de vida); no dado de 2026-10-04 a Silver só tem ~226 posts de ago/set-2026 e NENHUM dos 26 governadores atinge isso, então `consistencia_pendente = True` e `consistencia`/`consistencia_norm` são nulas em todos: o escore usa as 4 dimensões restantes com peso 0,25 cada (com as 5, 0,20 cada) e `n_dimensoes = 4`. Isso muda sozinho conforme a Silver acumular histórico. (4) Perfil com menos de 4 dimensões disponíveis fica com `escore` e `ranking` nulos. (5) São 26 governadores (a Silver filtra governadores removidos de governadores.xlsx), não 27. Amplitude zero numa dimensão (todos iguais) normaliza para 50.</t>
         </is>
       </c>
     </row>
@@ -2199,17 +2206,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>content_topic_priority_score</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>data/gold/governor_scorecard</t>
+          <t>data/gold/content_topic_priority_score</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Uma linha por governador (um perfil por `inputUrl` normalizado) -- snapshot recalculável a partir da Silver/Gold atual, sempre overwrite.</t>
+          <t>Uma linha por PAUTA (tópico de discurso da legenda do reel) -- ranking global, todos os perfis combinados, não por governador.</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2219,94 +2226,37 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/governor_scorecard.py (GovernorScorecardScorer), via src/modeling/orchestration.py::run_deterministic_modeling (pipeline.py --run-modeling / scripts/run_modeling.py) ou, isoladamente, scripts/run_governor_scorecard.py</t>
+          <t>src/features/gold/content_topic_priority_scorer.py (ContentTopicPriorityScorer), via src/modeling/orchestration.py::run_deterministic_modeling (provisório, rótulos brutos) e refine_discourse_topics_with_gemini (recalculado com os rótulos refinados)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>dashboard/screens/resumo_scorecard.py (Resumo, sub-aba Scorecard) via dashboard/core/data.py::load_governor_scorecard() -- o dashboard só lê, nada é recalculado</t>
+          <t>dashboard/screens/produzir.py (fila de pautas de "O que produzir") via dashboard/core/data.py::load_content_topic_priority()</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Produção -- com selo de confiabilidade: dimensão Consistência pendente nos 26 governadores no dado de 2026-10-04 (ver notas)</t>
+          <t>Produção -- com selo de confiabilidade: rótulos de pauta ainda provisórios até o refino manual via Gemini ser rodado de verdade (ver notas)</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>ADR 0030 / issue #184 (spec #182)</t>
+          <t>ADR 0020 Ficha 6 (fórmula); ADR 0028; issue #190 / #191 (spec #182)</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Escore composto (0 a 100) dos governadores: soma ponderada de cinco dimensões normalizadas min-máx entre os perfis (Alcance, Ativação, Qualidade, Profundidade, Consistência), seguindo a lógica de indicadores compostos do OECD Handbook (indicador bruto -&gt; normalização -&gt; ponderação -&gt; agregação). Relativo ao grupo: mede posição entre pares, não desempenho absoluto.</t>
+          <t>Score ICE (Impacto x Confiança x Facilidade) por PAUTA: sobre qual assunto de conteúdo o público reagiu bem. Pauta = tópico de discurso da LEGENDA do reel; os comentários são ligados à pauta pelo reel (`id_reel`).</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>SELOS DE CONFIABILIDADE. (1) Alcance é medido em REPRODUÇÕES (plays: `videoPlayCount` dos reels), nunca em "visualizações únicas"; posts de feed não têm plays, então só reels entram em Alcance e Profundidade. (2) Consistência mede a TENDÊNCIA do engajamento médio por post por mês de publicação (CMGR de engajamento), NÃO crescimento de audiência -- o CMGR de audiência (seguidores entre coletas, `governor_growth_metrics.cmgr`) continua pendente e fora do escore. (3) Consistência exige &gt;= 4 meses completos com &gt;= 3 posts maduros (&gt;= 7 dias de vida); no dado de 2026-10-04 a Silver só tem ~226 posts de ago/set-2026 e NENHUM dos 26 governadores atinge isso, então `consistencia_pendente = True` e `consistencia`/`consistencia_norm` são nulas em todos: o escore usa as 4 dimensões restantes com peso 0,25 cada (com as 5, 0,20 cada) e `n_dimensoes = 4`. Isso muda sozinho conforme a Silver acumular histórico. (4) Perfil com menos de 4 dimensões disponíveis fica com `escore` e `ranking` nulos. (5) São 26 governadores (a Silver filtra governadores removidos de governadores.xlsx), não 27. Amplitude zero numa dimensão (todos iguais) normaliza para 50.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>content_topic_priority_score</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>data/gold/content_topic_priority_score</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Uma linha por PAUTA (tópico de discurso da legenda do reel) -- ranking global, todos os perfis combinados, não por governador.</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>overwrite</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>src/features/gold/content_topic_priority_scorer.py (ContentTopicPriorityScorer), via src/modeling/orchestration.py::run_deterministic_modeling (provisório, rótulos brutos) e refine_discourse_topics_with_gemini (recalculado com os rótulos refinados)</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>dashboard/screens/produzir.py (fila de pautas de "O que produzir") via dashboard/core/data.py::load_content_topic_priority()</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Produção -- com selo de confiabilidade: rótulos de pauta ainda provisórios até o refino manual via Gemini ser rodado de verdade (ver notas)</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>ADR 0020 Ficha 6 (fórmula); ADR 0028; issue #190 / #191 (spec #182)</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>Score ICE (Impacto x Confiança x Facilidade) por PAUTA: sobre qual assunto de conteúdo o público reagiu bem. Pauta = tópico de discurso da LEGENDA do reel; os comentários são ligados à pauta pelo reel (`id_reel`).</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
           <t>Cada reel pertence a uma única pauta (a da legenda; `governor_discourse_topics` tem reels duplicados, deduplicados por `id_reel`); comentários de reels sem pauta de legenda ficam de fora; o tópico de ruído (-1) não é pauta; a transcrição não define pauta (exige plano pago do coletor). `alcance_pauta` é PROXY por engajamento (soma de likesCount + repliesCount dos comentários), nunca "visualizações". `facilidade` fixa em 1,0 (v1, sem dado de custo de produção). O selo de prioridade do dashboard (Alta/Média/Cuidado) vem dos tercis de `score` sobre o ranking global de pautas; o score bruto nunca é exibido. SELO DE CONFIABILIDADE: o refino real dos rótulos via Gemini ainda não foi rodado -- até lá `Name` traz os rótulos provisórios do BERTopic (palavras-chave) e o tópico sem palavra alguma aparece como "sem assunto definido". O ICE é recalculado quando o refino do discurso roda (`scripts/refine_topics.py --target all|discourse`).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K29"/>
+  <autoFilter ref="A1:K28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2317,7 +2267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2782,7 +2732,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -2816,12 +2766,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>instagram_posts</t>
+          <t>instagram_profiles</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>_raw</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2831,12 +2781,12 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Bronze fiel (ADR 0039): o item COMPLETO retornado pela Apify, serializado como JSON string (ensure_ascii=False), inclusive campos que as colunas tipadas não modelam. Fonte para reprocessar a Silver sem nova extração; parsing e validação ficam na Silver. Substitui a antiga landing zone.</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2798,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ownerId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2863,7 +2813,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2825,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>ownerId</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2890,7 +2840,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil que publicou o post/reel/comentário.</t>
+          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2852,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2917,7 +2867,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Username do perfil que publicou o post/reel/comentário.</t>
         </is>
       </c>
     </row>
@@ -2929,12 +2879,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -2944,7 +2894,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2906,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2971,7 +2921,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
@@ -2983,12 +2933,12 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -2998,7 +2948,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -3010,7 +2960,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3025,7 +2975,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
+          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
         </is>
       </c>
     </row>
@@ -3037,7 +2987,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -3052,7 +3002,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3014,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>caption</t>
+          <t>shortCode</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3079,7 +3029,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Legenda/texto do post ou reel.</t>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
         </is>
       </c>
     </row>
@@ -3091,12 +3041,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>videoViewCount</t>
+          <t>caption</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -3106,7 +3056,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Número de views do vídeo (métrica bruta do Apify, distinta de videoPlayCount).</t>
+          <t>Legenda/texto do post ou reel.</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3068,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>videoViewCount</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3133,7 +3083,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
+          <t>Número de views do vídeo (métrica bruta do Apify, distinta de videoPlayCount).</t>
         </is>
       </c>
     </row>
@@ -3145,12 +3095,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>videoDuration</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -3160,7 +3110,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Duração do vídeo em segundos.</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -3172,12 +3122,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>locationName</t>
+          <t>videoDuration</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -3187,7 +3137,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Nome do local marcado no post (quando presente).</t>
+          <t>Duração do vídeo em segundos.</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3149,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>latestComments</t>
+          <t>locationName</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -3214,7 +3164,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Lista bruta (JSON) dos comentários mais recentes do reel ou post, retornada pelo Apify -- fonte de comments_clean (reels) e de post_comments_clean (posts de feed, issue #212).</t>
+          <t>Nome do local marcado no post (quando presente).</t>
         </is>
       </c>
     </row>
@@ -3226,22 +3176,22 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>latestComments</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Lista bruta (JSON) dos comentários mais recentes do reel ou post, retornada pelo Apify -- fonte de comments_clean (reels) e de post_comments_clean (posts de feed, issue #212).</t>
         </is>
       </c>
     </row>
@@ -3253,12 +3203,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -3268,7 +3218,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3230,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>_source</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3295,19 +3245,19 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>instagram_reels</t>
+          <t>instagram_posts</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>_source</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3317,24 +3267,24 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>instagram_reels</t>
+          <t>instagram_posts</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>ownerId</t>
+          <t>_raw</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3344,12 +3294,12 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
+          <t>Bronze fiel (ADR 0039): o item COMPLETO retornado pela Apify, serializado como JSON string (ensure_ascii=False), inclusive campos que as colunas tipadas não modelam. Fonte para reprocessar a Silver sem nova extração; parsing e validação ficam na Silver. Substitui a antiga landing zone.</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3311,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3376,7 +3326,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil que publicou o post/reel/comentário.</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3338,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>ownerId</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3403,7 +3353,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
         </is>
       </c>
     </row>
@@ -3415,12 +3365,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -3430,7 +3380,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>Username do perfil que publicou o post/reel/comentário.</t>
         </is>
       </c>
     </row>
@@ -3442,12 +3392,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -3457,7 +3407,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3419,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>videoViewCount</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3484,7 +3434,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Número de views do vídeo (métrica bruta do Apify, distinta de videoPlayCount).</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3446,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -3511,7 +3461,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -3523,12 +3473,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>videoDuration</t>
+          <t>videoViewCount</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -3538,7 +3488,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Duração do vídeo em segundos.</t>
+          <t>Número de views do vídeo (métrica bruta do Apify, distinta de videoPlayCount).</t>
         </is>
       </c>
     </row>
@@ -3550,12 +3500,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -3565,7 +3515,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3527,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>videoDuration</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -3592,7 +3542,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
+          <t>Duração do vídeo em segundos.</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3554,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3619,7 +3569,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3581,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>isSponsored</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -3646,7 +3596,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Flag de conteúdo patrocinado no Reel (bruto do Apify).</t>
+          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
         </is>
       </c>
     </row>
@@ -3658,12 +3608,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>isCommentsDisabled</t>
+          <t>shortCode</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -3673,7 +3623,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Se os comentários estão desabilitados no post/reel.</t>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3635,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>isPinned</t>
+          <t>isSponsored</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3700,7 +3650,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Se o reel está fixado no perfil.</t>
+          <t>Flag de conteúdo patrocinado no Reel (bruto do Apify).</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3662,12 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>latestComments</t>
+          <t>isCommentsDisabled</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -3727,7 +3677,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Lista bruta (JSON) dos comentários mais recentes do reel ou post, retornada pelo Apify -- fonte de comments_clean (reels) e de post_comments_clean (posts de feed, issue #212).</t>
+          <t>Se os comentários estão desabilitados no post/reel.</t>
         </is>
       </c>
     </row>
@@ -3739,12 +3689,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>transcript</t>
+          <t>isPinned</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -3754,7 +3704,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Transcrição de fala do reel, via flag paga includeTranscript do actor -- nullable (vídeo mudo/flag desligada).</t>
+          <t>Se o reel está fixado no perfil.</t>
         </is>
       </c>
     </row>
@@ -3766,22 +3716,22 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>latestComments</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Lista bruta (JSON) dos comentários mais recentes do reel ou post, retornada pelo Apify -- fonte de comments_clean (reels) e de post_comments_clean (posts de feed, issue #212).</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3743,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>transcript</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3803,12 +3753,12 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Transcrição de fala do reel, via flag paga includeTranscript do actor -- nullable (vídeo mudo/flag desligada).</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3770,12 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>_source</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -3835,19 +3785,19 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>instagram_reels</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3857,24 +3807,24 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>instagram_reels</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>_source</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3884,24 +3834,24 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>instagram_reels</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>_raw</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3911,12 +3861,12 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
+          <t>Bronze fiel (ADR 0039): o item COMPLETO retornado pela Apify, serializado como JSON string (ensure_ascii=False), inclusive campos que as colunas tipadas não modelam. Fonte para reprocessar a Silver sem nova extração; parsing e validação ficam na Silver. Substitui a antiga landing zone.</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3878,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>caption</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3943,7 +3893,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Legenda/texto do post ou reel.</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3905,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>mentions</t>
+          <t>shortCode</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3970,7 +3920,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Lista de usernames @-mencionados em legenda/comentário do post de UGC, serializada como JSON string -- só ~31% dos posts reais têm este campo preenchido.</t>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3932,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>taggedUsers</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3997,7 +3947,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Lista de objetos (um por pessoa marcada visualmente na foto/vídeo, com `username`/`full_name`/`is_verified`/`is_private`) do post de UGC, serializada como JSON string -- substitui o campo `matchTypes` (não existe no actor real); presente em ~69% dos posts, mais frequente que `mentions`.</t>
+          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
         </is>
       </c>
     </row>
@@ -4009,12 +3959,12 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>caption</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -4024,7 +3974,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Legenda/texto do post ou reel.</t>
         </is>
       </c>
     </row>
@@ -4036,12 +3986,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>mentions</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -4051,7 +4001,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>Lista de usernames @-mencionados em legenda/comentário do post de UGC, serializada como JSON string -- só ~31% dos posts reais têm este campo preenchido.</t>
         </is>
       </c>
     </row>
@@ -4063,12 +4013,12 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>taggedUsers</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -4078,7 +4028,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
+          <t>Lista de objetos (um por pessoa marcada visualmente na foto/vídeo, com `username`/`full_name`/`is_verified`/`is_private`) do post de UGC, serializada como JSON string -- substitui o campo `matchTypes` (não existe no actor real); presente em ~69% dos posts, mais frequente que `mentions`.</t>
         </is>
       </c>
     </row>
@@ -4090,12 +4040,12 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -4105,7 +4055,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -4117,12 +4067,12 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -4132,7 +4082,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Username de quem publicou o post de UGC (autor terceiro que marcou/mencionou o governador -- Bronze, nome real do actor apify/instagram-tagged-scraper). Normalizado para `authorUsername` na Silver.</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4094,12 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>ownerFullName</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -4159,7 +4109,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Nome completo de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4121,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>ownerId</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -4186,7 +4136,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil de quem publicou o post de UGC (autor terceiro, Bronze, confirmado pelo piloto real) -- distinto do `ownerId` de posts/reels, que é o próprio governador.</t>
+          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
         </is>
       </c>
     </row>
@@ -4198,12 +4148,12 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>paidPartnership</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -4213,7 +4163,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Flag de parceria paga (publi) declarada pelo Instagram no post de UGC -- único campo de publi que o actor real expõe (piloto 2026-09-19); `isAd`/`isAffiliate` da especificação original não existem.</t>
+          <t>Username de quem publicou o post de UGC (autor terceiro que marcou/mencionou o governador -- Bronze, nome real do actor apify/instagram-tagged-scraper). Normalizado para `authorUsername` na Silver.</t>
         </is>
       </c>
     </row>
@@ -4225,22 +4175,22 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>ownerFullName</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Nome completo de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4202,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>ownerId</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -4262,12 +4212,12 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Id do perfil de quem publicou o post de UGC (autor terceiro, Bronze, confirmado pelo piloto real) -- distinto do `ownerId` de posts/reels, que é o próprio governador.</t>
         </is>
       </c>
     </row>
@@ -4279,27 +4229,135 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
+          <t>paidPartnership</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Flag de parceria paga (publi) declarada pelo Instagram no post de UGC -- único campo de publi que o actor real expõe (piloto 2026-09-19); `isAd`/`isAffiliate` da especificação original não existem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>_ingested_at</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>timestamp[us, tz=UTC]</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>_run_id</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
           <t>_source</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>_raw</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Bronze fiel (ADR 0039): o item COMPLETO retornado pela Apify, serializado como JSON string (ensure_ascii=False), inclusive campos que as colunas tipadas não modelam. Fonte para reprocessar a Silver sem nova extração; parsing e validação ficam na Silver. Substitui a antiga landing zone.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E73"/>
+  <autoFilter ref="A1:E77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4694,7 +4752,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -5153,7 +5211,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5724,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -5990,7 +6048,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6372,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6561,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6939,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E217"/>
+  <dimension ref="A1:E206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7443,7 +7501,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -7956,7 +8014,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8446,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8878,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9148,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9364,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9580,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9742,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -9954,7 +10012,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10228,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10552,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10849,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -10825,12 +10883,12 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -10845,19 +10903,19 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>shortCode</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -10872,100 +10930,100 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Nome de usuário do perfil de Instagram.</t>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_positivos</t>
+          <t>governor_username</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários (fonte == 'comentario') com sentiment_label == 'positive' deste perfil.</t>
+          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_totais</t>
+          <t>authorUsername</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Número total de comentários (fonte == 'comentario') deste perfil.</t>
+          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>proporcao_positivos</t>
+          <t>caption</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios_positivos / n_comentarios_totais -- 0.0 quando o perfil não tem nenhum comentário (nunca NaN/erro).</t>
+          <t>Legenda do post de UGC (do autor terceiro, não do governador).</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>total_engajamento</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -10980,19 +11038,19 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Cópia de governor_engagement['TOTAL ENGAJAMENTO'] para este perfil, mantida para auditoria/contraste no dashboard.</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>count_posts</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -11007,51 +11065,51 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Cópia de governor_engagement['count'] para este perfil.</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>alcance_medio</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>total_engajamento / count_posts -- PROXY de alcance (intensidade de engajamento por post), não alcance/views real. 0.0 quando count_posts == 0.</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>nsm</t>
+          <t>is_organic</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -11061,24 +11119,24 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>proporcao_positivos × alcance_medio -- North Star Metric de engajamento QUALIFICADO (pondera qualidade de reação, não só volume).</t>
+          <t>Derivado de `paidPartnership`: True quando ausente/False -- separa apoio espontâneo de publi paga.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us]</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -11088,24 +11146,24 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>governor_nsm_history</t>
+          <t>governor_ugc_mentions</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -11115,7 +11173,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -11127,34 +11185,34 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -11169,24 +11227,24 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>governor_username</t>
+          <t>valor_inicial</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -11196,24 +11254,24 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
+          <t>Valor da métrica-base (followersCount) no primeiro mês-calendário com execução registrada.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>authorUsername</t>
+          <t>valor_final</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -11223,24 +11281,24 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
+          <t>Valor da métrica-base (followersCount) no último mês-calendário com execução registrada.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>caption</t>
+          <t>cmgr</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -11250,19 +11308,19 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Legenda do post de UGC (do autor terceiro, não do governador).</t>
+          <t>(valor_final / valor_inicial) ** (1 / n_meses) - 1 -- crescimento mensal composto. NaN quando não calculável (ver cmgr_motivo).</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>cmgr_n_periodos</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -11277,24 +11335,24 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Número de meses-calendário com execução registrada usados no cálculo do CMGR.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>cmgr_confiavel</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -11304,24 +11362,24 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>False sempre que cmgr_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL) -- sinaliza resultado ilustrativo, não conclusivo.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>cmgr_motivo</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -11331,51 +11389,51 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
+          <t>Motivo do CMGR ser NaN, quando aplicável: historico_insuficiente / periodo_zero / valor_inicial_invalido.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>is_organic</t>
+          <t>retencao</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Derivado de `paidPartnership`: True quando ausente/False -- separa apoio espontâneo de publi paga.</t>
+          <t>Média de valor_t/valor_(t-1) (capada em 1.0) do share mensal de sentimento positivo entre meses consecutivos -- 1.0 = manteve 100% (ou mais); mede o quanto do período anterior foi retido, não crescimento.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>retencao_n_periodos</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us]</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -11385,24 +11443,24 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
+          <t>Número de meses-calendário com execução registrada usados no cálculo da retenção.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>retencao_n_pares_validos</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -11412,24 +11470,24 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Número de pares de meses consecutivos válidos usados na média da retenção.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>governor_ugc_mentions</t>
+          <t>governor_growth_metrics</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>retencao_confiavel</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -11439,7 +11497,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>False sempre que retencao_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL).</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11509,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>retencao_motivo</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -11466,7 +11524,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Motivo da retenção ser NaN, quando aplicável (mesmas categorias do cmgr_motivo).</t>
         </is>
       </c>
     </row>
@@ -11478,22 +11536,22 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>valor_inicial</t>
+          <t>ilustrativo</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Valor da métrica-base (followersCount) no primeiro mês-calendário com execução registrada.</t>
+          <t>True enquanto o pipeline não tiver acumulado histórico real suficiente -- sinaliza que o valor valida a FÓRMULA, não sustenta conclusão definitiva no TCC.</t>
         </is>
       </c>
     </row>
@@ -11505,22 +11563,22 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>valor_final</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>Valor da métrica-base (followersCount) no último mês-calendário com execução registrada.</t>
+          <t>Texto explicando por que o resultado é (ou não) ilustrativo, para exibição direta em dashboard/relatório sem reprocessar nada.</t>
         </is>
       </c>
     </row>
@@ -11532,22 +11590,22 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>cmgr</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>(valor_final / valor_inicial) ** (1 / n_meses) - 1 -- crescimento mensal composto. NaN quando não calculável (ver cmgr_motivo).</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -11559,12 +11617,12 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>cmgr_n_periodos</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -11574,24 +11632,24 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Número de meses-calendário com execução registrada usados no cálculo do CMGR.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>cmgr_confiavel</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -11601,19 +11659,19 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>False sempre que cmgr_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL) -- sinaliza resultado ilustrativo, não conclusivo.</t>
+          <t>URL do perfil do governador (chave de junção; normalizada em minúsculas, sem espaços e sem barra final para cruzar Silver e Gold).</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>cmgr_motivo</t>
+          <t>username</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -11628,19 +11686,19 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>Motivo do CMGR ser NaN, quando aplicável: historico_insuficiente / periodo_zero / valor_inicial_invalido.</t>
+          <t>Username do perfil (de governor_engagement); pode ser nulo.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>retencao</t>
+          <t>alcance</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -11655,105 +11713,105 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Média de valor_t/valor_(t-1) (capada em 1.0) do share mensal de sentimento positivo entre meses consecutivos -- 1.0 = manteve 100% (ou mais); mede o quanto do período anterior foi retido, não crescimento.</t>
+          <t>Dimensão Alcance bruta: média de videoPlayCount (REPRODUÇÕES / plays, nunca "visualizações únicas") dos reels do perfil. Posts de feed não têm plays e não entram. Nulo sem reels com plays.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>retencao_n_periodos</t>
+          <t>ativacao</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>Número de meses-calendário com execução registrada usados no cálculo da retenção.</t>
+          <t>Dimensão Ativação bruta: média de likesCount dos reels / followersCount do perfil. Nulo sem reels ou sem seguidores.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>retencao_n_pares_validos</t>
+          <t>qualidade</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Número de pares de meses consecutivos válidos usados na média da retenção.</t>
+          <t>Dimensão Qualidade bruta: comentários positivos / comentários totais do perfil (só governor_sentiment com fonte == 'comentario'). Nulo sem comentários.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>retencao_confiavel</t>
+          <t>profundidade</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>False sempre que retencao_n_periodos &lt; 6 (MIN_PERIODS_CONFIAVEL).</t>
+          <t>Dimensão Profundidade bruta: média de commentsCount / média de videoPlayCount, ambas sobre os reels com plays (mesma base do Alcance). Nulo sem reels com plays.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>retencao_motivo</t>
+          <t>consistencia</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -11763,115 +11821,115 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Motivo da retenção ser NaN, quando aplicável (mesmas categorias do cmgr_motivo).</t>
+          <t>Dimensão Consistência bruta: CMGR de engajamento por data de publicação = exp(inclinação) - 1 da regressão log-linear sobre o engajamento médio por post (curtidas + comentários) de cada mês de publicação. Janela de até 12 meses completos (mês corrente excluído), mês válido com &gt;= 3 posts, posts com &lt; 7 dias de vida excluídos. Nula (pendente) com &lt; 4 meses válidos. NÃO é crescimento de audiência.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>ilustrativo</t>
+          <t>alcance_norm</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>True enquanto o pipeline não tiver acumulado histórico real suficiente -- sinaliza que o valor valida a FÓRMULA, não sustenta conclusão definitiva no TCC.</t>
+          <t>alcance normalizado min-máx 0-100 entre os perfis com a dimensão (100 = maior). Amplitude zero -&gt; 50. Nulo quando a dimensão bruta é nula.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>ativacao_norm</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Texto explicando por que o resultado é (ou não) ilustrativo, para exibição direta em dashboard/relatório sem reprocessar nada.</t>
+          <t>ativacao normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>qualidade_norm</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>qualidade normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>governor_growth_metrics</t>
+          <t>governor_scorecard</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>profundidade_norm</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>profundidade normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
         </is>
       </c>
     </row>
@@ -11883,22 +11941,22 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>consistencia_norm</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil do governador (chave de junção; normalizada em minúsculas, sem espaços e sem barra final para cruzar Silver e Gold).</t>
+          <t>consistencia normalizada min-máx 0-100 entre os perfis com a dimensão. Nula quando Consistência está pendente (hoje, todos os 26 governadores).</t>
         </is>
       </c>
     </row>
@@ -11910,22 +11968,22 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>consistencia_pendente</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil (de governor_engagement); pode ser nulo.</t>
+          <t>True quando a Consistência não pôde ser calculada (&lt; 4 meses válidos). Selo de confiabilidade: o escore daquele perfil usa só as outras dimensões, com os pesos renormalizados.</t>
         </is>
       </c>
     </row>
@@ -11937,22 +11995,22 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>alcance</t>
+          <t>consistencia_n_meses</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Dimensão Alcance bruta: média de videoPlayCount (REPRODUÇÕES / plays, nunca "visualizações únicas") dos reels do perfil. Posts de feed não têm plays e não entram. Nulo sem reels com plays.</t>
+          <t>Número de meses de publicação válidos (&gt;= 3 posts maduros, dentro da janela) que entraram, ou entrariam, no cálculo da Consistência.</t>
         </is>
       </c>
     </row>
@@ -11964,22 +12022,22 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>ativacao</t>
+          <t>n_dimensoes</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Dimensão Ativação bruta: média de likesCount dos reels / followersCount do perfil. Nulo sem reels ou sem seguidores.</t>
+          <t>Quantas das 5 dimensões normalizadas entraram no escore deste perfil (5, ou 4 com Consistência pendente). Perfil com &lt; 4 fica sem escore.</t>
         </is>
       </c>
     </row>
@@ -11991,7 +12049,7 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>qualidade</t>
+          <t>escore</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -12006,7 +12064,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Dimensão Qualidade bruta: comentários positivos / comentários totais do perfil (só governor_sentiment com fonte == 'comentario'). Nulo sem comentários.</t>
+          <t>Escore composto 0-100: média simples das dimensões normalizadas disponíveis (soma ponderada com pesos iguais: 0,20 com 5 dimensões, 0,25 com 4). Nulo com &lt; 4 dimensões. Relativo ao grupo de perfis.</t>
         </is>
       </c>
     </row>
@@ -12018,12 +12076,12 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>profundidade</t>
+          <t>ranking</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -12033,7 +12091,7 @@
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Dimensão Profundidade bruta: média de commentsCount / média de videoPlayCount, ambas sobre os reels com plays (mesma base do Alcance). Nulo sem reels com plays.</t>
+          <t>Posição do perfil pelo escore (1 = maior; desempate por inputUrl). Nulo quando o perfil não tem escore.</t>
         </is>
       </c>
     </row>
@@ -12045,22 +12103,22 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>consistencia</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Dimensão Consistência bruta: CMGR de engajamento por data de publicação = exp(inclinação) - 1 da regressão log-linear sobre o engajamento médio por post (curtidas + comentários) de cada mês de publicação. Janela de até 12 meses completos (mês corrente excluído), mês válido com &gt;= 3 posts, posts com &lt; 7 dias de vida excluídos. Nula (pendente) com &lt; 4 meses válidos. NÃO é crescimento de audiência.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -12072,66 +12130,66 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>alcance_norm</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>alcance normalizado min-máx 0-100 entre os perfis com a dimensão (100 = maior). Amplitude zero -&gt; 50. Nulo quando a dimensão bruta é nula.</t>
+          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>content_topic_priority_score</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>ativacao_norm</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>ativacao normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
+          <t>Id numérico do tópico de DISCURSO (BERTopic de legendas) que define a pauta -- espaço de ids distinto do tópico de comentário. O ruído (-1) nunca é pauta.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>content_topic_priority_score</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>qualidade_norm</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -12141,78 +12199,78 @@
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>qualidade normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
+          <t>Rótulo da pauta: tópico de discurso sem o prefixo de id; rótulo refinado via Gemini quando o refino do discurso rodou, palavras-chave separadas por vírgula quando provisório, ou "sem assunto definido" quando o tópico é degenerado.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>content_topic_priority_score</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>profundidade_norm</t>
+          <t>n_reels</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>profundidade normalizada min-máx 0-100 entre os perfis (mesma regra de alcance_norm).</t>
+          <t>Número de reels distintos cuja legenda pertence à pauta e que receberam ao menos um comentário.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>content_topic_priority_score</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>consistencia_norm</t>
+          <t>n_comentarios</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>consistencia normalizada min-máx 0-100 entre os perfis com a dimensão. Nula quando Consistência está pendente (hoje, todos os 26 governadores).</t>
+          <t>Número de comentários (fonte == 'comentario') dos reels da pauta -- cada reel conta numa única pauta, então os totais somam o total real de comentários com pauta.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>content_topic_priority_score</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>consistencia_pendente</t>
+          <t>n_comentarios_positivos</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -12222,19 +12280,19 @@
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>True quando a Consistência não pôde ser calculada (&lt; 4 meses válidos). Selo de confiabilidade: o escore daquele perfil usa só as outras dimensões, com os pesos renormalizados.</t>
+          <t>Comentários da pauta com sentiment_label == 'positive'.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>content_topic_priority_score</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>consistencia_n_meses</t>
+          <t>n_comentarios_negativos</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -12249,24 +12307,24 @@
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Número de meses de publicação válidos (&gt;= 3 posts maduros, dentro da janela) que entraram, ou entrariam, no cálculo da Consistência.</t>
+          <t>Comentários da pauta com sentiment_label == 'negative'.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>content_topic_priority_score</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>n_dimensoes</t>
+          <t>proporcao_sentimento_positivo</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -12276,78 +12334,78 @@
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Quantas das 5 dimensões normalizadas entraram no escore deste perfil (5, ou 4 com Consistência pendente). Perfil com &lt; 4 fica sem escore.</t>
+          <t>n_comentarios_positivos / n_comentarios.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>content_topic_priority_score</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>escore</t>
+          <t>alcance_pauta</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Escore composto 0-100: média simples das dimensões normalizadas disponíveis (soma ponderada com pesos iguais: 0,20 com 5 dimensões, 0,25 com 4). Nulo com &lt; 4 dimensões. Relativo ao grupo de perfis.</t>
+          <t>Soma de (likesCount + repliesCount) dos comentários da pauta -- PROXY por engajamento, não alcance nem visualizações reais.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>content_topic_priority_score</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>ranking</t>
+          <t>alcance_normalizado</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Posição do perfil pelo escore (1 = maior; desempate por inputUrl). Nulo quando o perfil não tem escore.</t>
+          <t>alcance_pauta / (alcance_pauta + 1) -- satura suavemente em [0,1), estável entre execuções.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>content_topic_priority_score</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -12357,24 +12415,24 @@
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
+          <t>Média de sentiment_score (confiança do classificador, não polaridade) dos comentários da pauta.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>governor_scorecard</t>
+          <t>content_topic_priority_score</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>_generated_at</t>
+          <t>impacto</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -12384,7 +12442,7 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
+          <t>alcance_normalizado x proporcao_sentimento_positivo.</t>
         </is>
       </c>
     </row>
@@ -12396,12 +12454,12 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>facilidade</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -12411,7 +12469,7 @@
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Id numérico do tópico de DISCURSO (BERTopic de legendas) que define a pauta -- espaço de ids distinto do tópico de comentário. O ruído (-1) nunca é pauta.</t>
+          <t>Fixa em 1,0 (v1) -- sem dado de custo de produção real.</t>
         </is>
       </c>
     </row>
@@ -12423,22 +12481,22 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>score</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>Rótulo da pauta: tópico de discurso sem o prefixo de id; rótulo refinado via Gemini quando o refino do discurso rodou, palavras-chave separadas por vírgula quando provisório, ou "sem assunto definido" quando o tópico é degenerado.</t>
+          <t>Impacto x Confiança x Facilidade -- base do selo de prioridade (Alta/Média/Cuidado por tercis do ranking global de pautas) na fila de "O que produzir".</t>
         </is>
       </c>
     </row>
@@ -12450,12 +12508,12 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>n_reels</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -12465,7 +12523,7 @@
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Número de reels distintos cuja legenda pertence à pauta e que receberam ao menos um comentário.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -12477,12 +12535,12 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>n_comentarios</t>
+          <t>_generated_at</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -12492,309 +12550,12 @@
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários (fonte == 'comentario') dos reels da pauta -- cada reel conta numa única pauta, então os totais somam o total real de comentários com pauta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="3" t="inlineStr">
-        <is>
-          <t>content_topic_priority_score</t>
-        </is>
-      </c>
-      <c r="B207" s="3" t="inlineStr">
-        <is>
-          <t>n_comentarios_positivos</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="inlineStr">
-        <is>
-          <t>int64</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>Comentários da pauta com sentiment_label == 'positive'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="3" t="inlineStr">
-        <is>
-          <t>content_topic_priority_score</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="inlineStr">
-        <is>
-          <t>n_comentarios_negativos</t>
-        </is>
-      </c>
-      <c r="C208" s="3" t="inlineStr">
-        <is>
-          <t>int64</t>
-        </is>
-      </c>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>Comentários da pauta com sentiment_label == 'negative'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>content_topic_priority_score</t>
-        </is>
-      </c>
-      <c r="B209" s="3" t="inlineStr">
-        <is>
-          <t>proporcao_sentimento_positivo</t>
-        </is>
-      </c>
-      <c r="C209" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="D209" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>n_comentarios_positivos / n_comentarios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="3" t="inlineStr">
-        <is>
-          <t>content_topic_priority_score</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
-        <is>
-          <t>alcance_pauta</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="inlineStr">
-        <is>
-          <t>int64</t>
-        </is>
-      </c>
-      <c r="D210" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="inlineStr">
-        <is>
-          <t>Soma de (likesCount + repliesCount) dos comentários da pauta -- PROXY por engajamento, não alcance nem visualizações reais.</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="3" t="inlineStr">
-        <is>
-          <t>content_topic_priority_score</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="inlineStr">
-        <is>
-          <t>alcance_normalizado</t>
-        </is>
-      </c>
-      <c r="C211" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="inlineStr">
-        <is>
-          <t>alcance_pauta / (alcance_pauta + 1) -- satura suavemente em [0,1), estável entre execuções.</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="3" t="inlineStr">
-        <is>
-          <t>content_topic_priority_score</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="inlineStr">
-        <is>
-          <t>confianca</t>
-        </is>
-      </c>
-      <c r="C212" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="D212" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>Média de sentiment_score (confiança do classificador, não polaridade) dos comentários da pauta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="3" t="inlineStr">
-        <is>
-          <t>content_topic_priority_score</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="inlineStr">
-        <is>
-          <t>impacto</t>
-        </is>
-      </c>
-      <c r="C213" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="D213" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>alcance_normalizado x proporcao_sentimento_positivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="3" t="inlineStr">
-        <is>
-          <t>content_topic_priority_score</t>
-        </is>
-      </c>
-      <c r="B214" s="3" t="inlineStr">
-        <is>
-          <t>facilidade</t>
-        </is>
-      </c>
-      <c r="C214" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="D214" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E214" s="3" t="inlineStr">
-        <is>
-          <t>Fixa em 1,0 (v1) -- sem dado de custo de produção real.</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="3" t="inlineStr">
-        <is>
-          <t>content_topic_priority_score</t>
-        </is>
-      </c>
-      <c r="B215" s="3" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="C215" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="D215" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="inlineStr">
-        <is>
-          <t>Impacto x Confiança x Facilidade -- base do selo de prioridade (Alta/Média/Cuidado por tercis do ranking global de pautas) na fila de "O que produzir".</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="3" t="inlineStr">
-        <is>
-          <t>content_topic_priority_score</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="inlineStr">
-        <is>
-          <t>_run_id</t>
-        </is>
-      </c>
-      <c r="C216" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D216" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>Identificador da execução do pipeline que gravou a linha (src/run_id.py) -- rastreia de qual chamada de pipeline.py/scripts/*.py a linha se origina.</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="3" t="inlineStr">
-        <is>
-          <t>content_topic_priority_score</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="inlineStr">
-        <is>
-          <t>_generated_at</t>
-        </is>
-      </c>
-      <c r="C217" s="3" t="inlineStr">
-        <is>
-          <t>timestamp[us, tz=UTC]</t>
-        </is>
-      </c>
-      <c r="D217" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
           <t>Timestamp UTC de quando a linha foi calculada/gravada na Gold -- distinto de _ingested_at (que é do dado bruto na Bronze).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E217"/>
+  <autoFilter ref="A1:E206"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12844,545 +12605,545 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Landing zone: data/landing/&lt;run_id&gt;/profiles.json (local) ou /tmp/landing/&lt;run_id&gt;/profiles.json (Lambda, efêmero)</t>
+          <t>Bronze: instagram_profiles</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Arquivamento do JSON bruto retornado pela Apify, SEM projeção de schema -- fidelidade total, inclusive de campos que a Bronze descarta silenciosamente. Sempre executado antes da escrita Bronze, para que uma falha nesta não implique perda do dado já raspado (e já pago).</t>
+          <t>Ingestão FIEL (ADR 0039): o item completo da Apify vai para a coluna `_raw` (JSON string), além das colunas tipadas e dos metadados de ingestão (_ingested_at/_run_id/_source); campos list/dict viram JSON string nas colunas tipadas. Não há landing zone. Gravada em overwrite por Coleta. Destino físico: data/bronze/instagram_profiles (local) ou s3://&lt;bucket&gt;/bronze/instagram_profiles (reconstrução na Lambda `rebuild`).</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/ingestion.py (archive_raw_json / extract_and_land)</t>
+          <t>src/coleta/coletar.py -&gt; src/data_extract/ingestion.py::extract_and_land -&gt; src/data_extract/bronze_writer.py</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Landing zone: profiles.json</t>
+          <t>Apify (apify/instagram-post-scraper -- ver aba Actors Apify)</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_profiles</t>
+          <t>Bronze: instagram_posts</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ingestão bruta + metadados de execução (_ingested_at/_run_id/_source); serialização de campos list/dict para JSON string. Destino físico: data/bronze/instagram_profiles (local) ou s3://&lt;bucket&gt;/bronze/instagram_profiles (Lambda, quando infra AWS aplicada).</t>
+          <t>Idem instagram_profiles (inclui `_raw`). Destino físico: data/bronze/instagram_posts (local) ou s3://&lt;bucket&gt;/bronze/instagram_posts (reconstrução).</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/bronze_writer.py</t>
+          <t>src/coleta/coletar.py -&gt; src/data_extract/ingestion.py::extract_and_land -&gt; src/data_extract/bronze_writer.py</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Apify (apify/instagram-post-scraper -- ver aba Actors Apify)</t>
+          <t>Apify (apify/instagram-reel-scraper -- ver aba Actors Apify)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Landing zone: data/landing/&lt;run_id&gt;/posts.json (local) ou /tmp/landing/&lt;run_id&gt;/posts.json (Lambda, efêmero)</t>
+          <t>Bronze: instagram_reels</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Idem profiles.json.</t>
+          <t>Idem instagram_profiles (inclui `_raw`); o item já traz latestComments e, opcionalmente, transcript (flag paga includeTranscript). Destino físico: data/bronze/instagram_reels (local) ou s3://&lt;bucket&gt;/bronze/instagram_reels (reconstrução).</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/ingestion.py (archive_raw_json / extract_and_land)</t>
+          <t>src/coleta/coletar.py -&gt; src/data_extract/ingestion.py::extract_and_land -&gt; src/data_extract/bronze_writer.py</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Landing zone: posts.json</t>
+          <t>Bronze: instagram_profiles</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_posts</t>
+          <t>Silver: profiles_clean</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Idem instagram_profiles. Destino físico: data/bronze/instagram_posts (local) ou s3://&lt;bucket&gt;/bronze/instagram_posts (Lambda).</t>
+          <t>Descarta linha sem id; drop de colunas de baixo valor (biografia, URLs de foto); cast para int32/bool não-nulo; deduplicação por id; fallback de fullName.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/bronze_writer.py</t>
+          <t>src/features/silver/profile_cleaner.py</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Apify (apify/instagram-reel-scraper -- ver aba Actors Apify)</t>
+          <t>Bronze: instagram_posts</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Landing zone: data/landing/&lt;run_id&gt;/reels.json (local) ou /tmp/landing/&lt;run_id&gt;/reels.json (Lambda, efêmero)</t>
+          <t>Silver: posts_clean</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Idem profiles.json; payload já inclui latestComments e, opcionalmente, transcript (flag paga includeTranscript).</t>
+          <t>Descarta linha sem id; parse de timestamp -&gt; data_hora (America/Sao_Paulo); preserva type_raw; fixa Tipo='FEED'; cast numérico; drop de colunas ruído (mentions/images/musicInfo/...); deduplicação por id.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/ingestion.py (archive_raw_json / extract_and_land)</t>
+          <t>src/features/silver/post_cleaner.py</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Landing zone: reels.json</t>
+          <t>Bronze: instagram_reels</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_reels</t>
+          <t>Silver: reels_clean</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Idem instagram_profiles; inclui latestComments e, opcionalmente, transcript (flag paga includeTranscript). Destino físico: data/bronze/instagram_reels (local) ou s3://&lt;bucket&gt;/bronze/instagram_reels (Lambda).</t>
+          <t>Mesma limpeza de posts_clean, mais: fixa Tipo='REELS'; calcula 'Total de Engajamento' (likes+comentários); propaga transcript sem alteração.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/bronze_writer.py</t>
+          <t>src/features/silver/post_cleaner.py</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_profiles</t>
+          <t>Bronze: instagram_reels (campo latestComments)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Silver: profiles_clean</t>
+          <t>Silver: comments_clean</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Descarta linha sem id; drop de colunas de baixo valor (biografia, URLs de foto); cast para int32/bool não-nulo; deduplicação por id; fallback de fullName.</t>
+          <t>Explode a lista JSON de comentários em uma linha por comentário; filtra texto &gt;= 512 caracteres; deduplicação por id_comment.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/profile_cleaner.py</t>
+          <t>src/features/silver/comment_cleaner.py</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_posts</t>
+          <t>Bronze: instagram_posts (campo latestComments)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Silver: posts_clean</t>
+          <t>Silver: post_comments_clean</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Descarta linha sem id; parse de timestamp -&gt; data_hora (America/Sao_Paulo); preserva type_raw; fixa Tipo='FEED'; cast numérico; drop de colunas ruído (mentions/images/musicInfo/...); deduplicação por id.</t>
+          <t>Mesma explosão de comments_clean (CommentCleaner(origem='post')), com `id_post` no lugar de `id_reel` -- tabela separada (issue #212).</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/post_cleaner.py</t>
+          <t>src/features/silver/comment_cleaner.py</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_reels</t>
+          <t>reference/governadores.xlsx</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Silver: reels_clean</t>
+          <t>Silver: governors_metadata</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Mesma limpeza de posts_clean, mais: fixa Tipo='REELS'; calcula 'Total de Engajamento' (likes+comentários); propaga transcript sem alteração.</t>
+          <t>Renomeia colunas (Governador-&gt;nome, Unidade Federativa-&gt;uf, Partido-&gt;partido, Link-&gt;inputUrl); dedup por inputUrl.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/post_cleaner.py</t>
+          <t>src/features/silver/governors_metadata_cleaner.py</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_reels (campo latestComments)</t>
+          <t>Silver: profiles_clean + posts_clean + reels_clean</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Silver: comments_clean</t>
+          <t>Gold: governor_engagement / governor_engagement_history</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Explode a lista JSON de comentários em uma linha por comentário; filtra texto &gt;= 512 caracteres; deduplicação por id_comment.</t>
+          <t>Agrega posts+reels por perfil; calcula TOTAL ENGAJAMENTO, % ENGAJAMENTO (ponderado por _WC_COMENTARIO), RECENCIA e FREQUENCIA.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/comment_cleaner.py</t>
+          <t>src/features/gold/engagement_aggregator.py</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Bronze: instagram_posts (campo latestComments)</t>
+          <t>Silver: comments_clean + post_comments_clean (unidas por combine_comment_sources, dedup por id_comment preferindo reel) + reels_clean/posts_clean (legenda/transcrição)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Silver: post_comments_clean</t>
+          <t>Gold: governor_sentiment / governor_sentiment_history</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Mesma explosão de comments_clean (CommentCleaner(origem='post')), com `id_post` no lugar de `id_reel` -- tabela separada (issue #212).</t>
+          <t>Classificação de sentimento (cardiffnlp/twitter-xlm-roberta-base-sentiment) + tópico BERTopic determinístico, por comentário/legenda/transcrição.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/comment_cleaner.py</t>
+          <t>src/modeling/sentiment.py + src/modeling/topics.py, gravado por src/features/gold/model_enricher.py</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>reference/governadores.xlsx</t>
+          <t>Gold: governor_sentiment</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Silver: governors_metadata</t>
+          <t>governor_sentiment (rótulos atualizados)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Renomeia colunas (Governador-&gt;nome, Unidade Federativa-&gt;uf, Partido-&gt;partido, Link-&gt;inputUrl); dedup por inputUrl.</t>
+          <t>Refinamento manual dos rótulos de tópico (Name) via Gemini -- reescreve a mesma tabela, não gera nova medição de sentimento.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>src/features/silver/governors_metadata_cleaner.py</t>
+          <t>scripts/refine_topics.py + src/modeling/gemini_refiner.py</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Silver: profiles_clean + posts_clean + reels_clean</t>
+          <t>Silver: reels_clean + posts_clean</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_engagement / governor_engagement_history</t>
+          <t>Gold: governor_clusters_reels + governor_clusters_posts</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Agrega posts+reels por perfil; calcula TOTAL ENGAJAMENTO, % ENGAJAMENTO (ponderado por _WC_COMENTARIO), RECENCIA e FREQUENCIA.</t>
+          <t>PCA (engajamento/duração) + AutoClusterHPO (KMeans/DBSCAN/Agglomerative eleito por score CVI) por post; duas tabelas separadas (uma por formato, issue #152) em vez de uma combinada, porque reels_clean/posts_clean se sobrepõem (mesmo Reel capturado por dois actors Apify distintos).</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/engagement_aggregator.py</t>
+          <t>src/modeling/clustering.py, gravado por src/features/gold/model_enricher.py</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Silver: comments_clean + post_comments_clean (unidas por combine_comment_sources, dedup por id_comment preferindo reel) + reels_clean/posts_clean (legenda/transcrição)</t>
+          <t>Gold: governor_engagement</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment / governor_sentiment_history</t>
+          <t>Gold: governor_profile_clusters_engagement</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Classificação de sentimento (cardiffnlp/twitter-xlm-roberta-base-sentiment) + tópico BERTopic determinístico, por comentário/legenda/transcrição.</t>
+          <t>Mesma pipeline PCA-&gt;AutoClusterHPO, mas com features agregadas por PERFIL em vez de por post.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/sentiment.py + src/modeling/topics.py, gravado por src/features/gold/model_enricher.py</t>
+          <t>src/modeling/profile_clustering.py, via src/modeling/orchestration.py::run_deterministic_modeling (ou isoladamente via scripts/run_profile_clustering_engagement.py)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment</t>
+          <t>Silver: posts_clean (caption/hashtags/Topic) + reels_clean + Gold: governor_engagement</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>governor_sentiment (rótulos atualizados)</t>
+          <t>Gold: post_performance_coefficients / post_performance_predictions</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Refinamento manual dos rótulos de tópico (Name) via Gemini -- reescreve a mesma tabela, não gera nova medição de sentimento.</t>
+          <t>Regressão Lasso de Y = (likes+comentários×Wc)/seguidores sobre preditores temporais/de formato/conteúdo, separada em grupo vídeo/estático; checagem de circularidade antes de treinar.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>scripts/refine_topics.py + src/modeling/gemini_refiner.py</t>
+          <t>src/modeling/post_performance.py</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Silver: reels_clean + posts_clean</t>
+          <t>Gold: governor_sentiment (fonte='comentario')</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_clusters_reels + governor_clusters_posts</t>
+          <t>Gold: topic_priority_score</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>PCA (engajamento/duração) + AutoClusterHPO (KMeans/DBSCAN/Agglomerative eleito por score CVI) por post; duas tabelas separadas (uma por formato, issue #152) em vez de uma combinada, porque reels_clean/posts_clean se sobrepõem (mesmo Reel capturado por dois actors Apify distintos).</t>
+          <t>Score ICE = Impacto(alcance_normalizado×%positivo) × Confiança(sentiment_score médio) × Facilidade(fixa=1.0), agregado por Topic.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/clustering.py, gravado por src/features/gold/model_enricher.py</t>
+          <t>src/features/gold/topic_priority_scorer.py</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_engagement</t>
+          <t>Gold: governor_sentiment (fonte='comentario') + governor_engagement</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_profile_clusters_engagement</t>
+          <t>Gold: governor_nsm</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Mesma pipeline PCA-&gt;AutoClusterHPO, mas com features agregadas por PERFIL em vez de por post.</t>
+          <t>NSM = (%comentários positivos) × (TOTAL ENGAJAMENTO / count, como proxy de alcance), merge outer por inputUrl.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/profile_clustering.py, via src/modeling/orchestration.py::run_deterministic_modeling (ou isoladamente via scripts/run_profile_clustering_engagement.py)</t>
+          <t>src/features/gold/nsm_scorer.py</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Silver: posts_clean (caption/hashtags/Topic) + reels_clean + Gold: governor_engagement</t>
+          <t>Gold: governor_sentiment (fonte='comentario') + governor_discourse_topics (fonte='legenda')</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Gold: post_performance_coefficients / post_performance_predictions</t>
+          <t>Gold: content_topic_priority_score</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Regressão Lasso de Y = (likes+comentários×Wc)/seguidores sobre preditores temporais/de formato/conteúdo, separada em grupo vídeo/estático; checagem de circularidade antes de treinar.</t>
+          <t>Score ICE por pauta: comentários ligados à pauta do reel (legenda) via id_reel; Impacto(alcance_normalizado x %positivo) x Confiança(sentiment_score médio) x Facilidade(fixa=1,0), agregado por Topic de discurso. Calculado de forma provisória no estágio determinístico e recalculado após o refino Gemini do discurso.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/post_performance.py</t>
+          <t>src/features/gold/content_topic_priority_scorer.py (orchestration.py::run_deterministic_modeling e refine_discourse_topics_with_gemini)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment (fonte='comentario')</t>
+          <t>Gold: governor_discourse_topics</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Gold: topic_priority_score</t>
+          <t>governor_discourse_topics (rótulos refinados)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Score ICE = Impacto(alcance_normalizado×%positivo) × Confiança(sentiment_score médio) × Facilidade(fixa=1.0), agregado por Topic.</t>
+          <t>Refinamento manual dos rótulos de tópico de discurso (Name) via Gemini; ruído (-1) mantido, tópico degenerado vira "sem assunto definido". Reescreve a mesma tabela e recalcula content_topic_priority_score.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/topic_priority_scorer.py</t>
+          <t>scripts/refine_topics.py (--target all|discourse) + src/modeling/orchestration.py::refine_discourse_topics_with_gemini</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment (fonte='comentario') + governor_engagement</t>
+          <t>Gold: governor_engagement (seguidores) + Silver: reels_clean + posts_clean + Gold: governor_sentiment (fonte='comentario')</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_nsm</t>
+          <t>Gold: governor_scorecard</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>NSM = (%comentários positivos) × (TOTAL ENGAJAMENTO / count, como proxy de alcance), merge outer por inputUrl.</t>
+          <t>Escore composto: 5 dimensões por governador (Alcance, Ativação, Qualidade, Profundidade, Consistência), normalização min-máx 0-100 entre os perfis, média simples das dimensões disponíveis (pesos iguais renormalizados), ranking. Consistência = CMGR de engajamento por data de publicação (pendente sem &gt;= 4 meses válidos).</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/nsm_scorer.py</t>
+          <t>src/modeling/governor_scorecard.py (orchestration.py::run_deterministic_modeling ou scripts/run_governor_scorecard.py)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_sentiment (fonte='comentario') + governor_discourse_topics (fonte='legenda')</t>
+          <t>Gold: governor_engagement_history + governor_sentiment_history</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Gold: content_topic_priority_score</t>
+          <t>Gold: governor_growth_metrics</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Score ICE por pauta: comentários ligados à pauta do reel (legenda) via id_reel; Impacto(alcance_normalizado x %positivo) x Confiança(sentiment_score médio) x Facilidade(fixa=1,0), agregado por Topic de discurso. Calculado de forma provisória no estágio determinístico e recalculado após o refino Gemini do discurso.</t>
+          <t>CMGR sobre followersCount mensal + retenção sobre share mensal de sentimento positivo; marca ilustrativo/confiavel conforme volume de histórico.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>src/features/gold/content_topic_priority_scorer.py (orchestration.py::run_deterministic_modeling e refine_discourse_topics_with_gemini)</t>
+          <t>src/modeling/growth_history.py + scripts/run_growth_metrics.py</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_discourse_topics</t>
+          <t>Apify (apify/instagram-tagged-scraper -- ver aba Actors Apify)</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>governor_discourse_topics (rótulos refinados)</t>
+          <t>Bronze/Silver/Gold: ugc_mentions / governor_ugc_mentions</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Refinamento manual dos rótulos de tópico de discurso (Name) via Gemini; ruído (-1) mantido, tópico degenerado vira "sem assunto definido". Reescreve a mesma tabela e recalcula content_topic_priority_score.</t>
+          <t>Coleta -&gt; Bronze fiel (com `_raw`) -&gt; Silver (dedup id/shortCode, normalização de handle, resolução de governor_username via mentions+taggedUsers) -&gt; Gold (is_organic a partir de paidPartnership), tudo sob o mesmo run_id da Coleta (a coleta de UGC é a última etapa de extract_and_land, tolerante a falha). Schema corrigido contra o piloto real de 2026-09-19 (script run_apify_mentions_pilot.py, removido na ADR 0039). Writer de produção rodou contra a Apify de produção pela 1a vez em 2026-09-19 (achado no PR #140, que corrigiu um FutureWarning de pandas revelado por esse dado real).</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>scripts/refine_topics.py (--target all|discourse) + src/modeling/orchestration.py::refine_discourse_topics_with_gemini</t>
+          <t>src/data_extract/ingestion.py::extract_and_land + src/data_extract/bronze_writer.py + src/features/silver/ugc_mention_cleaner.py + src/features/gold/ugc_mentions_aggregator.py, orquestrados por src/coleta/coletar.py e src/coleta/derivacao.py (issue #211)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_engagement (seguidores) + Silver: reels_clean + posts_clean + Gold: governor_sentiment (fonte='comentario')</t>
+          <t>Snapshot local (Bronze + Silver + Gold + manifesto.json)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_scorecard</t>
+          <t>Hugging Face (dataset privado): main = Coleta vigente; Coletas anteriores em tags</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Escore composto: 5 dimensões por governador (Alcance, Ativação, Qualidade, Profundidade, Consistência), normalização min-máx 0-100 entre os perfis, média simples das dimensões disponíveis (pesos iguais renormalizados), ranking. Consistência = CMGR de engajamento por data de publicação (pendente sem &gt;= 4 meses válidos).</t>
+          <t>Publicação do Snapshot inteiro como um único commit de substituição na main e criação da tag da Coleta (nada é apagado nem reescrito por force-push). O manifesto traz identidade, Recorte, cobertura real, custo e contagem de linhas das tabelas derivadas -- sem conteúdo nem segredos.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/governor_scorecard.py (orchestration.py::run_deterministic_modeling ou scripts/run_governor_scorecard.py)</t>
+          <t>src/coleta/hf.py + src/coleta/manifesto.py (CLI `coleta.py publicar|restaurar|listar|baixar`)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_engagement_history + governor_sentiment_history</t>
+          <t>Hugging Face: tag de uma Coleta</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Gold: governor_growth_metrics</t>
+          <t>S3: bronze/, silver/ e gold/ (Delta) -- Lambda `rebuild`</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>CMGR sobre followersCount mensal + retenção sobre share mensal de sentimento positivo; marca ilustrativo/confiavel conforme volume de histórico.</t>
+          <t>Baixa o Snapshot da tag e reconstrói Bronze, Silver e Gold de engajamento/UGC no S3, só com etapas determinísticas (sem Apify e sem modelagem pesada). Invocação sempre manual; a nuvem não extrai nem agenda.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>src/modeling/growth_history.py + scripts/run_growth_metrics.py</t>
+          <t>lambdas/rebuild/handler.py + src/coleta/reconstruir.py + src/coleta/derivacao.py</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Apify (apify/instagram-tagged-scraper -- ver aba Actors Apify)</t>
+          <t>Hugging Face: main (ou revisão HF_DATASET_REVISAO)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Bronze/Silver/Gold: ugc_mentions / governor_ugc_mentions</t>
+          <t>data/silver e data/gold do app publicado (Streamlit Cloud)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Coleta -&gt; landing zone -&gt; Bronze -&gt; Silver (dedup id/shortCode, normalização de handle, resolução de governor_username via mentions+taggedUsers) -&gt; Gold (is_organic a partir de paidPartnership), tudo sob o mesmo run_id da extração principal (coleta de UGC é a última etapa de extract_and_land, tolerante a falha). Schema corrigido contra o piloto real (scripts/run_apify_mentions_pilot.py, 2026-09-19, data/pilot/*.json, fora do Delta Lake). Writer de produção rodou contra a Apify de produção pela 1a vez em 2026-09-19 (achado no PR #140, que corrigiu um FutureWarning de pandas revelado por esse dado real).</t>
+          <t>O dashboard baixa só Silver, Gold e manifesto.json da Coleta vigente (ou da tag/commit pedido) na inicialização.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>src/data_extract/ingestion.py::extract_and_land + src/data_extract/bronze_writer.py + src/features/silver/ugc_mention_cleaner.py + src/features/gold/ugc_mentions_aggregator.py, orquestrados por pipeline.py (issue #211)</t>
+          <t>src/publicacao_hf.py + dashboard/core/bootstrap_dados.py</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13306,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>username=&lt;usernames&gt;, resultsLimit=30 (ScraperConfig.results_limit) + extra_run_input opcional (ex.: onlyPostsNewerThan, usado por scripts/run_apify_backfill.py para recorte incremental).</t>
+          <t>username=&lt;usernames&gt;, resultsLimit=30 (ScraperConfig.results_limit) + extra_run_input opcional (ex.: onlyPostsNewerThan, usado por src/coleta/coletar.py para o Recorte por janela relativa).</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -13624,7 +13385,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Produção -- coletado a cada extração do pipeline.py (extract_and_land, issue #211); primeira execução real em 2026-09-19 (PR #140); o piloto isolado (scripts/run_apify_mentions_pilot.py, data/pilot/*.json) continua existindo à parte, para confirmar campo/schema antes de qualquer mudança futura de contrato.</t>
+          <t>Produção -- coletado a cada Coleta (`coleta.py coletar`, via extract_and_land, issue #211); primeira execução real em 2026-09-19 (PR #140). O script de piloto isolado (run_apify_mentions_pilot.py) foi removido na ADR 0039.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">

--- a/reference/dicionario_de_dados_medallion.xlsx
+++ b/reference/dicionario_de_dados_medallion.xlsx
@@ -18,11 +18,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabelas'!$A$1:$K$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Colunas - Bronze'!$A$1:$E$77</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Colunas - Silver'!$A$1:$E$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Colunas - Bronze'!$A$1:$E$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Colunas - Silver'!$A$1:$E$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Colunas - Gold'!$A$1:$E$206</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Linhagem'!$A$1:$D$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Actors Apify'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Actors Apify'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Glossário de Métricas'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2267,7 +2267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>latestComments</t>
+          <t>isPinned</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Lista bruta (JSON) dos comentários mais recentes do reel ou post, retornada pelo Apify -- fonte de comments_clean (reels) e de post_comments_clean (posts de feed, issue #212).</t>
+          <t>Se o reel está fixado no perfil.</t>
         </is>
       </c>
     </row>
@@ -3203,22 +3203,22 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>latestComments</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Lista bruta (JSON) dos comentários mais recentes do reel ou post, retornada pelo Apify -- fonte de comments_clean (reels) e de post_comments_clean (posts de feed, issue #212).</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>_source</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>_raw</t>
+          <t>_source</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3299,19 +3299,19 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Bronze fiel (ADR 0039): o item COMPLETO retornado pela Apify, serializado como JSON string (ensure_ascii=False), inclusive campos que as colunas tipadas não modelam. Fonte para reprocessar a Silver sem nova extração; parsing e validação ficam na Silver. Substitui a antiga landing zone.</t>
+          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>instagram_reels</t>
+          <t>instagram_posts</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>_raw</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Bronze fiel (ADR 0039): o item COMPLETO retornado pela Apify, serializado como JSON string (ensure_ascii=False), inclusive campos que as colunas tipadas não modelam. Fonte para reprocessar a Silver sem nova extração; parsing e validação ficam na Silver. Substitui a antiga landing zone.</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>ownerId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>ownerId</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil que publicou o post/reel/comentário.</t>
+          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Username do perfil que publicou o post/reel/comentário.</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>videoViewCount</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Número de views do vídeo (métrica bruta do Apify, distinta de videoPlayCount).</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>videoViewCount</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
+          <t>Número de views do vídeo (métrica bruta do Apify, distinta de videoPlayCount).</t>
         </is>
       </c>
     </row>
@@ -3527,12 +3527,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>videoDuration</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Duração do vídeo em segundos.</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -3554,12 +3554,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>videoDuration</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
+          <t>Duração do vídeo em segundos.</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
+          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
         </is>
       </c>
     </row>
@@ -3635,12 +3635,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>isSponsored</t>
+          <t>shortCode</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Flag de conteúdo patrocinado no Reel (bruto do Apify).</t>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>isCommentsDisabled</t>
+          <t>isSponsored</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Se os comentários estão desabilitados no post/reel.</t>
+          <t>Flag de conteúdo patrocinado no Reel (bruto do Apify).</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>isPinned</t>
+          <t>isCommentsDisabled</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Se o reel está fixado no perfil.</t>
+          <t>Se os comentários estão desabilitados no post/reel.</t>
         </is>
       </c>
     </row>
@@ -3716,12 +3716,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>latestComments</t>
+          <t>isPinned</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Lista bruta (JSON) dos comentários mais recentes do reel ou post, retornada pelo Apify -- fonte de comments_clean (reels) e de post_comments_clean (posts de feed, issue #212).</t>
+          <t>Se o reel está fixado no perfil.</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>transcript</t>
+          <t>latestComments</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Transcrição de fala do reel, via flag paga includeTranscript do actor -- nullable (vídeo mudo/flag desligada).</t>
+          <t>Lista bruta (JSON) dos comentários mais recentes do reel ou post, retornada pelo Apify -- fonte de comments_clean (reels) e de post_comments_clean (posts de feed, issue #212).</t>
         </is>
       </c>
     </row>
@@ -3770,22 +3770,22 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>transcript</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Transcrição de fala do reel, via flag paga includeTranscript do actor -- nullable (vídeo mudo/flag desligada).</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>_source</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>_raw</t>
+          <t>_source</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3866,19 +3866,19 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Bronze fiel (ADR 0039): o item COMPLETO retornado pela Apify, serializado como JSON string (ensure_ascii=False), inclusive campos que as colunas tipadas não modelam. Fonte para reprocessar a Silver sem nova extração; parsing e validação ficam na Silver. Substitui a antiga landing zone.</t>
+          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>instagram_reels</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>_raw</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Bronze fiel (ADR 0039): o item COMPLETO retornado pela Apify, serializado como JSON string (ensure_ascii=False), inclusive campos que as colunas tipadas não modelam. Fonte para reprocessar a Silver sem nova extração; parsing e validação ficam na Silver. Substitui a antiga landing zone.</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>shortCode</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>caption</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Legenda/texto do post ou reel.</t>
+          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>mentions</t>
+          <t>caption</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Lista de usernames @-mencionados em legenda/comentário do post de UGC, serializada como JSON string -- só ~31% dos posts reais têm este campo preenchido.</t>
+          <t>Legenda/texto do post ou reel.</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>taggedUsers</t>
+          <t>mentions</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Lista de objetos (um por pessoa marcada visualmente na foto/vídeo, com `username`/`full_name`/`is_verified`/`is_private`) do post de UGC, serializada como JSON string -- substitui o campo `matchTypes` (não existe no actor real); presente em ~69% dos posts, mais frequente que `mentions`.</t>
+          <t>Lista de usernames @-mencionados em legenda/comentário do post de UGC, serializada como JSON string -- só ~31% dos posts reais têm este campo preenchido.</t>
         </is>
       </c>
     </row>
@@ -4040,12 +4040,12 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>taggedUsers</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Lista de objetos (um por pessoa marcada visualmente na foto/vídeo, com `username`/`full_name`/`is_verified`/`is_private`) do post de UGC, serializada como JSON string -- substitui o campo `matchTypes` (não existe no actor real); presente em ~69% dos posts, mais frequente que `mentions`.</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Username de quem publicou o post de UGC (autor terceiro que marcou/mencionou o governador -- Bronze, nome real do actor apify/instagram-tagged-scraper). Normalizado para `authorUsername` na Silver.</t>
+          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>ownerFullName</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Nome completo de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
+          <t>Username de quem publicou o post de UGC (autor terceiro que marcou/mencionou o governador -- Bronze, nome real do actor apify/instagram-tagged-scraper). Normalizado para `authorUsername` na Silver.</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>ownerId</t>
+          <t>ownerFullName</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil de quem publicou o post de UGC (autor terceiro, Bronze, confirmado pelo piloto real) -- distinto do `ownerId` de posts/reels, que é o próprio governador.</t>
+          <t>Nome completo de quem publicou o post de UGC (Bronze, confirmado pelo piloto real).</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>paidPartnership</t>
+          <t>ownerId</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Flag de parceria paga (publi) declarada pelo Instagram no post de UGC -- único campo de publi que o actor real expõe (piloto 2026-09-19); `isAd`/`isAffiliate` da especificação original não existem.</t>
+          <t>Id do perfil de quem publicou o post de UGC (autor terceiro, Bronze, confirmado pelo piloto real) -- distinto do `ownerId` de posts/reels, que é o próprio governador.</t>
         </is>
       </c>
     </row>
@@ -4256,22 +4256,22 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>paidPartnership</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Flag de parceria paga (publi) declarada pelo Instagram no post de UGC -- único campo de publi que o actor real expõe (piloto 2026-09-19); `isAd`/`isAffiliate` da especificação original não existem.</t>
         </is>
       </c>
     </row>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>_source</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
@@ -4337,27 +4337,54 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
+          <t>_source</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Origem do dado bruto -- sempre 'apify' hoje (src/data_extract/scraper.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
           <t>_raw</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>Bronze fiel (ADR 0039): o item COMPLETO retornado pela Apify, serializado como JSON string (ensure_ascii=False), inclusive campos que as colunas tipadas não modelam. Fonte para reprocessar a Silver sem nova extração; parsing e validação ficam na Silver. Substitui a antiga landing zone.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E77"/>
+  <autoFilter ref="A1:E78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4368,7 +4395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5169,22 +5196,22 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>isPinned</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Se o reel está fixado no perfil.</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5223,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -5211,7 +5238,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5250,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>_source_layer</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5238,19 +5265,19 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>reels_clean</t>
+          <t>posts_clean</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>_source_layer</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -5265,7 +5292,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5304,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>ownerId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5292,7 +5319,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5331,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>ownerId</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -5319,7 +5346,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil que publicou o post/reel/comentário.</t>
+          <t>Id do perfil (Bronze/Instagram) que publicou o post/reel.</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5358,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -5341,12 +5368,12 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Username do perfil que publicou o post/reel/comentário.</t>
         </is>
       </c>
     </row>
@@ -5358,22 +5385,22 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5412,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -5400,7 +5427,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5439,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -5422,12 +5449,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -5439,12 +5466,12 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>videoDuration</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5454,7 +5481,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Duração do vídeo em segundos.</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -5466,22 +5493,22 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>videoDuration</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us]</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
+          <t>Duração do vídeo em segundos.</t>
         </is>
       </c>
     </row>
@@ -5493,12 +5520,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Tipo</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us]</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -5508,7 +5535,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Granularidade fixada pelo cleaner: 'FEED' (posts_clean) ou 'REELS' (reels_clean) -- não confundir com `type_raw` (bruto do Apify).</t>
+          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5547,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>type_raw</t>
+          <t>Tipo</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -5530,12 +5557,12 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Campo bruto `type` do Apify (Image/Video/Sidecar), preservado antes de `Tipo` (FEED/REELS) ser atribuído -- preditor de Formato da regressão de performance-por-post.</t>
+          <t>Granularidade fixada pelo cleaner: 'FEED' (posts_clean) ou 'REELS' (reels_clean) -- não confundir com `type_raw` (bruto do Apify).</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5574,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>type_raw</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -5562,7 +5589,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>Campo bruto `type` do Apify (Image/Video/Sidecar), preservado antes de `Tipo` (FEED/REELS) ser atribuído -- preditor de Formato da regressão de performance-por-post.</t>
         </is>
       </c>
     </row>
@@ -5574,12 +5601,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>isSponsored</t>
+          <t>shortCode</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -5589,7 +5616,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Flag de conteúdo patrocinado no Reel (bruto do Apify).</t>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5628,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>isCommentsDisabled</t>
+          <t>isSponsored</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -5616,7 +5643,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Se os comentários estão desabilitados no post/reel.</t>
+          <t>Flag de conteúdo patrocinado no Reel (bruto do Apify).</t>
         </is>
       </c>
     </row>
@@ -5628,22 +5655,22 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Total de Engajamento</t>
+          <t>isCommentsDisabled</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>likesCount + commentsCount deste reel (PostCleaner.clean_reels) -- por-REEL, insumo do PCA/AutoClusterHPO. Não confundir com 'TOTAL ENGAJAMENTO' (maiúsculo, com espaço) de governor_engagement, que é por-PERFIL agregado.</t>
+          <t>Se os comentários estão desabilitados no post/reel.</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5682,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>transcript</t>
+          <t>isPinned</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -5670,7 +5697,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Transcrição de fala do reel, via flag paga includeTranscript do actor -- nullable (vídeo mudo/flag desligada).</t>
+          <t>Se o reel está fixado no perfil.</t>
         </is>
       </c>
     </row>
@@ -5682,12 +5709,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>Total de Engajamento</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -5697,7 +5724,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>likesCount + commentsCount deste reel (PostCleaner.clean_reels) -- por-REEL, insumo do PCA/AutoClusterHPO. Não confundir com 'TOTAL ENGAJAMENTO' (maiúsculo, com espaço) de governor_engagement, que é por-PERFIL agregado.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5736,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>transcript</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -5719,12 +5746,12 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
+          <t>Transcrição de fala do reel, via flag paga includeTranscript do actor -- nullable (vídeo mudo/flag desligada).</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5763,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>_source_layer</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -5751,19 +5778,19 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>comments_clean</t>
+          <t>reels_clean</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>id_reel</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -5773,24 +5800,24 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Id da publicação (reel ou post) de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean; em governor_sentiment, comentários de posts (origem_comentario == 'post') também usam esta coluna.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>comments_clean</t>
+          <t>reels_clean</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>id_comment</t>
+          <t>_source_layer</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -5800,12 +5827,12 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Id único do comentário individual (pós-explosão de latestComments).</t>
+          <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5844,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>id_reel</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -5832,7 +5859,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Texto avaliado -- comentário, legenda ou transcrição, dependendo da tabela/coluna `fonte`.</t>
+          <t>Id da publicação (reel ou post) de origem do comentário/tópico -- chave de junção com reels_clean/posts_clean; em governor_sentiment, comentários de posts (origem_comentario == 'post') também usam esta coluna.</t>
         </is>
       </c>
     </row>
@@ -5844,22 +5871,22 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>comprimento texto</t>
+          <t>id_comment</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Número de caracteres de `text` -- usado para filtrar comentários &gt;= 512 caracteres (CommentCleaner.MAX_TEXT_LENGTH).</t>
+          <t>Id único do comentário individual (pós-explosão de latestComments).</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5898,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -5886,7 +5913,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil que publicou o post/reel/comentário.</t>
+          <t>Texto avaliado -- comentário, legenda ou transcrição, dependendo da tabela/coluna `fonte`.</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5925,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>comprimento texto</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -5908,12 +5935,12 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Número de caracteres de `text` -- usado para filtrar comentários &gt;= 512 caracteres (CommentCleaner.MAX_TEXT_LENGTH).</t>
         </is>
       </c>
     </row>
@@ -5925,12 +5952,12 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>repliesCount</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -5940,7 +5967,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Número de respostas a um comentário.</t>
+          <t>Username do perfil que publicou o post/reel/comentário.</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5979,12 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -5967,7 +5994,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -5979,12 +6006,12 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>repliesCount</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -5994,7 +6021,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Número de respostas a um comentário.</t>
         </is>
       </c>
     </row>
@@ -6006,22 +6033,22 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6060,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -6043,12 +6070,12 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -6060,12 +6087,12 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>_source_layer</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -6075,19 +6102,19 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>post_comments_clean</t>
+          <t>comments_clean</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>id_post</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -6097,24 +6124,24 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Id do post de feed comentado (inclui reels capturados no grid de posts, issue #152) -- vira `id_reel` ao entrar em governor_sentiment.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>post_comments_clean</t>
+          <t>comments_clean</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>id_comment</t>
+          <t>_source_layer</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -6124,12 +6151,12 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Id único do comentário individual (pós-explosão de latestComments).</t>
+          <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6168,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>id_post</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -6156,7 +6183,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Texto avaliado -- comentário, legenda ou transcrição, dependendo da tabela/coluna `fonte`.</t>
+          <t>Id do post de feed comentado (inclui reels capturados no grid de posts, issue #152) -- vira `id_reel` ao entrar em governor_sentiment.</t>
         </is>
       </c>
     </row>
@@ -6168,22 +6195,22 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>comprimento texto</t>
+          <t>id_comment</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Número de caracteres de `text` -- usado para filtrar comentários &gt;= 512 caracteres (CommentCleaner.MAX_TEXT_LENGTH).</t>
+          <t>Id único do comentário individual (pós-explosão de latestComments).</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6222,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>ownerUsername</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -6210,7 +6237,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Username do perfil que publicou o post/reel/comentário.</t>
+          <t>Texto avaliado -- comentário, legenda ou transcrição, dependendo da tabela/coluna `fonte`.</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6249,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>comprimento texto</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -6232,12 +6259,12 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Número de caracteres de `text` -- usado para filtrar comentários &gt;= 512 caracteres (CommentCleaner.MAX_TEXT_LENGTH).</t>
         </is>
       </c>
     </row>
@@ -6249,12 +6276,12 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>repliesCount</t>
+          <t>ownerUsername</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -6264,7 +6291,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Número de respostas a um comentário.</t>
+          <t>Username do perfil que publicou o post/reel/comentário.</t>
         </is>
       </c>
     </row>
@@ -6276,12 +6303,12 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -6291,7 +6318,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -6303,12 +6330,12 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>repliesCount</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -6318,7 +6345,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Número de respostas a um comentário.</t>
         </is>
       </c>
     </row>
@@ -6330,22 +6357,22 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Timestamp bruto do Apify, como string ISO -- ver `data_hora` para a versão já parseada/tipada (Silver).</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6384,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -6367,12 +6394,12 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -6384,12 +6411,12 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>_source_layer</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -6399,19 +6426,19 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>governors_metadata</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>inputUrl</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -6426,19 +6453,19 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>governors_metadata</t>
+          <t>post_comments_clean</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>nome</t>
+          <t>_source_layer</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -6453,7 +6480,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Nome do governador (reference/governadores.xlsx, coluna 'Governador').</t>
+          <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6492,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>uf</t>
+          <t>inputUrl</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -6475,12 +6502,12 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Unidade Federativa do governador (reference/governadores.xlsx, coluna 'Unidade Federativa').</t>
+          <t>URL do perfil de Instagram do governador (chave de junção mais usada entre perfis/posts/reels/Gold).</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6519,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>partido</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -6502,12 +6529,12 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Partido do governador (reference/governadores.xlsx, coluna 'Partido').</t>
+          <t>Nome do governador (reference/governadores.xlsx, coluna 'Governador').</t>
         </is>
       </c>
     </row>
@@ -6519,22 +6546,22 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>uf</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Unidade Federativa do governador (reference/governadores.xlsx, coluna 'Unidade Federativa').</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6573,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>partido</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -6556,12 +6583,12 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
+          <t>Partido do governador (reference/governadores.xlsx, coluna 'Partido').</t>
         </is>
       </c>
     </row>
@@ -6573,12 +6600,12 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>_source_layer</t>
+          <t>_ingested_at</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us, tz=UTC]</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -6588,19 +6615,19 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>governors_metadata</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>_run_id</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -6610,24 +6637,24 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>ugc_mentions</t>
+          <t>governors_metadata</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>shortCode</t>
+          <t>_source_layer</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -6637,12 +6664,12 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
+          <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6681,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -6669,7 +6696,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
+          <t>Identificador único do registro na origem (Instagram/Apify) -- semântica varia por tabela, ver coluna Grão.</t>
         </is>
       </c>
     </row>
@@ -6681,7 +6708,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>caption</t>
+          <t>shortCode</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -6696,7 +6723,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Legenda/texto do post ou reel.</t>
+          <t>Código curto do post/reel usado na URL pública do Instagram.</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6735,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>governor_username</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -6723,7 +6750,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
+          <t>Tipo bruto do post retornado pelo Apify (Image/Video/Sidecar/Reel).</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6762,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>authorUsername</t>
+          <t>caption</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -6750,7 +6777,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
+          <t>Legenda/texto do post ou reel.</t>
         </is>
       </c>
     </row>
@@ -6762,22 +6789,22 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>paidPartnership</t>
+          <t>governor_username</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Flag de parceria paga (publi) declarada pelo Instagram no post de UGC -- único campo de publi que o actor real expõe (piloto 2026-09-19); `isAd`/`isAffiliate` da especificação original não existem.</t>
+          <t>Username do governador mencionado/marcado, resolvido cruzando `mentions` E `taggedUsers` (Bronze) com a lista de perfis conhecidos -- piloto real confirmou que ~69% dos posts só correlacionam via `taggedUsers`.</t>
         </is>
       </c>
     </row>
@@ -6789,22 +6816,22 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>likesCount</t>
+          <t>authorUsername</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Número de curtidas.</t>
+          <t>Username de quem publicou o post de UGC (autor, distinto do governador mencionado) -- campo normalizado na Silver; na Bronze o actor real só preenche `ownerUsername` (ver override específico de ugc_mentions, coluna `ownerUsername` colide de nome com posts/reels/comentários).</t>
         </is>
       </c>
     </row>
@@ -6816,12 +6843,12 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>commentsCount</t>
+          <t>paidPartnership</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -6831,7 +6858,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Número de comentários.</t>
+          <t>Flag de parceria paga (publi) declarada pelo Instagram no post de UGC -- único campo de publi que o actor real expõe (piloto 2026-09-19); `isAd`/`isAffiliate` da especificação original não existem.</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6870,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>videoPlayCount</t>
+          <t>likesCount</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -6853,12 +6880,12 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
+          <t>Número de curtidas.</t>
         </is>
       </c>
     </row>
@@ -6870,12 +6897,12 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>commentsCount</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us]</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -6885,7 +6912,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
+          <t>Número de comentários.</t>
         </is>
       </c>
     </row>
@@ -6897,22 +6924,22 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>_ingested_at</t>
+          <t>videoPlayCount</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>timestamp[us, tz=UTC]</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+          <t>Reproduções (plays) do vídeo -- Reels/vídeo de feed. Nome correto da métrica: "reproduções (plays)", nunca "visualizações únicas" nem alcance. Insumo de Alcance/Profundidade do governor_scorecard e do estágio "Visualizações" do funil.</t>
         </is>
       </c>
     </row>
@@ -6924,12 +6951,12 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>_run_id</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>timestamp[us]</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -6939,7 +6966,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
+          <t>Timestamp parseado e convertido para America/Sao_Paulo (naive), a partir de `timestamp` bruto (PostCleaner._parse_timestamp).</t>
         </is>
       </c>
     </row>
@@ -6951,27 +6978,81 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
+          <t>_ingested_at</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>timestamp[us, tz=UTC]</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Timestamp UTC de quando o registro entrou na camada Bronze (BronzeWriter._add_ingestion_metadata).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>_run_id</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Identificador da execução (src/run_id.py) que gravou a linha -- na Bronze, o run_id da Coleta (`coleta.py coletar`); como a Bronze é overwrite por Coleta, cada tabela Bronze tem um único run_id. Nas demais camadas, o da etapa que gravou.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>ugc_mentions</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
           <t>_source_layer</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>Camada de origem da linha na Silver -- 'bronze' para a maioria, 'raw_xlsx' só para governors_metadata.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E96"/>
+  <autoFilter ref="A1:E98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13181,7 +13262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -13189,9 +13270,10 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13222,15 +13304,20 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
+          <t>Preço por resultado (verificado em 2026-10-13)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
           <t>Parâmetros usados em produção</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Confiabilidade da fonte</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -13264,15 +13351,20 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>Pay-per-event, evento 'result'. US$ por 1.000 resultados, por plano: Free 2,70 | Bronze 2,30 | Silver 1,90 | Gold 1,50 | Platinum 0,90 | Diamond 0,50.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>directUrls=&lt;links&gt;, addParentData=False, resultsLimit=100, resultsType='details', searchType='user' (src/data_extract/scraper.py::InstagramScraper.scrape_profiles).</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>ID confirmado via api.apify.com/v2/acts/shu8hvrXbJbY3Eb9W -&gt; {"name":"instagram-scraper","username":"apify"} (docs/research/..., §0).</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>É o actor GENÉRICO "canivete suíço" da Apify, não o dedicado apify/instagram-profile-scraper -- rodado só em resultsType='details' hoje. O mesmo actor/ID também suporta resultsType='mentions'/'comments' e busca por hashtag, não explorado no pipeline atual (ver docs/research/..., §7.3, para a rota de UGC que reaproveitaria este mesmo actor sem integrar um novo).</t>
         </is>
@@ -13291,7 +13383,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>(resolvido pelo slug pela Apify -- não fixado como ID literal no código)</t>
+          <t>nH2AHrwxeTRJoN5hX (resolvido pelo slug pela Apify -- o código usa o slug, não o ID literal)</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -13306,15 +13398,20 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>Pay-per-event. Evento 'post', US$ por 1.000: Free 1,70 | Bronze 1,50 | Silver 1,30 | Gold 1,00 | Platinum 0,80 | Diamond 0,40. MAIS o evento 'post-details' ("post gravado com informação detalhada"), US$ por 1.000: Free 1,00 | Bronze 0,80 | Silver 0,70 | Gold 0,60 | Platinum 0,20 | Diamond 0,10. Se os dois incidem em cada post (a confirmar pelo faturamento da primeira Coleta de 90 dias), o total em Bronze é 2,30 por 1.000, igual aos demais actors. Add-on 'music-data' (Bronze 6,00 por 1.000 imagens/carrosséis com música) não usado.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>username=&lt;usernames&gt;, resultsLimit=30 (ScraperConfig.results_limit) + extra_run_input opcional (ex.: onlyPostsNewerThan, usado por src/coleta/coletar.py para o Recorte por janela relativa).</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Confirmado via página do actor + input-schema (docs/research/..., §1.1) -- pay-per-event, ~$1.00/1.000 posts.</t>
-        </is>
-      </c>
       <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Input-schema confirmado (docs/research/..., §1.1). Preço reverificado em 2026-10-13 pela API pública (api.apify.com/v2/acts/apify~instagram-post-scraper, pricingInfos mais recente); o '~$1.00/1.000' da pesquisa de 2026-09-08 está desatualizado (o preço mudou em 2026-03-10, 2026-07-13 e 2026-10-07).</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Não tem includeTranscript nem includeSharesCount (esses são do reel-scraper) -- não confundir com o actor genérico usado para perfis.</t>
         </is>
@@ -13333,7 +13430,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>(resolvido pelo slug pela Apify -- não fixado como ID literal no código)</t>
+          <t>xMc5Ga1oCONPmWJIa (resolvido pelo slug pela Apify -- o código usa o slug, não o ID literal)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -13348,15 +13445,20 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>Pay-per-event. Evento 'reel', US$ por 1.000: Free 2,60 | Bronze 2,30 | Silver 1,40 | Gold 1,00 | Platinum 0,80 | Diamond 0,40. MAIS 'actor-start' de US$ 0,001 fixo por execução. Add-ons não habilitados hoje: 'shares-count' (Bronze 6,00 por 1.000 reels) e 'transcript' (Bronze US$ 0,041 por minuto iniciado de vídeo).</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>username=&lt;usernames&gt;, resultsLimit=30 + includeTranscript=True SOMENTE quando ScraperConfig.include_transcript=True (default False -- flag paga, cobrada por minuto de vídeo transcrito) + extra_run_input opcional.</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Confirmado via página do actor + input-schema (docs/research/..., §1.2) -- pay-per-event, ~$1.00/1.000 reels.</t>
-        </is>
-      </c>
       <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Input-schema confirmado (docs/research/..., §1.2). Preço reverificado em 2026-10-13 pela API pública (api.apify.com/v2/acts/apify~instagram-reel-scraper, pricingInfos mais recente); o '~$1.00/1.000' da pesquisa de 2026-09-08 não vale para o plano Bronze.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Também suporta includeSharesCount (plano Starter+) e includeDownloadedVideo (cobrado por MB) -- nenhuma das duas está habilitada em ScraperConfig hoje (ver docs/research/..., §1.2, achado chave sobre sharesCount).</t>
         </is>
@@ -13375,7 +13477,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>(resolvido pelo slug pela Apify -- não fixado como ID literal no código)</t>
+          <t>zTSjdcGqjg6KEIBlt (resolvido pelo slug pela Apify -- o código usa o slug, não o ID literal)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -13390,22 +13492,27 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>Pay-per-event, evento 'post'. US$ por 1.000 posts, por plano: Free 2,70 | Bronze 2,30 | Silver 1,90 | Gold 1,50 | Platinum 1,00 | Diamond 0,50. A pesquisa de 2026-09-08 citava US$ 1,50 por 1.000, que hoje é o preço do plano Gold.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>username=&lt;usernames&gt;, resultsLimit=&lt;baixo no piloto&gt; (ScraperConfig.mentions_actor_id, InstagramScraper.scrape_mentions).</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Escolhido sobre fetch_cat/instagram-mentions-scraper por reprodutibilidade (9.999 usuários, 5.0 estrelas vs. actor community "under maintenance", 2 usuários -- docs/research/..., §7.1). Schema de output confirmado 1:1 contra os 27 perfis do projeto pelo piloto real de 2026-09-19, e validado de novo pela execução de produção do mesmo dia.</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>docs/research/apify-instagram-actors-cobra-mapping.md (§7) também mapeia uma rota alternativa sem integrar actor novo: reconfigurar o actor de perfis já em uso (shu8hvrXbJbY3Eb9W) para resultsType='mentions' -- capacidade confirmada, schema de output dessa rota específica NÃO confirmado por exemplo primário.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H5"/>
+  <autoFilter ref="A1:I5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
